--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -344,18 +344,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00_ ;[RED]\-#,##0.00\ "/>
     <numFmt numFmtId="166" formatCode="[$-F800]dddd&quot;, &quot;mmmm\ dd&quot;, &quot;yyyy"/>
-    <numFmt numFmtId="167" formatCode="d\-mmm\-yy"/>
+    <numFmt numFmtId="167" formatCode="dd\-mmm\-yy"/>
     <numFmt numFmtId="168" formatCode="[$-809]dd\ mmmm\ yyyy;@"/>
-    <numFmt numFmtId="169" formatCode="General"/>
-    <numFmt numFmtId="170" formatCode="#,##0_ ;[RED]\-#,##0\ "/>
-    <numFmt numFmtId="171" formatCode="0"/>
-    <numFmt numFmtId="172" formatCode="#,##0"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0_ ;[RED]\-#,##0.0\ "/>
-    <numFmt numFmtId="174" formatCode="0.00"/>
+    <numFmt numFmtId="169" formatCode="#,##0_ ;[RED]\-#,##0\ "/>
+    <numFmt numFmtId="170" formatCode="0"/>
+    <numFmt numFmtId="171" formatCode="#,##0"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0_ ;[RED]\-#,##0.0\ "/>
+    <numFmt numFmtId="173" formatCode="0.00"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -848,7 +847,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
@@ -872,11 +871,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
@@ -888,7 +887,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
@@ -1036,7 +1035,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1080,11 +1079,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1092,11 +1091,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1116,11 +1115,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1144,11 +1143,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1160,7 +1159,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1184,7 +1183,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1196,7 +1195,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1204,7 +1203,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1216,7 +1215,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1762,37 +1761,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1866,7 +1865,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.66"/>
@@ -2432,8 +2431,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW201"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="98" width="9.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="99" width="20.15"/>
@@ -2445,7 +2444,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="9" style="102" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="106" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="103" t="s">
         <v>29</v>
       </c>
@@ -2467,8 +2466,257 @@
         <f aca="false">SUM(H5:H500)</f>
         <v>1500</v>
       </c>
-    </row>
-    <row r="2" s="106" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
+      <c r="AC1" s="106"/>
+      <c r="AD1" s="106"/>
+      <c r="AE1" s="106"/>
+      <c r="AF1" s="106"/>
+      <c r="AG1" s="106"/>
+      <c r="AH1" s="106"/>
+      <c r="AI1" s="106"/>
+      <c r="AJ1" s="106"/>
+      <c r="AK1" s="106"/>
+      <c r="AL1" s="106"/>
+      <c r="AM1" s="106"/>
+      <c r="AN1" s="106"/>
+      <c r="AO1" s="106"/>
+      <c r="AP1" s="106"/>
+      <c r="AQ1" s="106"/>
+      <c r="AR1" s="106"/>
+      <c r="AS1" s="106"/>
+      <c r="AT1" s="106"/>
+      <c r="AU1" s="106"/>
+      <c r="AV1" s="106"/>
+      <c r="AW1" s="106"/>
+      <c r="AX1" s="106"/>
+      <c r="AY1" s="106"/>
+      <c r="AZ1" s="106"/>
+      <c r="BA1" s="106"/>
+      <c r="BB1" s="106"/>
+      <c r="BC1" s="106"/>
+      <c r="BD1" s="106"/>
+      <c r="BE1" s="106"/>
+      <c r="BF1" s="106"/>
+      <c r="BG1" s="106"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="106"/>
+      <c r="BJ1" s="106"/>
+      <c r="BK1" s="106"/>
+      <c r="BL1" s="106"/>
+      <c r="BM1" s="106"/>
+      <c r="BN1" s="106"/>
+      <c r="BO1" s="106"/>
+      <c r="BP1" s="106"/>
+      <c r="BQ1" s="106"/>
+      <c r="BR1" s="106"/>
+      <c r="BS1" s="106"/>
+      <c r="BT1" s="106"/>
+      <c r="BU1" s="106"/>
+      <c r="BV1" s="106"/>
+      <c r="BW1" s="106"/>
+      <c r="BX1" s="106"/>
+      <c r="BY1" s="106"/>
+      <c r="BZ1" s="106"/>
+      <c r="CA1" s="106"/>
+      <c r="CB1" s="106"/>
+      <c r="CC1" s="106"/>
+      <c r="CD1" s="106"/>
+      <c r="CE1" s="106"/>
+      <c r="CF1" s="106"/>
+      <c r="CG1" s="106"/>
+      <c r="CH1" s="106"/>
+      <c r="CI1" s="106"/>
+      <c r="CJ1" s="106"/>
+      <c r="CK1" s="106"/>
+      <c r="CL1" s="106"/>
+      <c r="CM1" s="106"/>
+      <c r="CN1" s="106"/>
+      <c r="CO1" s="106"/>
+      <c r="CP1" s="106"/>
+      <c r="CQ1" s="106"/>
+      <c r="CR1" s="106"/>
+      <c r="CS1" s="106"/>
+      <c r="CT1" s="106"/>
+      <c r="CU1" s="106"/>
+      <c r="CV1" s="106"/>
+      <c r="CW1" s="106"/>
+      <c r="CX1" s="106"/>
+      <c r="CY1" s="106"/>
+      <c r="CZ1" s="106"/>
+      <c r="DA1" s="106"/>
+      <c r="DB1" s="106"/>
+      <c r="DC1" s="106"/>
+      <c r="DD1" s="106"/>
+      <c r="DE1" s="106"/>
+      <c r="DF1" s="106"/>
+      <c r="DG1" s="106"/>
+      <c r="DH1" s="106"/>
+      <c r="DI1" s="106"/>
+      <c r="DJ1" s="106"/>
+      <c r="DK1" s="106"/>
+      <c r="DL1" s="106"/>
+      <c r="DM1" s="106"/>
+      <c r="DN1" s="106"/>
+      <c r="DO1" s="106"/>
+      <c r="DP1" s="106"/>
+      <c r="DQ1" s="106"/>
+      <c r="DR1" s="106"/>
+      <c r="DS1" s="106"/>
+      <c r="DT1" s="106"/>
+      <c r="DU1" s="106"/>
+      <c r="DV1" s="106"/>
+      <c r="DW1" s="106"/>
+      <c r="DX1" s="106"/>
+      <c r="DY1" s="106"/>
+      <c r="DZ1" s="106"/>
+      <c r="EA1" s="106"/>
+      <c r="EB1" s="106"/>
+      <c r="EC1" s="106"/>
+      <c r="ED1" s="106"/>
+      <c r="EE1" s="106"/>
+      <c r="EF1" s="106"/>
+      <c r="EG1" s="106"/>
+      <c r="EH1" s="106"/>
+      <c r="EI1" s="106"/>
+      <c r="EJ1" s="106"/>
+      <c r="EK1" s="106"/>
+      <c r="EL1" s="106"/>
+      <c r="EM1" s="106"/>
+      <c r="EN1" s="106"/>
+      <c r="EO1" s="106"/>
+      <c r="EP1" s="106"/>
+      <c r="EQ1" s="106"/>
+      <c r="ER1" s="106"/>
+      <c r="ES1" s="106"/>
+      <c r="ET1" s="106"/>
+      <c r="EU1" s="106"/>
+      <c r="EV1" s="106"/>
+      <c r="EW1" s="106"/>
+      <c r="EX1" s="106"/>
+      <c r="EY1" s="106"/>
+      <c r="EZ1" s="106"/>
+      <c r="FA1" s="106"/>
+      <c r="FB1" s="106"/>
+      <c r="FC1" s="106"/>
+      <c r="FD1" s="106"/>
+      <c r="FE1" s="106"/>
+      <c r="FF1" s="106"/>
+      <c r="FG1" s="106"/>
+      <c r="FH1" s="106"/>
+      <c r="FI1" s="106"/>
+      <c r="FJ1" s="106"/>
+      <c r="FK1" s="106"/>
+      <c r="FL1" s="106"/>
+      <c r="FM1" s="106"/>
+      <c r="FN1" s="106"/>
+      <c r="FO1" s="106"/>
+      <c r="FP1" s="106"/>
+      <c r="FQ1" s="106"/>
+      <c r="FR1" s="106"/>
+      <c r="FS1" s="106"/>
+      <c r="FT1" s="106"/>
+      <c r="FU1" s="106"/>
+      <c r="FV1" s="106"/>
+      <c r="FW1" s="106"/>
+      <c r="FX1" s="106"/>
+      <c r="FY1" s="106"/>
+      <c r="FZ1" s="106"/>
+      <c r="GA1" s="106"/>
+      <c r="GB1" s="106"/>
+      <c r="GC1" s="106"/>
+      <c r="GD1" s="106"/>
+      <c r="GE1" s="106"/>
+      <c r="GF1" s="106"/>
+      <c r="GG1" s="106"/>
+      <c r="GH1" s="106"/>
+      <c r="GI1" s="106"/>
+      <c r="GJ1" s="106"/>
+      <c r="GK1" s="106"/>
+      <c r="GL1" s="106"/>
+      <c r="GM1" s="106"/>
+      <c r="GN1" s="106"/>
+      <c r="GO1" s="106"/>
+      <c r="GP1" s="106"/>
+      <c r="GQ1" s="106"/>
+      <c r="GR1" s="106"/>
+      <c r="GS1" s="106"/>
+      <c r="GT1" s="106"/>
+      <c r="GU1" s="106"/>
+      <c r="GV1" s="106"/>
+      <c r="GW1" s="106"/>
+      <c r="GX1" s="106"/>
+      <c r="GY1" s="106"/>
+      <c r="GZ1" s="106"/>
+      <c r="HA1" s="106"/>
+      <c r="HB1" s="106"/>
+      <c r="HC1" s="106"/>
+      <c r="HD1" s="106"/>
+      <c r="HE1" s="106"/>
+      <c r="HF1" s="106"/>
+      <c r="HG1" s="106"/>
+      <c r="HH1" s="106"/>
+      <c r="HI1" s="106"/>
+      <c r="HJ1" s="106"/>
+      <c r="HK1" s="106"/>
+      <c r="HL1" s="106"/>
+      <c r="HM1" s="106"/>
+      <c r="HN1" s="106"/>
+      <c r="HO1" s="106"/>
+      <c r="HP1" s="106"/>
+      <c r="HQ1" s="106"/>
+      <c r="HR1" s="106"/>
+      <c r="HS1" s="106"/>
+      <c r="HT1" s="106"/>
+      <c r="HU1" s="106"/>
+      <c r="HV1" s="106"/>
+      <c r="HW1" s="106"/>
+      <c r="HX1" s="106"/>
+      <c r="HY1" s="106"/>
+      <c r="HZ1" s="106"/>
+      <c r="IA1" s="106"/>
+      <c r="IB1" s="106"/>
+      <c r="IC1" s="106"/>
+      <c r="ID1" s="106"/>
+      <c r="IE1" s="106"/>
+      <c r="IF1" s="106"/>
+      <c r="IG1" s="106"/>
+      <c r="IH1" s="106"/>
+      <c r="II1" s="106"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="106"/>
+      <c r="IL1" s="106"/>
+      <c r="IM1" s="106"/>
+      <c r="IN1" s="106"/>
+      <c r="IO1" s="106"/>
+      <c r="IP1" s="106"/>
+      <c r="IQ1" s="106"/>
+      <c r="IR1" s="106"/>
+      <c r="IS1" s="106"/>
+      <c r="IT1" s="106"/>
+      <c r="IU1" s="106"/>
+      <c r="IV1" s="106"/>
+      <c r="IW1" s="106"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
         <v>31</v>
       </c>
@@ -2492,8 +2740,257 @@
       <c r="H2" s="108" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" s="112" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="106"/>
+      <c r="R2" s="106"/>
+      <c r="S2" s="106"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="106"/>
+      <c r="W2" s="106"/>
+      <c r="X2" s="106"/>
+      <c r="Y2" s="106"/>
+      <c r="Z2" s="106"/>
+      <c r="AA2" s="106"/>
+      <c r="AB2" s="106"/>
+      <c r="AC2" s="106"/>
+      <c r="AD2" s="106"/>
+      <c r="AE2" s="106"/>
+      <c r="AF2" s="106"/>
+      <c r="AG2" s="106"/>
+      <c r="AH2" s="106"/>
+      <c r="AI2" s="106"/>
+      <c r="AJ2" s="106"/>
+      <c r="AK2" s="106"/>
+      <c r="AL2" s="106"/>
+      <c r="AM2" s="106"/>
+      <c r="AN2" s="106"/>
+      <c r="AO2" s="106"/>
+      <c r="AP2" s="106"/>
+      <c r="AQ2" s="106"/>
+      <c r="AR2" s="106"/>
+      <c r="AS2" s="106"/>
+      <c r="AT2" s="106"/>
+      <c r="AU2" s="106"/>
+      <c r="AV2" s="106"/>
+      <c r="AW2" s="106"/>
+      <c r="AX2" s="106"/>
+      <c r="AY2" s="106"/>
+      <c r="AZ2" s="106"/>
+      <c r="BA2" s="106"/>
+      <c r="BB2" s="106"/>
+      <c r="BC2" s="106"/>
+      <c r="BD2" s="106"/>
+      <c r="BE2" s="106"/>
+      <c r="BF2" s="106"/>
+      <c r="BG2" s="106"/>
+      <c r="BH2" s="106"/>
+      <c r="BI2" s="106"/>
+      <c r="BJ2" s="106"/>
+      <c r="BK2" s="106"/>
+      <c r="BL2" s="106"/>
+      <c r="BM2" s="106"/>
+      <c r="BN2" s="106"/>
+      <c r="BO2" s="106"/>
+      <c r="BP2" s="106"/>
+      <c r="BQ2" s="106"/>
+      <c r="BR2" s="106"/>
+      <c r="BS2" s="106"/>
+      <c r="BT2" s="106"/>
+      <c r="BU2" s="106"/>
+      <c r="BV2" s="106"/>
+      <c r="BW2" s="106"/>
+      <c r="BX2" s="106"/>
+      <c r="BY2" s="106"/>
+      <c r="BZ2" s="106"/>
+      <c r="CA2" s="106"/>
+      <c r="CB2" s="106"/>
+      <c r="CC2" s="106"/>
+      <c r="CD2" s="106"/>
+      <c r="CE2" s="106"/>
+      <c r="CF2" s="106"/>
+      <c r="CG2" s="106"/>
+      <c r="CH2" s="106"/>
+      <c r="CI2" s="106"/>
+      <c r="CJ2" s="106"/>
+      <c r="CK2" s="106"/>
+      <c r="CL2" s="106"/>
+      <c r="CM2" s="106"/>
+      <c r="CN2" s="106"/>
+      <c r="CO2" s="106"/>
+      <c r="CP2" s="106"/>
+      <c r="CQ2" s="106"/>
+      <c r="CR2" s="106"/>
+      <c r="CS2" s="106"/>
+      <c r="CT2" s="106"/>
+      <c r="CU2" s="106"/>
+      <c r="CV2" s="106"/>
+      <c r="CW2" s="106"/>
+      <c r="CX2" s="106"/>
+      <c r="CY2" s="106"/>
+      <c r="CZ2" s="106"/>
+      <c r="DA2" s="106"/>
+      <c r="DB2" s="106"/>
+      <c r="DC2" s="106"/>
+      <c r="DD2" s="106"/>
+      <c r="DE2" s="106"/>
+      <c r="DF2" s="106"/>
+      <c r="DG2" s="106"/>
+      <c r="DH2" s="106"/>
+      <c r="DI2" s="106"/>
+      <c r="DJ2" s="106"/>
+      <c r="DK2" s="106"/>
+      <c r="DL2" s="106"/>
+      <c r="DM2" s="106"/>
+      <c r="DN2" s="106"/>
+      <c r="DO2" s="106"/>
+      <c r="DP2" s="106"/>
+      <c r="DQ2" s="106"/>
+      <c r="DR2" s="106"/>
+      <c r="DS2" s="106"/>
+      <c r="DT2" s="106"/>
+      <c r="DU2" s="106"/>
+      <c r="DV2" s="106"/>
+      <c r="DW2" s="106"/>
+      <c r="DX2" s="106"/>
+      <c r="DY2" s="106"/>
+      <c r="DZ2" s="106"/>
+      <c r="EA2" s="106"/>
+      <c r="EB2" s="106"/>
+      <c r="EC2" s="106"/>
+      <c r="ED2" s="106"/>
+      <c r="EE2" s="106"/>
+      <c r="EF2" s="106"/>
+      <c r="EG2" s="106"/>
+      <c r="EH2" s="106"/>
+      <c r="EI2" s="106"/>
+      <c r="EJ2" s="106"/>
+      <c r="EK2" s="106"/>
+      <c r="EL2" s="106"/>
+      <c r="EM2" s="106"/>
+      <c r="EN2" s="106"/>
+      <c r="EO2" s="106"/>
+      <c r="EP2" s="106"/>
+      <c r="EQ2" s="106"/>
+      <c r="ER2" s="106"/>
+      <c r="ES2" s="106"/>
+      <c r="ET2" s="106"/>
+      <c r="EU2" s="106"/>
+      <c r="EV2" s="106"/>
+      <c r="EW2" s="106"/>
+      <c r="EX2" s="106"/>
+      <c r="EY2" s="106"/>
+      <c r="EZ2" s="106"/>
+      <c r="FA2" s="106"/>
+      <c r="FB2" s="106"/>
+      <c r="FC2" s="106"/>
+      <c r="FD2" s="106"/>
+      <c r="FE2" s="106"/>
+      <c r="FF2" s="106"/>
+      <c r="FG2" s="106"/>
+      <c r="FH2" s="106"/>
+      <c r="FI2" s="106"/>
+      <c r="FJ2" s="106"/>
+      <c r="FK2" s="106"/>
+      <c r="FL2" s="106"/>
+      <c r="FM2" s="106"/>
+      <c r="FN2" s="106"/>
+      <c r="FO2" s="106"/>
+      <c r="FP2" s="106"/>
+      <c r="FQ2" s="106"/>
+      <c r="FR2" s="106"/>
+      <c r="FS2" s="106"/>
+      <c r="FT2" s="106"/>
+      <c r="FU2" s="106"/>
+      <c r="FV2" s="106"/>
+      <c r="FW2" s="106"/>
+      <c r="FX2" s="106"/>
+      <c r="FY2" s="106"/>
+      <c r="FZ2" s="106"/>
+      <c r="GA2" s="106"/>
+      <c r="GB2" s="106"/>
+      <c r="GC2" s="106"/>
+      <c r="GD2" s="106"/>
+      <c r="GE2" s="106"/>
+      <c r="GF2" s="106"/>
+      <c r="GG2" s="106"/>
+      <c r="GH2" s="106"/>
+      <c r="GI2" s="106"/>
+      <c r="GJ2" s="106"/>
+      <c r="GK2" s="106"/>
+      <c r="GL2" s="106"/>
+      <c r="GM2" s="106"/>
+      <c r="GN2" s="106"/>
+      <c r="GO2" s="106"/>
+      <c r="GP2" s="106"/>
+      <c r="GQ2" s="106"/>
+      <c r="GR2" s="106"/>
+      <c r="GS2" s="106"/>
+      <c r="GT2" s="106"/>
+      <c r="GU2" s="106"/>
+      <c r="GV2" s="106"/>
+      <c r="GW2" s="106"/>
+      <c r="GX2" s="106"/>
+      <c r="GY2" s="106"/>
+      <c r="GZ2" s="106"/>
+      <c r="HA2" s="106"/>
+      <c r="HB2" s="106"/>
+      <c r="HC2" s="106"/>
+      <c r="HD2" s="106"/>
+      <c r="HE2" s="106"/>
+      <c r="HF2" s="106"/>
+      <c r="HG2" s="106"/>
+      <c r="HH2" s="106"/>
+      <c r="HI2" s="106"/>
+      <c r="HJ2" s="106"/>
+      <c r="HK2" s="106"/>
+      <c r="HL2" s="106"/>
+      <c r="HM2" s="106"/>
+      <c r="HN2" s="106"/>
+      <c r="HO2" s="106"/>
+      <c r="HP2" s="106"/>
+      <c r="HQ2" s="106"/>
+      <c r="HR2" s="106"/>
+      <c r="HS2" s="106"/>
+      <c r="HT2" s="106"/>
+      <c r="HU2" s="106"/>
+      <c r="HV2" s="106"/>
+      <c r="HW2" s="106"/>
+      <c r="HX2" s="106"/>
+      <c r="HY2" s="106"/>
+      <c r="HZ2" s="106"/>
+      <c r="IA2" s="106"/>
+      <c r="IB2" s="106"/>
+      <c r="IC2" s="106"/>
+      <c r="ID2" s="106"/>
+      <c r="IE2" s="106"/>
+      <c r="IF2" s="106"/>
+      <c r="IG2" s="106"/>
+      <c r="IH2" s="106"/>
+      <c r="II2" s="106"/>
+      <c r="IJ2" s="106"/>
+      <c r="IK2" s="106"/>
+      <c r="IL2" s="106"/>
+      <c r="IM2" s="106"/>
+      <c r="IN2" s="106"/>
+      <c r="IO2" s="106"/>
+      <c r="IP2" s="106"/>
+      <c r="IQ2" s="106"/>
+      <c r="IR2" s="106"/>
+      <c r="IS2" s="106"/>
+      <c r="IT2" s="106"/>
+      <c r="IU2" s="106"/>
+      <c r="IV2" s="106"/>
+      <c r="IW2" s="106"/>
+    </row>
+    <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="107"/>
       <c r="B3" s="108"/>
       <c r="C3" s="109"/>
@@ -2504,6 +3001,255 @@
         <v>37</v>
       </c>
       <c r="H3" s="108"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
+      <c r="L3" s="112"/>
+      <c r="M3" s="112"/>
+      <c r="N3" s="112"/>
+      <c r="O3" s="112"/>
+      <c r="P3" s="112"/>
+      <c r="Q3" s="112"/>
+      <c r="R3" s="112"/>
+      <c r="S3" s="112"/>
+      <c r="T3" s="112"/>
+      <c r="U3" s="112"/>
+      <c r="V3" s="112"/>
+      <c r="W3" s="112"/>
+      <c r="X3" s="112"/>
+      <c r="Y3" s="112"/>
+      <c r="Z3" s="112"/>
+      <c r="AA3" s="112"/>
+      <c r="AB3" s="112"/>
+      <c r="AC3" s="112"/>
+      <c r="AD3" s="112"/>
+      <c r="AE3" s="112"/>
+      <c r="AF3" s="112"/>
+      <c r="AG3" s="112"/>
+      <c r="AH3" s="112"/>
+      <c r="AI3" s="112"/>
+      <c r="AJ3" s="112"/>
+      <c r="AK3" s="112"/>
+      <c r="AL3" s="112"/>
+      <c r="AM3" s="112"/>
+      <c r="AN3" s="112"/>
+      <c r="AO3" s="112"/>
+      <c r="AP3" s="112"/>
+      <c r="AQ3" s="112"/>
+      <c r="AR3" s="112"/>
+      <c r="AS3" s="112"/>
+      <c r="AT3" s="112"/>
+      <c r="AU3" s="112"/>
+      <c r="AV3" s="112"/>
+      <c r="AW3" s="112"/>
+      <c r="AX3" s="112"/>
+      <c r="AY3" s="112"/>
+      <c r="AZ3" s="112"/>
+      <c r="BA3" s="112"/>
+      <c r="BB3" s="112"/>
+      <c r="BC3" s="112"/>
+      <c r="BD3" s="112"/>
+      <c r="BE3" s="112"/>
+      <c r="BF3" s="112"/>
+      <c r="BG3" s="112"/>
+      <c r="BH3" s="112"/>
+      <c r="BI3" s="112"/>
+      <c r="BJ3" s="112"/>
+      <c r="BK3" s="112"/>
+      <c r="BL3" s="112"/>
+      <c r="BM3" s="112"/>
+      <c r="BN3" s="112"/>
+      <c r="BO3" s="112"/>
+      <c r="BP3" s="112"/>
+      <c r="BQ3" s="112"/>
+      <c r="BR3" s="112"/>
+      <c r="BS3" s="112"/>
+      <c r="BT3" s="112"/>
+      <c r="BU3" s="112"/>
+      <c r="BV3" s="112"/>
+      <c r="BW3" s="112"/>
+      <c r="BX3" s="112"/>
+      <c r="BY3" s="112"/>
+      <c r="BZ3" s="112"/>
+      <c r="CA3" s="112"/>
+      <c r="CB3" s="112"/>
+      <c r="CC3" s="112"/>
+      <c r="CD3" s="112"/>
+      <c r="CE3" s="112"/>
+      <c r="CF3" s="112"/>
+      <c r="CG3" s="112"/>
+      <c r="CH3" s="112"/>
+      <c r="CI3" s="112"/>
+      <c r="CJ3" s="112"/>
+      <c r="CK3" s="112"/>
+      <c r="CL3" s="112"/>
+      <c r="CM3" s="112"/>
+      <c r="CN3" s="112"/>
+      <c r="CO3" s="112"/>
+      <c r="CP3" s="112"/>
+      <c r="CQ3" s="112"/>
+      <c r="CR3" s="112"/>
+      <c r="CS3" s="112"/>
+      <c r="CT3" s="112"/>
+      <c r="CU3" s="112"/>
+      <c r="CV3" s="112"/>
+      <c r="CW3" s="112"/>
+      <c r="CX3" s="112"/>
+      <c r="CY3" s="112"/>
+      <c r="CZ3" s="112"/>
+      <c r="DA3" s="112"/>
+      <c r="DB3" s="112"/>
+      <c r="DC3" s="112"/>
+      <c r="DD3" s="112"/>
+      <c r="DE3" s="112"/>
+      <c r="DF3" s="112"/>
+      <c r="DG3" s="112"/>
+      <c r="DH3" s="112"/>
+      <c r="DI3" s="112"/>
+      <c r="DJ3" s="112"/>
+      <c r="DK3" s="112"/>
+      <c r="DL3" s="112"/>
+      <c r="DM3" s="112"/>
+      <c r="DN3" s="112"/>
+      <c r="DO3" s="112"/>
+      <c r="DP3" s="112"/>
+      <c r="DQ3" s="112"/>
+      <c r="DR3" s="112"/>
+      <c r="DS3" s="112"/>
+      <c r="DT3" s="112"/>
+      <c r="DU3" s="112"/>
+      <c r="DV3" s="112"/>
+      <c r="DW3" s="112"/>
+      <c r="DX3" s="112"/>
+      <c r="DY3" s="112"/>
+      <c r="DZ3" s="112"/>
+      <c r="EA3" s="112"/>
+      <c r="EB3" s="112"/>
+      <c r="EC3" s="112"/>
+      <c r="ED3" s="112"/>
+      <c r="EE3" s="112"/>
+      <c r="EF3" s="112"/>
+      <c r="EG3" s="112"/>
+      <c r="EH3" s="112"/>
+      <c r="EI3" s="112"/>
+      <c r="EJ3" s="112"/>
+      <c r="EK3" s="112"/>
+      <c r="EL3" s="112"/>
+      <c r="EM3" s="112"/>
+      <c r="EN3" s="112"/>
+      <c r="EO3" s="112"/>
+      <c r="EP3" s="112"/>
+      <c r="EQ3" s="112"/>
+      <c r="ER3" s="112"/>
+      <c r="ES3" s="112"/>
+      <c r="ET3" s="112"/>
+      <c r="EU3" s="112"/>
+      <c r="EV3" s="112"/>
+      <c r="EW3" s="112"/>
+      <c r="EX3" s="112"/>
+      <c r="EY3" s="112"/>
+      <c r="EZ3" s="112"/>
+      <c r="FA3" s="112"/>
+      <c r="FB3" s="112"/>
+      <c r="FC3" s="112"/>
+      <c r="FD3" s="112"/>
+      <c r="FE3" s="112"/>
+      <c r="FF3" s="112"/>
+      <c r="FG3" s="112"/>
+      <c r="FH3" s="112"/>
+      <c r="FI3" s="112"/>
+      <c r="FJ3" s="112"/>
+      <c r="FK3" s="112"/>
+      <c r="FL3" s="112"/>
+      <c r="FM3" s="112"/>
+      <c r="FN3" s="112"/>
+      <c r="FO3" s="112"/>
+      <c r="FP3" s="112"/>
+      <c r="FQ3" s="112"/>
+      <c r="FR3" s="112"/>
+      <c r="FS3" s="112"/>
+      <c r="FT3" s="112"/>
+      <c r="FU3" s="112"/>
+      <c r="FV3" s="112"/>
+      <c r="FW3" s="112"/>
+      <c r="FX3" s="112"/>
+      <c r="FY3" s="112"/>
+      <c r="FZ3" s="112"/>
+      <c r="GA3" s="112"/>
+      <c r="GB3" s="112"/>
+      <c r="GC3" s="112"/>
+      <c r="GD3" s="112"/>
+      <c r="GE3" s="112"/>
+      <c r="GF3" s="112"/>
+      <c r="GG3" s="112"/>
+      <c r="GH3" s="112"/>
+      <c r="GI3" s="112"/>
+      <c r="GJ3" s="112"/>
+      <c r="GK3" s="112"/>
+      <c r="GL3" s="112"/>
+      <c r="GM3" s="112"/>
+      <c r="GN3" s="112"/>
+      <c r="GO3" s="112"/>
+      <c r="GP3" s="112"/>
+      <c r="GQ3" s="112"/>
+      <c r="GR3" s="112"/>
+      <c r="GS3" s="112"/>
+      <c r="GT3" s="112"/>
+      <c r="GU3" s="112"/>
+      <c r="GV3" s="112"/>
+      <c r="GW3" s="112"/>
+      <c r="GX3" s="112"/>
+      <c r="GY3" s="112"/>
+      <c r="GZ3" s="112"/>
+      <c r="HA3" s="112"/>
+      <c r="HB3" s="112"/>
+      <c r="HC3" s="112"/>
+      <c r="HD3" s="112"/>
+      <c r="HE3" s="112"/>
+      <c r="HF3" s="112"/>
+      <c r="HG3" s="112"/>
+      <c r="HH3" s="112"/>
+      <c r="HI3" s="112"/>
+      <c r="HJ3" s="112"/>
+      <c r="HK3" s="112"/>
+      <c r="HL3" s="112"/>
+      <c r="HM3" s="112"/>
+      <c r="HN3" s="112"/>
+      <c r="HO3" s="112"/>
+      <c r="HP3" s="112"/>
+      <c r="HQ3" s="112"/>
+      <c r="HR3" s="112"/>
+      <c r="HS3" s="112"/>
+      <c r="HT3" s="112"/>
+      <c r="HU3" s="112"/>
+      <c r="HV3" s="112"/>
+      <c r="HW3" s="112"/>
+      <c r="HX3" s="112"/>
+      <c r="HY3" s="112"/>
+      <c r="HZ3" s="112"/>
+      <c r="IA3" s="112"/>
+      <c r="IB3" s="112"/>
+      <c r="IC3" s="112"/>
+      <c r="ID3" s="112"/>
+      <c r="IE3" s="112"/>
+      <c r="IF3" s="112"/>
+      <c r="IG3" s="112"/>
+      <c r="IH3" s="112"/>
+      <c r="II3" s="112"/>
+      <c r="IJ3" s="112"/>
+      <c r="IK3" s="112"/>
+      <c r="IL3" s="112"/>
+      <c r="IM3" s="112"/>
+      <c r="IN3" s="112"/>
+      <c r="IO3" s="112"/>
+      <c r="IP3" s="112"/>
+      <c r="IQ3" s="112"/>
+      <c r="IR3" s="112"/>
+      <c r="IS3" s="112"/>
+      <c r="IT3" s="112"/>
+      <c r="IU3" s="112"/>
+      <c r="IV3" s="112"/>
+      <c r="IW3" s="112"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="107"/>
@@ -4528,8 +5274,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW201"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="98" width="9.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="99" width="20.15"/>
@@ -4541,7 +5287,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="9" style="102" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="106" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="103" t="s">
         <v>29</v>
       </c>
@@ -4563,8 +5309,257 @@
         <f aca="false">SUM(H5:H500)</f>
         <v>1000</v>
       </c>
-    </row>
-    <row r="2" s="106" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
+      <c r="AC1" s="106"/>
+      <c r="AD1" s="106"/>
+      <c r="AE1" s="106"/>
+      <c r="AF1" s="106"/>
+      <c r="AG1" s="106"/>
+      <c r="AH1" s="106"/>
+      <c r="AI1" s="106"/>
+      <c r="AJ1" s="106"/>
+      <c r="AK1" s="106"/>
+      <c r="AL1" s="106"/>
+      <c r="AM1" s="106"/>
+      <c r="AN1" s="106"/>
+      <c r="AO1" s="106"/>
+      <c r="AP1" s="106"/>
+      <c r="AQ1" s="106"/>
+      <c r="AR1" s="106"/>
+      <c r="AS1" s="106"/>
+      <c r="AT1" s="106"/>
+      <c r="AU1" s="106"/>
+      <c r="AV1" s="106"/>
+      <c r="AW1" s="106"/>
+      <c r="AX1" s="106"/>
+      <c r="AY1" s="106"/>
+      <c r="AZ1" s="106"/>
+      <c r="BA1" s="106"/>
+      <c r="BB1" s="106"/>
+      <c r="BC1" s="106"/>
+      <c r="BD1" s="106"/>
+      <c r="BE1" s="106"/>
+      <c r="BF1" s="106"/>
+      <c r="BG1" s="106"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="106"/>
+      <c r="BJ1" s="106"/>
+      <c r="BK1" s="106"/>
+      <c r="BL1" s="106"/>
+      <c r="BM1" s="106"/>
+      <c r="BN1" s="106"/>
+      <c r="BO1" s="106"/>
+      <c r="BP1" s="106"/>
+      <c r="BQ1" s="106"/>
+      <c r="BR1" s="106"/>
+      <c r="BS1" s="106"/>
+      <c r="BT1" s="106"/>
+      <c r="BU1" s="106"/>
+      <c r="BV1" s="106"/>
+      <c r="BW1" s="106"/>
+      <c r="BX1" s="106"/>
+      <c r="BY1" s="106"/>
+      <c r="BZ1" s="106"/>
+      <c r="CA1" s="106"/>
+      <c r="CB1" s="106"/>
+      <c r="CC1" s="106"/>
+      <c r="CD1" s="106"/>
+      <c r="CE1" s="106"/>
+      <c r="CF1" s="106"/>
+      <c r="CG1" s="106"/>
+      <c r="CH1" s="106"/>
+      <c r="CI1" s="106"/>
+      <c r="CJ1" s="106"/>
+      <c r="CK1" s="106"/>
+      <c r="CL1" s="106"/>
+      <c r="CM1" s="106"/>
+      <c r="CN1" s="106"/>
+      <c r="CO1" s="106"/>
+      <c r="CP1" s="106"/>
+      <c r="CQ1" s="106"/>
+      <c r="CR1" s="106"/>
+      <c r="CS1" s="106"/>
+      <c r="CT1" s="106"/>
+      <c r="CU1" s="106"/>
+      <c r="CV1" s="106"/>
+      <c r="CW1" s="106"/>
+      <c r="CX1" s="106"/>
+      <c r="CY1" s="106"/>
+      <c r="CZ1" s="106"/>
+      <c r="DA1" s="106"/>
+      <c r="DB1" s="106"/>
+      <c r="DC1" s="106"/>
+      <c r="DD1" s="106"/>
+      <c r="DE1" s="106"/>
+      <c r="DF1" s="106"/>
+      <c r="DG1" s="106"/>
+      <c r="DH1" s="106"/>
+      <c r="DI1" s="106"/>
+      <c r="DJ1" s="106"/>
+      <c r="DK1" s="106"/>
+      <c r="DL1" s="106"/>
+      <c r="DM1" s="106"/>
+      <c r="DN1" s="106"/>
+      <c r="DO1" s="106"/>
+      <c r="DP1" s="106"/>
+      <c r="DQ1" s="106"/>
+      <c r="DR1" s="106"/>
+      <c r="DS1" s="106"/>
+      <c r="DT1" s="106"/>
+      <c r="DU1" s="106"/>
+      <c r="DV1" s="106"/>
+      <c r="DW1" s="106"/>
+      <c r="DX1" s="106"/>
+      <c r="DY1" s="106"/>
+      <c r="DZ1" s="106"/>
+      <c r="EA1" s="106"/>
+      <c r="EB1" s="106"/>
+      <c r="EC1" s="106"/>
+      <c r="ED1" s="106"/>
+      <c r="EE1" s="106"/>
+      <c r="EF1" s="106"/>
+      <c r="EG1" s="106"/>
+      <c r="EH1" s="106"/>
+      <c r="EI1" s="106"/>
+      <c r="EJ1" s="106"/>
+      <c r="EK1" s="106"/>
+      <c r="EL1" s="106"/>
+      <c r="EM1" s="106"/>
+      <c r="EN1" s="106"/>
+      <c r="EO1" s="106"/>
+      <c r="EP1" s="106"/>
+      <c r="EQ1" s="106"/>
+      <c r="ER1" s="106"/>
+      <c r="ES1" s="106"/>
+      <c r="ET1" s="106"/>
+      <c r="EU1" s="106"/>
+      <c r="EV1" s="106"/>
+      <c r="EW1" s="106"/>
+      <c r="EX1" s="106"/>
+      <c r="EY1" s="106"/>
+      <c r="EZ1" s="106"/>
+      <c r="FA1" s="106"/>
+      <c r="FB1" s="106"/>
+      <c r="FC1" s="106"/>
+      <c r="FD1" s="106"/>
+      <c r="FE1" s="106"/>
+      <c r="FF1" s="106"/>
+      <c r="FG1" s="106"/>
+      <c r="FH1" s="106"/>
+      <c r="FI1" s="106"/>
+      <c r="FJ1" s="106"/>
+      <c r="FK1" s="106"/>
+      <c r="FL1" s="106"/>
+      <c r="FM1" s="106"/>
+      <c r="FN1" s="106"/>
+      <c r="FO1" s="106"/>
+      <c r="FP1" s="106"/>
+      <c r="FQ1" s="106"/>
+      <c r="FR1" s="106"/>
+      <c r="FS1" s="106"/>
+      <c r="FT1" s="106"/>
+      <c r="FU1" s="106"/>
+      <c r="FV1" s="106"/>
+      <c r="FW1" s="106"/>
+      <c r="FX1" s="106"/>
+      <c r="FY1" s="106"/>
+      <c r="FZ1" s="106"/>
+      <c r="GA1" s="106"/>
+      <c r="GB1" s="106"/>
+      <c r="GC1" s="106"/>
+      <c r="GD1" s="106"/>
+      <c r="GE1" s="106"/>
+      <c r="GF1" s="106"/>
+      <c r="GG1" s="106"/>
+      <c r="GH1" s="106"/>
+      <c r="GI1" s="106"/>
+      <c r="GJ1" s="106"/>
+      <c r="GK1" s="106"/>
+      <c r="GL1" s="106"/>
+      <c r="GM1" s="106"/>
+      <c r="GN1" s="106"/>
+      <c r="GO1" s="106"/>
+      <c r="GP1" s="106"/>
+      <c r="GQ1" s="106"/>
+      <c r="GR1" s="106"/>
+      <c r="GS1" s="106"/>
+      <c r="GT1" s="106"/>
+      <c r="GU1" s="106"/>
+      <c r="GV1" s="106"/>
+      <c r="GW1" s="106"/>
+      <c r="GX1" s="106"/>
+      <c r="GY1" s="106"/>
+      <c r="GZ1" s="106"/>
+      <c r="HA1" s="106"/>
+      <c r="HB1" s="106"/>
+      <c r="HC1" s="106"/>
+      <c r="HD1" s="106"/>
+      <c r="HE1" s="106"/>
+      <c r="HF1" s="106"/>
+      <c r="HG1" s="106"/>
+      <c r="HH1" s="106"/>
+      <c r="HI1" s="106"/>
+      <c r="HJ1" s="106"/>
+      <c r="HK1" s="106"/>
+      <c r="HL1" s="106"/>
+      <c r="HM1" s="106"/>
+      <c r="HN1" s="106"/>
+      <c r="HO1" s="106"/>
+      <c r="HP1" s="106"/>
+      <c r="HQ1" s="106"/>
+      <c r="HR1" s="106"/>
+      <c r="HS1" s="106"/>
+      <c r="HT1" s="106"/>
+      <c r="HU1" s="106"/>
+      <c r="HV1" s="106"/>
+      <c r="HW1" s="106"/>
+      <c r="HX1" s="106"/>
+      <c r="HY1" s="106"/>
+      <c r="HZ1" s="106"/>
+      <c r="IA1" s="106"/>
+      <c r="IB1" s="106"/>
+      <c r="IC1" s="106"/>
+      <c r="ID1" s="106"/>
+      <c r="IE1" s="106"/>
+      <c r="IF1" s="106"/>
+      <c r="IG1" s="106"/>
+      <c r="IH1" s="106"/>
+      <c r="II1" s="106"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="106"/>
+      <c r="IL1" s="106"/>
+      <c r="IM1" s="106"/>
+      <c r="IN1" s="106"/>
+      <c r="IO1" s="106"/>
+      <c r="IP1" s="106"/>
+      <c r="IQ1" s="106"/>
+      <c r="IR1" s="106"/>
+      <c r="IS1" s="106"/>
+      <c r="IT1" s="106"/>
+      <c r="IU1" s="106"/>
+      <c r="IV1" s="106"/>
+      <c r="IW1" s="106"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
         <v>31</v>
       </c>
@@ -4588,8 +5583,257 @@
       <c r="H2" s="108" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" s="112" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="106"/>
+      <c r="R2" s="106"/>
+      <c r="S2" s="106"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="106"/>
+      <c r="W2" s="106"/>
+      <c r="X2" s="106"/>
+      <c r="Y2" s="106"/>
+      <c r="Z2" s="106"/>
+      <c r="AA2" s="106"/>
+      <c r="AB2" s="106"/>
+      <c r="AC2" s="106"/>
+      <c r="AD2" s="106"/>
+      <c r="AE2" s="106"/>
+      <c r="AF2" s="106"/>
+      <c r="AG2" s="106"/>
+      <c r="AH2" s="106"/>
+      <c r="AI2" s="106"/>
+      <c r="AJ2" s="106"/>
+      <c r="AK2" s="106"/>
+      <c r="AL2" s="106"/>
+      <c r="AM2" s="106"/>
+      <c r="AN2" s="106"/>
+      <c r="AO2" s="106"/>
+      <c r="AP2" s="106"/>
+      <c r="AQ2" s="106"/>
+      <c r="AR2" s="106"/>
+      <c r="AS2" s="106"/>
+      <c r="AT2" s="106"/>
+      <c r="AU2" s="106"/>
+      <c r="AV2" s="106"/>
+      <c r="AW2" s="106"/>
+      <c r="AX2" s="106"/>
+      <c r="AY2" s="106"/>
+      <c r="AZ2" s="106"/>
+      <c r="BA2" s="106"/>
+      <c r="BB2" s="106"/>
+      <c r="BC2" s="106"/>
+      <c r="BD2" s="106"/>
+      <c r="BE2" s="106"/>
+      <c r="BF2" s="106"/>
+      <c r="BG2" s="106"/>
+      <c r="BH2" s="106"/>
+      <c r="BI2" s="106"/>
+      <c r="BJ2" s="106"/>
+      <c r="BK2" s="106"/>
+      <c r="BL2" s="106"/>
+      <c r="BM2" s="106"/>
+      <c r="BN2" s="106"/>
+      <c r="BO2" s="106"/>
+      <c r="BP2" s="106"/>
+      <c r="BQ2" s="106"/>
+      <c r="BR2" s="106"/>
+      <c r="BS2" s="106"/>
+      <c r="BT2" s="106"/>
+      <c r="BU2" s="106"/>
+      <c r="BV2" s="106"/>
+      <c r="BW2" s="106"/>
+      <c r="BX2" s="106"/>
+      <c r="BY2" s="106"/>
+      <c r="BZ2" s="106"/>
+      <c r="CA2" s="106"/>
+      <c r="CB2" s="106"/>
+      <c r="CC2" s="106"/>
+      <c r="CD2" s="106"/>
+      <c r="CE2" s="106"/>
+      <c r="CF2" s="106"/>
+      <c r="CG2" s="106"/>
+      <c r="CH2" s="106"/>
+      <c r="CI2" s="106"/>
+      <c r="CJ2" s="106"/>
+      <c r="CK2" s="106"/>
+      <c r="CL2" s="106"/>
+      <c r="CM2" s="106"/>
+      <c r="CN2" s="106"/>
+      <c r="CO2" s="106"/>
+      <c r="CP2" s="106"/>
+      <c r="CQ2" s="106"/>
+      <c r="CR2" s="106"/>
+      <c r="CS2" s="106"/>
+      <c r="CT2" s="106"/>
+      <c r="CU2" s="106"/>
+      <c r="CV2" s="106"/>
+      <c r="CW2" s="106"/>
+      <c r="CX2" s="106"/>
+      <c r="CY2" s="106"/>
+      <c r="CZ2" s="106"/>
+      <c r="DA2" s="106"/>
+      <c r="DB2" s="106"/>
+      <c r="DC2" s="106"/>
+      <c r="DD2" s="106"/>
+      <c r="DE2" s="106"/>
+      <c r="DF2" s="106"/>
+      <c r="DG2" s="106"/>
+      <c r="DH2" s="106"/>
+      <c r="DI2" s="106"/>
+      <c r="DJ2" s="106"/>
+      <c r="DK2" s="106"/>
+      <c r="DL2" s="106"/>
+      <c r="DM2" s="106"/>
+      <c r="DN2" s="106"/>
+      <c r="DO2" s="106"/>
+      <c r="DP2" s="106"/>
+      <c r="DQ2" s="106"/>
+      <c r="DR2" s="106"/>
+      <c r="DS2" s="106"/>
+      <c r="DT2" s="106"/>
+      <c r="DU2" s="106"/>
+      <c r="DV2" s="106"/>
+      <c r="DW2" s="106"/>
+      <c r="DX2" s="106"/>
+      <c r="DY2" s="106"/>
+      <c r="DZ2" s="106"/>
+      <c r="EA2" s="106"/>
+      <c r="EB2" s="106"/>
+      <c r="EC2" s="106"/>
+      <c r="ED2" s="106"/>
+      <c r="EE2" s="106"/>
+      <c r="EF2" s="106"/>
+      <c r="EG2" s="106"/>
+      <c r="EH2" s="106"/>
+      <c r="EI2" s="106"/>
+      <c r="EJ2" s="106"/>
+      <c r="EK2" s="106"/>
+      <c r="EL2" s="106"/>
+      <c r="EM2" s="106"/>
+      <c r="EN2" s="106"/>
+      <c r="EO2" s="106"/>
+      <c r="EP2" s="106"/>
+      <c r="EQ2" s="106"/>
+      <c r="ER2" s="106"/>
+      <c r="ES2" s="106"/>
+      <c r="ET2" s="106"/>
+      <c r="EU2" s="106"/>
+      <c r="EV2" s="106"/>
+      <c r="EW2" s="106"/>
+      <c r="EX2" s="106"/>
+      <c r="EY2" s="106"/>
+      <c r="EZ2" s="106"/>
+      <c r="FA2" s="106"/>
+      <c r="FB2" s="106"/>
+      <c r="FC2" s="106"/>
+      <c r="FD2" s="106"/>
+      <c r="FE2" s="106"/>
+      <c r="FF2" s="106"/>
+      <c r="FG2" s="106"/>
+      <c r="FH2" s="106"/>
+      <c r="FI2" s="106"/>
+      <c r="FJ2" s="106"/>
+      <c r="FK2" s="106"/>
+      <c r="FL2" s="106"/>
+      <c r="FM2" s="106"/>
+      <c r="FN2" s="106"/>
+      <c r="FO2" s="106"/>
+      <c r="FP2" s="106"/>
+      <c r="FQ2" s="106"/>
+      <c r="FR2" s="106"/>
+      <c r="FS2" s="106"/>
+      <c r="FT2" s="106"/>
+      <c r="FU2" s="106"/>
+      <c r="FV2" s="106"/>
+      <c r="FW2" s="106"/>
+      <c r="FX2" s="106"/>
+      <c r="FY2" s="106"/>
+      <c r="FZ2" s="106"/>
+      <c r="GA2" s="106"/>
+      <c r="GB2" s="106"/>
+      <c r="GC2" s="106"/>
+      <c r="GD2" s="106"/>
+      <c r="GE2" s="106"/>
+      <c r="GF2" s="106"/>
+      <c r="GG2" s="106"/>
+      <c r="GH2" s="106"/>
+      <c r="GI2" s="106"/>
+      <c r="GJ2" s="106"/>
+      <c r="GK2" s="106"/>
+      <c r="GL2" s="106"/>
+      <c r="GM2" s="106"/>
+      <c r="GN2" s="106"/>
+      <c r="GO2" s="106"/>
+      <c r="GP2" s="106"/>
+      <c r="GQ2" s="106"/>
+      <c r="GR2" s="106"/>
+      <c r="GS2" s="106"/>
+      <c r="GT2" s="106"/>
+      <c r="GU2" s="106"/>
+      <c r="GV2" s="106"/>
+      <c r="GW2" s="106"/>
+      <c r="GX2" s="106"/>
+      <c r="GY2" s="106"/>
+      <c r="GZ2" s="106"/>
+      <c r="HA2" s="106"/>
+      <c r="HB2" s="106"/>
+      <c r="HC2" s="106"/>
+      <c r="HD2" s="106"/>
+      <c r="HE2" s="106"/>
+      <c r="HF2" s="106"/>
+      <c r="HG2" s="106"/>
+      <c r="HH2" s="106"/>
+      <c r="HI2" s="106"/>
+      <c r="HJ2" s="106"/>
+      <c r="HK2" s="106"/>
+      <c r="HL2" s="106"/>
+      <c r="HM2" s="106"/>
+      <c r="HN2" s="106"/>
+      <c r="HO2" s="106"/>
+      <c r="HP2" s="106"/>
+      <c r="HQ2" s="106"/>
+      <c r="HR2" s="106"/>
+      <c r="HS2" s="106"/>
+      <c r="HT2" s="106"/>
+      <c r="HU2" s="106"/>
+      <c r="HV2" s="106"/>
+      <c r="HW2" s="106"/>
+      <c r="HX2" s="106"/>
+      <c r="HY2" s="106"/>
+      <c r="HZ2" s="106"/>
+      <c r="IA2" s="106"/>
+      <c r="IB2" s="106"/>
+      <c r="IC2" s="106"/>
+      <c r="ID2" s="106"/>
+      <c r="IE2" s="106"/>
+      <c r="IF2" s="106"/>
+      <c r="IG2" s="106"/>
+      <c r="IH2" s="106"/>
+      <c r="II2" s="106"/>
+      <c r="IJ2" s="106"/>
+      <c r="IK2" s="106"/>
+      <c r="IL2" s="106"/>
+      <c r="IM2" s="106"/>
+      <c r="IN2" s="106"/>
+      <c r="IO2" s="106"/>
+      <c r="IP2" s="106"/>
+      <c r="IQ2" s="106"/>
+      <c r="IR2" s="106"/>
+      <c r="IS2" s="106"/>
+      <c r="IT2" s="106"/>
+      <c r="IU2" s="106"/>
+      <c r="IV2" s="106"/>
+      <c r="IW2" s="106"/>
+    </row>
+    <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="107"/>
       <c r="B3" s="108"/>
       <c r="C3" s="109"/>
@@ -4600,6 +5844,255 @@
         <v>37</v>
       </c>
       <c r="H3" s="108"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
+      <c r="L3" s="112"/>
+      <c r="M3" s="112"/>
+      <c r="N3" s="112"/>
+      <c r="O3" s="112"/>
+      <c r="P3" s="112"/>
+      <c r="Q3" s="112"/>
+      <c r="R3" s="112"/>
+      <c r="S3" s="112"/>
+      <c r="T3" s="112"/>
+      <c r="U3" s="112"/>
+      <c r="V3" s="112"/>
+      <c r="W3" s="112"/>
+      <c r="X3" s="112"/>
+      <c r="Y3" s="112"/>
+      <c r="Z3" s="112"/>
+      <c r="AA3" s="112"/>
+      <c r="AB3" s="112"/>
+      <c r="AC3" s="112"/>
+      <c r="AD3" s="112"/>
+      <c r="AE3" s="112"/>
+      <c r="AF3" s="112"/>
+      <c r="AG3" s="112"/>
+      <c r="AH3" s="112"/>
+      <c r="AI3" s="112"/>
+      <c r="AJ3" s="112"/>
+      <c r="AK3" s="112"/>
+      <c r="AL3" s="112"/>
+      <c r="AM3" s="112"/>
+      <c r="AN3" s="112"/>
+      <c r="AO3" s="112"/>
+      <c r="AP3" s="112"/>
+      <c r="AQ3" s="112"/>
+      <c r="AR3" s="112"/>
+      <c r="AS3" s="112"/>
+      <c r="AT3" s="112"/>
+      <c r="AU3" s="112"/>
+      <c r="AV3" s="112"/>
+      <c r="AW3" s="112"/>
+      <c r="AX3" s="112"/>
+      <c r="AY3" s="112"/>
+      <c r="AZ3" s="112"/>
+      <c r="BA3" s="112"/>
+      <c r="BB3" s="112"/>
+      <c r="BC3" s="112"/>
+      <c r="BD3" s="112"/>
+      <c r="BE3" s="112"/>
+      <c r="BF3" s="112"/>
+      <c r="BG3" s="112"/>
+      <c r="BH3" s="112"/>
+      <c r="BI3" s="112"/>
+      <c r="BJ3" s="112"/>
+      <c r="BK3" s="112"/>
+      <c r="BL3" s="112"/>
+      <c r="BM3" s="112"/>
+      <c r="BN3" s="112"/>
+      <c r="BO3" s="112"/>
+      <c r="BP3" s="112"/>
+      <c r="BQ3" s="112"/>
+      <c r="BR3" s="112"/>
+      <c r="BS3" s="112"/>
+      <c r="BT3" s="112"/>
+      <c r="BU3" s="112"/>
+      <c r="BV3" s="112"/>
+      <c r="BW3" s="112"/>
+      <c r="BX3" s="112"/>
+      <c r="BY3" s="112"/>
+      <c r="BZ3" s="112"/>
+      <c r="CA3" s="112"/>
+      <c r="CB3" s="112"/>
+      <c r="CC3" s="112"/>
+      <c r="CD3" s="112"/>
+      <c r="CE3" s="112"/>
+      <c r="CF3" s="112"/>
+      <c r="CG3" s="112"/>
+      <c r="CH3" s="112"/>
+      <c r="CI3" s="112"/>
+      <c r="CJ3" s="112"/>
+      <c r="CK3" s="112"/>
+      <c r="CL3" s="112"/>
+      <c r="CM3" s="112"/>
+      <c r="CN3" s="112"/>
+      <c r="CO3" s="112"/>
+      <c r="CP3" s="112"/>
+      <c r="CQ3" s="112"/>
+      <c r="CR3" s="112"/>
+      <c r="CS3" s="112"/>
+      <c r="CT3" s="112"/>
+      <c r="CU3" s="112"/>
+      <c r="CV3" s="112"/>
+      <c r="CW3" s="112"/>
+      <c r="CX3" s="112"/>
+      <c r="CY3" s="112"/>
+      <c r="CZ3" s="112"/>
+      <c r="DA3" s="112"/>
+      <c r="DB3" s="112"/>
+      <c r="DC3" s="112"/>
+      <c r="DD3" s="112"/>
+      <c r="DE3" s="112"/>
+      <c r="DF3" s="112"/>
+      <c r="DG3" s="112"/>
+      <c r="DH3" s="112"/>
+      <c r="DI3" s="112"/>
+      <c r="DJ3" s="112"/>
+      <c r="DK3" s="112"/>
+      <c r="DL3" s="112"/>
+      <c r="DM3" s="112"/>
+      <c r="DN3" s="112"/>
+      <c r="DO3" s="112"/>
+      <c r="DP3" s="112"/>
+      <c r="DQ3" s="112"/>
+      <c r="DR3" s="112"/>
+      <c r="DS3" s="112"/>
+      <c r="DT3" s="112"/>
+      <c r="DU3" s="112"/>
+      <c r="DV3" s="112"/>
+      <c r="DW3" s="112"/>
+      <c r="DX3" s="112"/>
+      <c r="DY3" s="112"/>
+      <c r="DZ3" s="112"/>
+      <c r="EA3" s="112"/>
+      <c r="EB3" s="112"/>
+      <c r="EC3" s="112"/>
+      <c r="ED3" s="112"/>
+      <c r="EE3" s="112"/>
+      <c r="EF3" s="112"/>
+      <c r="EG3" s="112"/>
+      <c r="EH3" s="112"/>
+      <c r="EI3" s="112"/>
+      <c r="EJ3" s="112"/>
+      <c r="EK3" s="112"/>
+      <c r="EL3" s="112"/>
+      <c r="EM3" s="112"/>
+      <c r="EN3" s="112"/>
+      <c r="EO3" s="112"/>
+      <c r="EP3" s="112"/>
+      <c r="EQ3" s="112"/>
+      <c r="ER3" s="112"/>
+      <c r="ES3" s="112"/>
+      <c r="ET3" s="112"/>
+      <c r="EU3" s="112"/>
+      <c r="EV3" s="112"/>
+      <c r="EW3" s="112"/>
+      <c r="EX3" s="112"/>
+      <c r="EY3" s="112"/>
+      <c r="EZ3" s="112"/>
+      <c r="FA3" s="112"/>
+      <c r="FB3" s="112"/>
+      <c r="FC3" s="112"/>
+      <c r="FD3" s="112"/>
+      <c r="FE3" s="112"/>
+      <c r="FF3" s="112"/>
+      <c r="FG3" s="112"/>
+      <c r="FH3" s="112"/>
+      <c r="FI3" s="112"/>
+      <c r="FJ3" s="112"/>
+      <c r="FK3" s="112"/>
+      <c r="FL3" s="112"/>
+      <c r="FM3" s="112"/>
+      <c r="FN3" s="112"/>
+      <c r="FO3" s="112"/>
+      <c r="FP3" s="112"/>
+      <c r="FQ3" s="112"/>
+      <c r="FR3" s="112"/>
+      <c r="FS3" s="112"/>
+      <c r="FT3" s="112"/>
+      <c r="FU3" s="112"/>
+      <c r="FV3" s="112"/>
+      <c r="FW3" s="112"/>
+      <c r="FX3" s="112"/>
+      <c r="FY3" s="112"/>
+      <c r="FZ3" s="112"/>
+      <c r="GA3" s="112"/>
+      <c r="GB3" s="112"/>
+      <c r="GC3" s="112"/>
+      <c r="GD3" s="112"/>
+      <c r="GE3" s="112"/>
+      <c r="GF3" s="112"/>
+      <c r="GG3" s="112"/>
+      <c r="GH3" s="112"/>
+      <c r="GI3" s="112"/>
+      <c r="GJ3" s="112"/>
+      <c r="GK3" s="112"/>
+      <c r="GL3" s="112"/>
+      <c r="GM3" s="112"/>
+      <c r="GN3" s="112"/>
+      <c r="GO3" s="112"/>
+      <c r="GP3" s="112"/>
+      <c r="GQ3" s="112"/>
+      <c r="GR3" s="112"/>
+      <c r="GS3" s="112"/>
+      <c r="GT3" s="112"/>
+      <c r="GU3" s="112"/>
+      <c r="GV3" s="112"/>
+      <c r="GW3" s="112"/>
+      <c r="GX3" s="112"/>
+      <c r="GY3" s="112"/>
+      <c r="GZ3" s="112"/>
+      <c r="HA3" s="112"/>
+      <c r="HB3" s="112"/>
+      <c r="HC3" s="112"/>
+      <c r="HD3" s="112"/>
+      <c r="HE3" s="112"/>
+      <c r="HF3" s="112"/>
+      <c r="HG3" s="112"/>
+      <c r="HH3" s="112"/>
+      <c r="HI3" s="112"/>
+      <c r="HJ3" s="112"/>
+      <c r="HK3" s="112"/>
+      <c r="HL3" s="112"/>
+      <c r="HM3" s="112"/>
+      <c r="HN3" s="112"/>
+      <c r="HO3" s="112"/>
+      <c r="HP3" s="112"/>
+      <c r="HQ3" s="112"/>
+      <c r="HR3" s="112"/>
+      <c r="HS3" s="112"/>
+      <c r="HT3" s="112"/>
+      <c r="HU3" s="112"/>
+      <c r="HV3" s="112"/>
+      <c r="HW3" s="112"/>
+      <c r="HX3" s="112"/>
+      <c r="HY3" s="112"/>
+      <c r="HZ3" s="112"/>
+      <c r="IA3" s="112"/>
+      <c r="IB3" s="112"/>
+      <c r="IC3" s="112"/>
+      <c r="ID3" s="112"/>
+      <c r="IE3" s="112"/>
+      <c r="IF3" s="112"/>
+      <c r="IG3" s="112"/>
+      <c r="IH3" s="112"/>
+      <c r="II3" s="112"/>
+      <c r="IJ3" s="112"/>
+      <c r="IK3" s="112"/>
+      <c r="IL3" s="112"/>
+      <c r="IM3" s="112"/>
+      <c r="IN3" s="112"/>
+      <c r="IO3" s="112"/>
+      <c r="IP3" s="112"/>
+      <c r="IQ3" s="112"/>
+      <c r="IR3" s="112"/>
+      <c r="IS3" s="112"/>
+      <c r="IT3" s="112"/>
+      <c r="IU3" s="112"/>
+      <c r="IV3" s="112"/>
+      <c r="IW3" s="112"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="107"/>
@@ -6624,8 +8117,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW201"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="118" width="8.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="119" width="19.66"/>
@@ -6638,7 +8131,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="9" style="119" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="103" t="s">
         <v>29</v>
       </c>
@@ -6660,8 +8153,257 @@
         <f aca="false">SUM(H5:H200)</f>
         <v>600</v>
       </c>
-    </row>
-    <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="102"/>
+      <c r="AG1" s="102"/>
+      <c r="AH1" s="102"/>
+      <c r="AI1" s="102"/>
+      <c r="AJ1" s="102"/>
+      <c r="AK1" s="102"/>
+      <c r="AL1" s="102"/>
+      <c r="AM1" s="102"/>
+      <c r="AN1" s="102"/>
+      <c r="AO1" s="102"/>
+      <c r="AP1" s="102"/>
+      <c r="AQ1" s="102"/>
+      <c r="AR1" s="102"/>
+      <c r="AS1" s="102"/>
+      <c r="AT1" s="102"/>
+      <c r="AU1" s="102"/>
+      <c r="AV1" s="102"/>
+      <c r="AW1" s="102"/>
+      <c r="AX1" s="102"/>
+      <c r="AY1" s="102"/>
+      <c r="AZ1" s="102"/>
+      <c r="BA1" s="102"/>
+      <c r="BB1" s="102"/>
+      <c r="BC1" s="102"/>
+      <c r="BD1" s="102"/>
+      <c r="BE1" s="102"/>
+      <c r="BF1" s="102"/>
+      <c r="BG1" s="102"/>
+      <c r="BH1" s="102"/>
+      <c r="BI1" s="102"/>
+      <c r="BJ1" s="102"/>
+      <c r="BK1" s="102"/>
+      <c r="BL1" s="102"/>
+      <c r="BM1" s="102"/>
+      <c r="BN1" s="102"/>
+      <c r="BO1" s="102"/>
+      <c r="BP1" s="102"/>
+      <c r="BQ1" s="102"/>
+      <c r="BR1" s="102"/>
+      <c r="BS1" s="102"/>
+      <c r="BT1" s="102"/>
+      <c r="BU1" s="102"/>
+      <c r="BV1" s="102"/>
+      <c r="BW1" s="102"/>
+      <c r="BX1" s="102"/>
+      <c r="BY1" s="102"/>
+      <c r="BZ1" s="102"/>
+      <c r="CA1" s="102"/>
+      <c r="CB1" s="102"/>
+      <c r="CC1" s="102"/>
+      <c r="CD1" s="102"/>
+      <c r="CE1" s="102"/>
+      <c r="CF1" s="102"/>
+      <c r="CG1" s="102"/>
+      <c r="CH1" s="102"/>
+      <c r="CI1" s="102"/>
+      <c r="CJ1" s="102"/>
+      <c r="CK1" s="102"/>
+      <c r="CL1" s="102"/>
+      <c r="CM1" s="102"/>
+      <c r="CN1" s="102"/>
+      <c r="CO1" s="102"/>
+      <c r="CP1" s="102"/>
+      <c r="CQ1" s="102"/>
+      <c r="CR1" s="102"/>
+      <c r="CS1" s="102"/>
+      <c r="CT1" s="102"/>
+      <c r="CU1" s="102"/>
+      <c r="CV1" s="102"/>
+      <c r="CW1" s="102"/>
+      <c r="CX1" s="102"/>
+      <c r="CY1" s="102"/>
+      <c r="CZ1" s="102"/>
+      <c r="DA1" s="102"/>
+      <c r="DB1" s="102"/>
+      <c r="DC1" s="102"/>
+      <c r="DD1" s="102"/>
+      <c r="DE1" s="102"/>
+      <c r="DF1" s="102"/>
+      <c r="DG1" s="102"/>
+      <c r="DH1" s="102"/>
+      <c r="DI1" s="102"/>
+      <c r="DJ1" s="102"/>
+      <c r="DK1" s="102"/>
+      <c r="DL1" s="102"/>
+      <c r="DM1" s="102"/>
+      <c r="DN1" s="102"/>
+      <c r="DO1" s="102"/>
+      <c r="DP1" s="102"/>
+      <c r="DQ1" s="102"/>
+      <c r="DR1" s="102"/>
+      <c r="DS1" s="102"/>
+      <c r="DT1" s="102"/>
+      <c r="DU1" s="102"/>
+      <c r="DV1" s="102"/>
+      <c r="DW1" s="102"/>
+      <c r="DX1" s="102"/>
+      <c r="DY1" s="102"/>
+      <c r="DZ1" s="102"/>
+      <c r="EA1" s="102"/>
+      <c r="EB1" s="102"/>
+      <c r="EC1" s="102"/>
+      <c r="ED1" s="102"/>
+      <c r="EE1" s="102"/>
+      <c r="EF1" s="102"/>
+      <c r="EG1" s="102"/>
+      <c r="EH1" s="102"/>
+      <c r="EI1" s="102"/>
+      <c r="EJ1" s="102"/>
+      <c r="EK1" s="102"/>
+      <c r="EL1" s="102"/>
+      <c r="EM1" s="102"/>
+      <c r="EN1" s="102"/>
+      <c r="EO1" s="102"/>
+      <c r="EP1" s="102"/>
+      <c r="EQ1" s="102"/>
+      <c r="ER1" s="102"/>
+      <c r="ES1" s="102"/>
+      <c r="ET1" s="102"/>
+      <c r="EU1" s="102"/>
+      <c r="EV1" s="102"/>
+      <c r="EW1" s="102"/>
+      <c r="EX1" s="102"/>
+      <c r="EY1" s="102"/>
+      <c r="EZ1" s="102"/>
+      <c r="FA1" s="102"/>
+      <c r="FB1" s="102"/>
+      <c r="FC1" s="102"/>
+      <c r="FD1" s="102"/>
+      <c r="FE1" s="102"/>
+      <c r="FF1" s="102"/>
+      <c r="FG1" s="102"/>
+      <c r="FH1" s="102"/>
+      <c r="FI1" s="102"/>
+      <c r="FJ1" s="102"/>
+      <c r="FK1" s="102"/>
+      <c r="FL1" s="102"/>
+      <c r="FM1" s="102"/>
+      <c r="FN1" s="102"/>
+      <c r="FO1" s="102"/>
+      <c r="FP1" s="102"/>
+      <c r="FQ1" s="102"/>
+      <c r="FR1" s="102"/>
+      <c r="FS1" s="102"/>
+      <c r="FT1" s="102"/>
+      <c r="FU1" s="102"/>
+      <c r="FV1" s="102"/>
+      <c r="FW1" s="102"/>
+      <c r="FX1" s="102"/>
+      <c r="FY1" s="102"/>
+      <c r="FZ1" s="102"/>
+      <c r="GA1" s="102"/>
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="102"/>
+      <c r="HF1" s="102"/>
+      <c r="HG1" s="102"/>
+      <c r="HH1" s="102"/>
+      <c r="HI1" s="102"/>
+      <c r="HJ1" s="102"/>
+      <c r="HK1" s="102"/>
+      <c r="HL1" s="102"/>
+      <c r="HM1" s="102"/>
+      <c r="HN1" s="102"/>
+      <c r="HO1" s="102"/>
+      <c r="HP1" s="102"/>
+      <c r="HQ1" s="102"/>
+      <c r="HR1" s="102"/>
+      <c r="HS1" s="102"/>
+      <c r="HT1" s="102"/>
+      <c r="HU1" s="102"/>
+      <c r="HV1" s="102"/>
+      <c r="HW1" s="102"/>
+      <c r="HX1" s="102"/>
+      <c r="HY1" s="102"/>
+      <c r="HZ1" s="102"/>
+      <c r="IA1" s="102"/>
+      <c r="IB1" s="102"/>
+      <c r="IC1" s="102"/>
+      <c r="ID1" s="102"/>
+      <c r="IE1" s="102"/>
+      <c r="IF1" s="102"/>
+      <c r="IG1" s="102"/>
+      <c r="IH1" s="102"/>
+      <c r="II1" s="102"/>
+      <c r="IJ1" s="102"/>
+      <c r="IK1" s="102"/>
+      <c r="IL1" s="102"/>
+      <c r="IM1" s="102"/>
+      <c r="IN1" s="102"/>
+      <c r="IO1" s="102"/>
+      <c r="IP1" s="102"/>
+      <c r="IQ1" s="102"/>
+      <c r="IR1" s="102"/>
+      <c r="IS1" s="102"/>
+      <c r="IT1" s="102"/>
+      <c r="IU1" s="102"/>
+      <c r="IV1" s="102"/>
+      <c r="IW1" s="102"/>
+    </row>
+    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
         <v>47</v>
       </c>
@@ -6686,8 +8428,257 @@
       <c r="H2" s="108" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
+      <c r="U2" s="127"/>
+      <c r="V2" s="127"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="127"/>
+      <c r="Y2" s="127"/>
+      <c r="Z2" s="127"/>
+      <c r="AA2" s="127"/>
+      <c r="AB2" s="127"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="127"/>
+      <c r="AE2" s="127"/>
+      <c r="AF2" s="127"/>
+      <c r="AG2" s="127"/>
+      <c r="AH2" s="127"/>
+      <c r="AI2" s="127"/>
+      <c r="AJ2" s="127"/>
+      <c r="AK2" s="127"/>
+      <c r="AL2" s="127"/>
+      <c r="AM2" s="127"/>
+      <c r="AN2" s="127"/>
+      <c r="AO2" s="127"/>
+      <c r="AP2" s="127"/>
+      <c r="AQ2" s="127"/>
+      <c r="AR2" s="127"/>
+      <c r="AS2" s="127"/>
+      <c r="AT2" s="127"/>
+      <c r="AU2" s="127"/>
+      <c r="AV2" s="127"/>
+      <c r="AW2" s="127"/>
+      <c r="AX2" s="127"/>
+      <c r="AY2" s="127"/>
+      <c r="AZ2" s="127"/>
+      <c r="BA2" s="127"/>
+      <c r="BB2" s="127"/>
+      <c r="BC2" s="127"/>
+      <c r="BD2" s="127"/>
+      <c r="BE2" s="127"/>
+      <c r="BF2" s="127"/>
+      <c r="BG2" s="127"/>
+      <c r="BH2" s="127"/>
+      <c r="BI2" s="127"/>
+      <c r="BJ2" s="127"/>
+      <c r="BK2" s="127"/>
+      <c r="BL2" s="127"/>
+      <c r="BM2" s="127"/>
+      <c r="BN2" s="127"/>
+      <c r="BO2" s="127"/>
+      <c r="BP2" s="127"/>
+      <c r="BQ2" s="127"/>
+      <c r="BR2" s="127"/>
+      <c r="BS2" s="127"/>
+      <c r="BT2" s="127"/>
+      <c r="BU2" s="127"/>
+      <c r="BV2" s="127"/>
+      <c r="BW2" s="127"/>
+      <c r="BX2" s="127"/>
+      <c r="BY2" s="127"/>
+      <c r="BZ2" s="127"/>
+      <c r="CA2" s="127"/>
+      <c r="CB2" s="127"/>
+      <c r="CC2" s="127"/>
+      <c r="CD2" s="127"/>
+      <c r="CE2" s="127"/>
+      <c r="CF2" s="127"/>
+      <c r="CG2" s="127"/>
+      <c r="CH2" s="127"/>
+      <c r="CI2" s="127"/>
+      <c r="CJ2" s="127"/>
+      <c r="CK2" s="127"/>
+      <c r="CL2" s="127"/>
+      <c r="CM2" s="127"/>
+      <c r="CN2" s="127"/>
+      <c r="CO2" s="127"/>
+      <c r="CP2" s="127"/>
+      <c r="CQ2" s="127"/>
+      <c r="CR2" s="127"/>
+      <c r="CS2" s="127"/>
+      <c r="CT2" s="127"/>
+      <c r="CU2" s="127"/>
+      <c r="CV2" s="127"/>
+      <c r="CW2" s="127"/>
+      <c r="CX2" s="127"/>
+      <c r="CY2" s="127"/>
+      <c r="CZ2" s="127"/>
+      <c r="DA2" s="127"/>
+      <c r="DB2" s="127"/>
+      <c r="DC2" s="127"/>
+      <c r="DD2" s="127"/>
+      <c r="DE2" s="127"/>
+      <c r="DF2" s="127"/>
+      <c r="DG2" s="127"/>
+      <c r="DH2" s="127"/>
+      <c r="DI2" s="127"/>
+      <c r="DJ2" s="127"/>
+      <c r="DK2" s="127"/>
+      <c r="DL2" s="127"/>
+      <c r="DM2" s="127"/>
+      <c r="DN2" s="127"/>
+      <c r="DO2" s="127"/>
+      <c r="DP2" s="127"/>
+      <c r="DQ2" s="127"/>
+      <c r="DR2" s="127"/>
+      <c r="DS2" s="127"/>
+      <c r="DT2" s="127"/>
+      <c r="DU2" s="127"/>
+      <c r="DV2" s="127"/>
+      <c r="DW2" s="127"/>
+      <c r="DX2" s="127"/>
+      <c r="DY2" s="127"/>
+      <c r="DZ2" s="127"/>
+      <c r="EA2" s="127"/>
+      <c r="EB2" s="127"/>
+      <c r="EC2" s="127"/>
+      <c r="ED2" s="127"/>
+      <c r="EE2" s="127"/>
+      <c r="EF2" s="127"/>
+      <c r="EG2" s="127"/>
+      <c r="EH2" s="127"/>
+      <c r="EI2" s="127"/>
+      <c r="EJ2" s="127"/>
+      <c r="EK2" s="127"/>
+      <c r="EL2" s="127"/>
+      <c r="EM2" s="127"/>
+      <c r="EN2" s="127"/>
+      <c r="EO2" s="127"/>
+      <c r="EP2" s="127"/>
+      <c r="EQ2" s="127"/>
+      <c r="ER2" s="127"/>
+      <c r="ES2" s="127"/>
+      <c r="ET2" s="127"/>
+      <c r="EU2" s="127"/>
+      <c r="EV2" s="127"/>
+      <c r="EW2" s="127"/>
+      <c r="EX2" s="127"/>
+      <c r="EY2" s="127"/>
+      <c r="EZ2" s="127"/>
+      <c r="FA2" s="127"/>
+      <c r="FB2" s="127"/>
+      <c r="FC2" s="127"/>
+      <c r="FD2" s="127"/>
+      <c r="FE2" s="127"/>
+      <c r="FF2" s="127"/>
+      <c r="FG2" s="127"/>
+      <c r="FH2" s="127"/>
+      <c r="FI2" s="127"/>
+      <c r="FJ2" s="127"/>
+      <c r="FK2" s="127"/>
+      <c r="FL2" s="127"/>
+      <c r="FM2" s="127"/>
+      <c r="FN2" s="127"/>
+      <c r="FO2" s="127"/>
+      <c r="FP2" s="127"/>
+      <c r="FQ2" s="127"/>
+      <c r="FR2" s="127"/>
+      <c r="FS2" s="127"/>
+      <c r="FT2" s="127"/>
+      <c r="FU2" s="127"/>
+      <c r="FV2" s="127"/>
+      <c r="FW2" s="127"/>
+      <c r="FX2" s="127"/>
+      <c r="FY2" s="127"/>
+      <c r="FZ2" s="127"/>
+      <c r="GA2" s="127"/>
+      <c r="GB2" s="127"/>
+      <c r="GC2" s="127"/>
+      <c r="GD2" s="127"/>
+      <c r="GE2" s="127"/>
+      <c r="GF2" s="127"/>
+      <c r="GG2" s="127"/>
+      <c r="GH2" s="127"/>
+      <c r="GI2" s="127"/>
+      <c r="GJ2" s="127"/>
+      <c r="GK2" s="127"/>
+      <c r="GL2" s="127"/>
+      <c r="GM2" s="127"/>
+      <c r="GN2" s="127"/>
+      <c r="GO2" s="127"/>
+      <c r="GP2" s="127"/>
+      <c r="GQ2" s="127"/>
+      <c r="GR2" s="127"/>
+      <c r="GS2" s="127"/>
+      <c r="GT2" s="127"/>
+      <c r="GU2" s="127"/>
+      <c r="GV2" s="127"/>
+      <c r="GW2" s="127"/>
+      <c r="GX2" s="127"/>
+      <c r="GY2" s="127"/>
+      <c r="GZ2" s="127"/>
+      <c r="HA2" s="127"/>
+      <c r="HB2" s="127"/>
+      <c r="HC2" s="127"/>
+      <c r="HD2" s="127"/>
+      <c r="HE2" s="127"/>
+      <c r="HF2" s="127"/>
+      <c r="HG2" s="127"/>
+      <c r="HH2" s="127"/>
+      <c r="HI2" s="127"/>
+      <c r="HJ2" s="127"/>
+      <c r="HK2" s="127"/>
+      <c r="HL2" s="127"/>
+      <c r="HM2" s="127"/>
+      <c r="HN2" s="127"/>
+      <c r="HO2" s="127"/>
+      <c r="HP2" s="127"/>
+      <c r="HQ2" s="127"/>
+      <c r="HR2" s="127"/>
+      <c r="HS2" s="127"/>
+      <c r="HT2" s="127"/>
+      <c r="HU2" s="127"/>
+      <c r="HV2" s="127"/>
+      <c r="HW2" s="127"/>
+      <c r="HX2" s="127"/>
+      <c r="HY2" s="127"/>
+      <c r="HZ2" s="127"/>
+      <c r="IA2" s="127"/>
+      <c r="IB2" s="127"/>
+      <c r="IC2" s="127"/>
+      <c r="ID2" s="127"/>
+      <c r="IE2" s="127"/>
+      <c r="IF2" s="127"/>
+      <c r="IG2" s="127"/>
+      <c r="IH2" s="127"/>
+      <c r="II2" s="127"/>
+      <c r="IJ2" s="127"/>
+      <c r="IK2" s="127"/>
+      <c r="IL2" s="127"/>
+      <c r="IM2" s="127"/>
+      <c r="IN2" s="127"/>
+      <c r="IO2" s="127"/>
+      <c r="IP2" s="127"/>
+      <c r="IQ2" s="127"/>
+      <c r="IR2" s="127"/>
+      <c r="IS2" s="127"/>
+      <c r="IT2" s="127"/>
+      <c r="IU2" s="127"/>
+      <c r="IV2" s="127"/>
+      <c r="IW2" s="127"/>
+    </row>
+    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="107"/>
       <c r="B3" s="107"/>
       <c r="C3" s="107"/>
@@ -6698,6 +8689,255 @@
         <v>52</v>
       </c>
       <c r="H3" s="108"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="128"/>
+      <c r="S3" s="128"/>
+      <c r="T3" s="128"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="128"/>
+      <c r="AB3" s="128"/>
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="128"/>
+      <c r="AF3" s="128"/>
+      <c r="AG3" s="128"/>
+      <c r="AH3" s="128"/>
+      <c r="AI3" s="128"/>
+      <c r="AJ3" s="128"/>
+      <c r="AK3" s="128"/>
+      <c r="AL3" s="128"/>
+      <c r="AM3" s="128"/>
+      <c r="AN3" s="128"/>
+      <c r="AO3" s="128"/>
+      <c r="AP3" s="128"/>
+      <c r="AQ3" s="128"/>
+      <c r="AR3" s="128"/>
+      <c r="AS3" s="128"/>
+      <c r="AT3" s="128"/>
+      <c r="AU3" s="128"/>
+      <c r="AV3" s="128"/>
+      <c r="AW3" s="128"/>
+      <c r="AX3" s="128"/>
+      <c r="AY3" s="128"/>
+      <c r="AZ3" s="128"/>
+      <c r="BA3" s="128"/>
+      <c r="BB3" s="128"/>
+      <c r="BC3" s="128"/>
+      <c r="BD3" s="128"/>
+      <c r="BE3" s="128"/>
+      <c r="BF3" s="128"/>
+      <c r="BG3" s="128"/>
+      <c r="BH3" s="128"/>
+      <c r="BI3" s="128"/>
+      <c r="BJ3" s="128"/>
+      <c r="BK3" s="128"/>
+      <c r="BL3" s="128"/>
+      <c r="BM3" s="128"/>
+      <c r="BN3" s="128"/>
+      <c r="BO3" s="128"/>
+      <c r="BP3" s="128"/>
+      <c r="BQ3" s="128"/>
+      <c r="BR3" s="128"/>
+      <c r="BS3" s="128"/>
+      <c r="BT3" s="128"/>
+      <c r="BU3" s="128"/>
+      <c r="BV3" s="128"/>
+      <c r="BW3" s="128"/>
+      <c r="BX3" s="128"/>
+      <c r="BY3" s="128"/>
+      <c r="BZ3" s="128"/>
+      <c r="CA3" s="128"/>
+      <c r="CB3" s="128"/>
+      <c r="CC3" s="128"/>
+      <c r="CD3" s="128"/>
+      <c r="CE3" s="128"/>
+      <c r="CF3" s="128"/>
+      <c r="CG3" s="128"/>
+      <c r="CH3" s="128"/>
+      <c r="CI3" s="128"/>
+      <c r="CJ3" s="128"/>
+      <c r="CK3" s="128"/>
+      <c r="CL3" s="128"/>
+      <c r="CM3" s="128"/>
+      <c r="CN3" s="128"/>
+      <c r="CO3" s="128"/>
+      <c r="CP3" s="128"/>
+      <c r="CQ3" s="128"/>
+      <c r="CR3" s="128"/>
+      <c r="CS3" s="128"/>
+      <c r="CT3" s="128"/>
+      <c r="CU3" s="128"/>
+      <c r="CV3" s="128"/>
+      <c r="CW3" s="128"/>
+      <c r="CX3" s="128"/>
+      <c r="CY3" s="128"/>
+      <c r="CZ3" s="128"/>
+      <c r="DA3" s="128"/>
+      <c r="DB3" s="128"/>
+      <c r="DC3" s="128"/>
+      <c r="DD3" s="128"/>
+      <c r="DE3" s="128"/>
+      <c r="DF3" s="128"/>
+      <c r="DG3" s="128"/>
+      <c r="DH3" s="128"/>
+      <c r="DI3" s="128"/>
+      <c r="DJ3" s="128"/>
+      <c r="DK3" s="128"/>
+      <c r="DL3" s="128"/>
+      <c r="DM3" s="128"/>
+      <c r="DN3" s="128"/>
+      <c r="DO3" s="128"/>
+      <c r="DP3" s="128"/>
+      <c r="DQ3" s="128"/>
+      <c r="DR3" s="128"/>
+      <c r="DS3" s="128"/>
+      <c r="DT3" s="128"/>
+      <c r="DU3" s="128"/>
+      <c r="DV3" s="128"/>
+      <c r="DW3" s="128"/>
+      <c r="DX3" s="128"/>
+      <c r="DY3" s="128"/>
+      <c r="DZ3" s="128"/>
+      <c r="EA3" s="128"/>
+      <c r="EB3" s="128"/>
+      <c r="EC3" s="128"/>
+      <c r="ED3" s="128"/>
+      <c r="EE3" s="128"/>
+      <c r="EF3" s="128"/>
+      <c r="EG3" s="128"/>
+      <c r="EH3" s="128"/>
+      <c r="EI3" s="128"/>
+      <c r="EJ3" s="128"/>
+      <c r="EK3" s="128"/>
+      <c r="EL3" s="128"/>
+      <c r="EM3" s="128"/>
+      <c r="EN3" s="128"/>
+      <c r="EO3" s="128"/>
+      <c r="EP3" s="128"/>
+      <c r="EQ3" s="128"/>
+      <c r="ER3" s="128"/>
+      <c r="ES3" s="128"/>
+      <c r="ET3" s="128"/>
+      <c r="EU3" s="128"/>
+      <c r="EV3" s="128"/>
+      <c r="EW3" s="128"/>
+      <c r="EX3" s="128"/>
+      <c r="EY3" s="128"/>
+      <c r="EZ3" s="128"/>
+      <c r="FA3" s="128"/>
+      <c r="FB3" s="128"/>
+      <c r="FC3" s="128"/>
+      <c r="FD3" s="128"/>
+      <c r="FE3" s="128"/>
+      <c r="FF3" s="128"/>
+      <c r="FG3" s="128"/>
+      <c r="FH3" s="128"/>
+      <c r="FI3" s="128"/>
+      <c r="FJ3" s="128"/>
+      <c r="FK3" s="128"/>
+      <c r="FL3" s="128"/>
+      <c r="FM3" s="128"/>
+      <c r="FN3" s="128"/>
+      <c r="FO3" s="128"/>
+      <c r="FP3" s="128"/>
+      <c r="FQ3" s="128"/>
+      <c r="FR3" s="128"/>
+      <c r="FS3" s="128"/>
+      <c r="FT3" s="128"/>
+      <c r="FU3" s="128"/>
+      <c r="FV3" s="128"/>
+      <c r="FW3" s="128"/>
+      <c r="FX3" s="128"/>
+      <c r="FY3" s="128"/>
+      <c r="FZ3" s="128"/>
+      <c r="GA3" s="128"/>
+      <c r="GB3" s="128"/>
+      <c r="GC3" s="128"/>
+      <c r="GD3" s="128"/>
+      <c r="GE3" s="128"/>
+      <c r="GF3" s="128"/>
+      <c r="GG3" s="128"/>
+      <c r="GH3" s="128"/>
+      <c r="GI3" s="128"/>
+      <c r="GJ3" s="128"/>
+      <c r="GK3" s="128"/>
+      <c r="GL3" s="128"/>
+      <c r="GM3" s="128"/>
+      <c r="GN3" s="128"/>
+      <c r="GO3" s="128"/>
+      <c r="GP3" s="128"/>
+      <c r="GQ3" s="128"/>
+      <c r="GR3" s="128"/>
+      <c r="GS3" s="128"/>
+      <c r="GT3" s="128"/>
+      <c r="GU3" s="128"/>
+      <c r="GV3" s="128"/>
+      <c r="GW3" s="128"/>
+      <c r="GX3" s="128"/>
+      <c r="GY3" s="128"/>
+      <c r="GZ3" s="128"/>
+      <c r="HA3" s="128"/>
+      <c r="HB3" s="128"/>
+      <c r="HC3" s="128"/>
+      <c r="HD3" s="128"/>
+      <c r="HE3" s="128"/>
+      <c r="HF3" s="128"/>
+      <c r="HG3" s="128"/>
+      <c r="HH3" s="128"/>
+      <c r="HI3" s="128"/>
+      <c r="HJ3" s="128"/>
+      <c r="HK3" s="128"/>
+      <c r="HL3" s="128"/>
+      <c r="HM3" s="128"/>
+      <c r="HN3" s="128"/>
+      <c r="HO3" s="128"/>
+      <c r="HP3" s="128"/>
+      <c r="HQ3" s="128"/>
+      <c r="HR3" s="128"/>
+      <c r="HS3" s="128"/>
+      <c r="HT3" s="128"/>
+      <c r="HU3" s="128"/>
+      <c r="HV3" s="128"/>
+      <c r="HW3" s="128"/>
+      <c r="HX3" s="128"/>
+      <c r="HY3" s="128"/>
+      <c r="HZ3" s="128"/>
+      <c r="IA3" s="128"/>
+      <c r="IB3" s="128"/>
+      <c r="IC3" s="128"/>
+      <c r="ID3" s="128"/>
+      <c r="IE3" s="128"/>
+      <c r="IF3" s="128"/>
+      <c r="IG3" s="128"/>
+      <c r="IH3" s="128"/>
+      <c r="II3" s="128"/>
+      <c r="IJ3" s="128"/>
+      <c r="IK3" s="128"/>
+      <c r="IL3" s="128"/>
+      <c r="IM3" s="128"/>
+      <c r="IN3" s="128"/>
+      <c r="IO3" s="128"/>
+      <c r="IP3" s="128"/>
+      <c r="IQ3" s="128"/>
+      <c r="IR3" s="128"/>
+      <c r="IS3" s="128"/>
+      <c r="IT3" s="128"/>
+      <c r="IU3" s="128"/>
+      <c r="IV3" s="128"/>
+      <c r="IW3" s="128"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="107"/>
@@ -6709,7 +8949,7 @@
       <c r="G4" s="108"/>
       <c r="H4" s="108"/>
     </row>
-    <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
         <v>46285</v>
       </c>
@@ -6720,6 +8960,7 @@
         <v>54</v>
       </c>
       <c r="D5" s="122"/>
+      <c r="E5" s="119"/>
       <c r="F5" s="130" t="n">
         <v>720</v>
       </c>
@@ -8917,8 +11158,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW201"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="118" width="8.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="119" width="19.66"/>
@@ -8931,7 +11172,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="9" style="119" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="103" t="s">
         <v>29</v>
       </c>
@@ -8953,8 +11194,257 @@
         <f aca="false">SUM(H5:H200)</f>
         <v>1000</v>
       </c>
-    </row>
-    <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="102"/>
+      <c r="AG1" s="102"/>
+      <c r="AH1" s="102"/>
+      <c r="AI1" s="102"/>
+      <c r="AJ1" s="102"/>
+      <c r="AK1" s="102"/>
+      <c r="AL1" s="102"/>
+      <c r="AM1" s="102"/>
+      <c r="AN1" s="102"/>
+      <c r="AO1" s="102"/>
+      <c r="AP1" s="102"/>
+      <c r="AQ1" s="102"/>
+      <c r="AR1" s="102"/>
+      <c r="AS1" s="102"/>
+      <c r="AT1" s="102"/>
+      <c r="AU1" s="102"/>
+      <c r="AV1" s="102"/>
+      <c r="AW1" s="102"/>
+      <c r="AX1" s="102"/>
+      <c r="AY1" s="102"/>
+      <c r="AZ1" s="102"/>
+      <c r="BA1" s="102"/>
+      <c r="BB1" s="102"/>
+      <c r="BC1" s="102"/>
+      <c r="BD1" s="102"/>
+      <c r="BE1" s="102"/>
+      <c r="BF1" s="102"/>
+      <c r="BG1" s="102"/>
+      <c r="BH1" s="102"/>
+      <c r="BI1" s="102"/>
+      <c r="BJ1" s="102"/>
+      <c r="BK1" s="102"/>
+      <c r="BL1" s="102"/>
+      <c r="BM1" s="102"/>
+      <c r="BN1" s="102"/>
+      <c r="BO1" s="102"/>
+      <c r="BP1" s="102"/>
+      <c r="BQ1" s="102"/>
+      <c r="BR1" s="102"/>
+      <c r="BS1" s="102"/>
+      <c r="BT1" s="102"/>
+      <c r="BU1" s="102"/>
+      <c r="BV1" s="102"/>
+      <c r="BW1" s="102"/>
+      <c r="BX1" s="102"/>
+      <c r="BY1" s="102"/>
+      <c r="BZ1" s="102"/>
+      <c r="CA1" s="102"/>
+      <c r="CB1" s="102"/>
+      <c r="CC1" s="102"/>
+      <c r="CD1" s="102"/>
+      <c r="CE1" s="102"/>
+      <c r="CF1" s="102"/>
+      <c r="CG1" s="102"/>
+      <c r="CH1" s="102"/>
+      <c r="CI1" s="102"/>
+      <c r="CJ1" s="102"/>
+      <c r="CK1" s="102"/>
+      <c r="CL1" s="102"/>
+      <c r="CM1" s="102"/>
+      <c r="CN1" s="102"/>
+      <c r="CO1" s="102"/>
+      <c r="CP1" s="102"/>
+      <c r="CQ1" s="102"/>
+      <c r="CR1" s="102"/>
+      <c r="CS1" s="102"/>
+      <c r="CT1" s="102"/>
+      <c r="CU1" s="102"/>
+      <c r="CV1" s="102"/>
+      <c r="CW1" s="102"/>
+      <c r="CX1" s="102"/>
+      <c r="CY1" s="102"/>
+      <c r="CZ1" s="102"/>
+      <c r="DA1" s="102"/>
+      <c r="DB1" s="102"/>
+      <c r="DC1" s="102"/>
+      <c r="DD1" s="102"/>
+      <c r="DE1" s="102"/>
+      <c r="DF1" s="102"/>
+      <c r="DG1" s="102"/>
+      <c r="DH1" s="102"/>
+      <c r="DI1" s="102"/>
+      <c r="DJ1" s="102"/>
+      <c r="DK1" s="102"/>
+      <c r="DL1" s="102"/>
+      <c r="DM1" s="102"/>
+      <c r="DN1" s="102"/>
+      <c r="DO1" s="102"/>
+      <c r="DP1" s="102"/>
+      <c r="DQ1" s="102"/>
+      <c r="DR1" s="102"/>
+      <c r="DS1" s="102"/>
+      <c r="DT1" s="102"/>
+      <c r="DU1" s="102"/>
+      <c r="DV1" s="102"/>
+      <c r="DW1" s="102"/>
+      <c r="DX1" s="102"/>
+      <c r="DY1" s="102"/>
+      <c r="DZ1" s="102"/>
+      <c r="EA1" s="102"/>
+      <c r="EB1" s="102"/>
+      <c r="EC1" s="102"/>
+      <c r="ED1" s="102"/>
+      <c r="EE1" s="102"/>
+      <c r="EF1" s="102"/>
+      <c r="EG1" s="102"/>
+      <c r="EH1" s="102"/>
+      <c r="EI1" s="102"/>
+      <c r="EJ1" s="102"/>
+      <c r="EK1" s="102"/>
+      <c r="EL1" s="102"/>
+      <c r="EM1" s="102"/>
+      <c r="EN1" s="102"/>
+      <c r="EO1" s="102"/>
+      <c r="EP1" s="102"/>
+      <c r="EQ1" s="102"/>
+      <c r="ER1" s="102"/>
+      <c r="ES1" s="102"/>
+      <c r="ET1" s="102"/>
+      <c r="EU1" s="102"/>
+      <c r="EV1" s="102"/>
+      <c r="EW1" s="102"/>
+      <c r="EX1" s="102"/>
+      <c r="EY1" s="102"/>
+      <c r="EZ1" s="102"/>
+      <c r="FA1" s="102"/>
+      <c r="FB1" s="102"/>
+      <c r="FC1" s="102"/>
+      <c r="FD1" s="102"/>
+      <c r="FE1" s="102"/>
+      <c r="FF1" s="102"/>
+      <c r="FG1" s="102"/>
+      <c r="FH1" s="102"/>
+      <c r="FI1" s="102"/>
+      <c r="FJ1" s="102"/>
+      <c r="FK1" s="102"/>
+      <c r="FL1" s="102"/>
+      <c r="FM1" s="102"/>
+      <c r="FN1" s="102"/>
+      <c r="FO1" s="102"/>
+      <c r="FP1" s="102"/>
+      <c r="FQ1" s="102"/>
+      <c r="FR1" s="102"/>
+      <c r="FS1" s="102"/>
+      <c r="FT1" s="102"/>
+      <c r="FU1" s="102"/>
+      <c r="FV1" s="102"/>
+      <c r="FW1" s="102"/>
+      <c r="FX1" s="102"/>
+      <c r="FY1" s="102"/>
+      <c r="FZ1" s="102"/>
+      <c r="GA1" s="102"/>
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="102"/>
+      <c r="HF1" s="102"/>
+      <c r="HG1" s="102"/>
+      <c r="HH1" s="102"/>
+      <c r="HI1" s="102"/>
+      <c r="HJ1" s="102"/>
+      <c r="HK1" s="102"/>
+      <c r="HL1" s="102"/>
+      <c r="HM1" s="102"/>
+      <c r="HN1" s="102"/>
+      <c r="HO1" s="102"/>
+      <c r="HP1" s="102"/>
+      <c r="HQ1" s="102"/>
+      <c r="HR1" s="102"/>
+      <c r="HS1" s="102"/>
+      <c r="HT1" s="102"/>
+      <c r="HU1" s="102"/>
+      <c r="HV1" s="102"/>
+      <c r="HW1" s="102"/>
+      <c r="HX1" s="102"/>
+      <c r="HY1" s="102"/>
+      <c r="HZ1" s="102"/>
+      <c r="IA1" s="102"/>
+      <c r="IB1" s="102"/>
+      <c r="IC1" s="102"/>
+      <c r="ID1" s="102"/>
+      <c r="IE1" s="102"/>
+      <c r="IF1" s="102"/>
+      <c r="IG1" s="102"/>
+      <c r="IH1" s="102"/>
+      <c r="II1" s="102"/>
+      <c r="IJ1" s="102"/>
+      <c r="IK1" s="102"/>
+      <c r="IL1" s="102"/>
+      <c r="IM1" s="102"/>
+      <c r="IN1" s="102"/>
+      <c r="IO1" s="102"/>
+      <c r="IP1" s="102"/>
+      <c r="IQ1" s="102"/>
+      <c r="IR1" s="102"/>
+      <c r="IS1" s="102"/>
+      <c r="IT1" s="102"/>
+      <c r="IU1" s="102"/>
+      <c r="IV1" s="102"/>
+      <c r="IW1" s="102"/>
+    </row>
+    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
         <v>47</v>
       </c>
@@ -8979,8 +11469,257 @@
       <c r="H2" s="108" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
+      <c r="U2" s="127"/>
+      <c r="V2" s="127"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="127"/>
+      <c r="Y2" s="127"/>
+      <c r="Z2" s="127"/>
+      <c r="AA2" s="127"/>
+      <c r="AB2" s="127"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="127"/>
+      <c r="AE2" s="127"/>
+      <c r="AF2" s="127"/>
+      <c r="AG2" s="127"/>
+      <c r="AH2" s="127"/>
+      <c r="AI2" s="127"/>
+      <c r="AJ2" s="127"/>
+      <c r="AK2" s="127"/>
+      <c r="AL2" s="127"/>
+      <c r="AM2" s="127"/>
+      <c r="AN2" s="127"/>
+      <c r="AO2" s="127"/>
+      <c r="AP2" s="127"/>
+      <c r="AQ2" s="127"/>
+      <c r="AR2" s="127"/>
+      <c r="AS2" s="127"/>
+      <c r="AT2" s="127"/>
+      <c r="AU2" s="127"/>
+      <c r="AV2" s="127"/>
+      <c r="AW2" s="127"/>
+      <c r="AX2" s="127"/>
+      <c r="AY2" s="127"/>
+      <c r="AZ2" s="127"/>
+      <c r="BA2" s="127"/>
+      <c r="BB2" s="127"/>
+      <c r="BC2" s="127"/>
+      <c r="BD2" s="127"/>
+      <c r="BE2" s="127"/>
+      <c r="BF2" s="127"/>
+      <c r="BG2" s="127"/>
+      <c r="BH2" s="127"/>
+      <c r="BI2" s="127"/>
+      <c r="BJ2" s="127"/>
+      <c r="BK2" s="127"/>
+      <c r="BL2" s="127"/>
+      <c r="BM2" s="127"/>
+      <c r="BN2" s="127"/>
+      <c r="BO2" s="127"/>
+      <c r="BP2" s="127"/>
+      <c r="BQ2" s="127"/>
+      <c r="BR2" s="127"/>
+      <c r="BS2" s="127"/>
+      <c r="BT2" s="127"/>
+      <c r="BU2" s="127"/>
+      <c r="BV2" s="127"/>
+      <c r="BW2" s="127"/>
+      <c r="BX2" s="127"/>
+      <c r="BY2" s="127"/>
+      <c r="BZ2" s="127"/>
+      <c r="CA2" s="127"/>
+      <c r="CB2" s="127"/>
+      <c r="CC2" s="127"/>
+      <c r="CD2" s="127"/>
+      <c r="CE2" s="127"/>
+      <c r="CF2" s="127"/>
+      <c r="CG2" s="127"/>
+      <c r="CH2" s="127"/>
+      <c r="CI2" s="127"/>
+      <c r="CJ2" s="127"/>
+      <c r="CK2" s="127"/>
+      <c r="CL2" s="127"/>
+      <c r="CM2" s="127"/>
+      <c r="CN2" s="127"/>
+      <c r="CO2" s="127"/>
+      <c r="CP2" s="127"/>
+      <c r="CQ2" s="127"/>
+      <c r="CR2" s="127"/>
+      <c r="CS2" s="127"/>
+      <c r="CT2" s="127"/>
+      <c r="CU2" s="127"/>
+      <c r="CV2" s="127"/>
+      <c r="CW2" s="127"/>
+      <c r="CX2" s="127"/>
+      <c r="CY2" s="127"/>
+      <c r="CZ2" s="127"/>
+      <c r="DA2" s="127"/>
+      <c r="DB2" s="127"/>
+      <c r="DC2" s="127"/>
+      <c r="DD2" s="127"/>
+      <c r="DE2" s="127"/>
+      <c r="DF2" s="127"/>
+      <c r="DG2" s="127"/>
+      <c r="DH2" s="127"/>
+      <c r="DI2" s="127"/>
+      <c r="DJ2" s="127"/>
+      <c r="DK2" s="127"/>
+      <c r="DL2" s="127"/>
+      <c r="DM2" s="127"/>
+      <c r="DN2" s="127"/>
+      <c r="DO2" s="127"/>
+      <c r="DP2" s="127"/>
+      <c r="DQ2" s="127"/>
+      <c r="DR2" s="127"/>
+      <c r="DS2" s="127"/>
+      <c r="DT2" s="127"/>
+      <c r="DU2" s="127"/>
+      <c r="DV2" s="127"/>
+      <c r="DW2" s="127"/>
+      <c r="DX2" s="127"/>
+      <c r="DY2" s="127"/>
+      <c r="DZ2" s="127"/>
+      <c r="EA2" s="127"/>
+      <c r="EB2" s="127"/>
+      <c r="EC2" s="127"/>
+      <c r="ED2" s="127"/>
+      <c r="EE2" s="127"/>
+      <c r="EF2" s="127"/>
+      <c r="EG2" s="127"/>
+      <c r="EH2" s="127"/>
+      <c r="EI2" s="127"/>
+      <c r="EJ2" s="127"/>
+      <c r="EK2" s="127"/>
+      <c r="EL2" s="127"/>
+      <c r="EM2" s="127"/>
+      <c r="EN2" s="127"/>
+      <c r="EO2" s="127"/>
+      <c r="EP2" s="127"/>
+      <c r="EQ2" s="127"/>
+      <c r="ER2" s="127"/>
+      <c r="ES2" s="127"/>
+      <c r="ET2" s="127"/>
+      <c r="EU2" s="127"/>
+      <c r="EV2" s="127"/>
+      <c r="EW2" s="127"/>
+      <c r="EX2" s="127"/>
+      <c r="EY2" s="127"/>
+      <c r="EZ2" s="127"/>
+      <c r="FA2" s="127"/>
+      <c r="FB2" s="127"/>
+      <c r="FC2" s="127"/>
+      <c r="FD2" s="127"/>
+      <c r="FE2" s="127"/>
+      <c r="FF2" s="127"/>
+      <c r="FG2" s="127"/>
+      <c r="FH2" s="127"/>
+      <c r="FI2" s="127"/>
+      <c r="FJ2" s="127"/>
+      <c r="FK2" s="127"/>
+      <c r="FL2" s="127"/>
+      <c r="FM2" s="127"/>
+      <c r="FN2" s="127"/>
+      <c r="FO2" s="127"/>
+      <c r="FP2" s="127"/>
+      <c r="FQ2" s="127"/>
+      <c r="FR2" s="127"/>
+      <c r="FS2" s="127"/>
+      <c r="FT2" s="127"/>
+      <c r="FU2" s="127"/>
+      <c r="FV2" s="127"/>
+      <c r="FW2" s="127"/>
+      <c r="FX2" s="127"/>
+      <c r="FY2" s="127"/>
+      <c r="FZ2" s="127"/>
+      <c r="GA2" s="127"/>
+      <c r="GB2" s="127"/>
+      <c r="GC2" s="127"/>
+      <c r="GD2" s="127"/>
+      <c r="GE2" s="127"/>
+      <c r="GF2" s="127"/>
+      <c r="GG2" s="127"/>
+      <c r="GH2" s="127"/>
+      <c r="GI2" s="127"/>
+      <c r="GJ2" s="127"/>
+      <c r="GK2" s="127"/>
+      <c r="GL2" s="127"/>
+      <c r="GM2" s="127"/>
+      <c r="GN2" s="127"/>
+      <c r="GO2" s="127"/>
+      <c r="GP2" s="127"/>
+      <c r="GQ2" s="127"/>
+      <c r="GR2" s="127"/>
+      <c r="GS2" s="127"/>
+      <c r="GT2" s="127"/>
+      <c r="GU2" s="127"/>
+      <c r="GV2" s="127"/>
+      <c r="GW2" s="127"/>
+      <c r="GX2" s="127"/>
+      <c r="GY2" s="127"/>
+      <c r="GZ2" s="127"/>
+      <c r="HA2" s="127"/>
+      <c r="HB2" s="127"/>
+      <c r="HC2" s="127"/>
+      <c r="HD2" s="127"/>
+      <c r="HE2" s="127"/>
+      <c r="HF2" s="127"/>
+      <c r="HG2" s="127"/>
+      <c r="HH2" s="127"/>
+      <c r="HI2" s="127"/>
+      <c r="HJ2" s="127"/>
+      <c r="HK2" s="127"/>
+      <c r="HL2" s="127"/>
+      <c r="HM2" s="127"/>
+      <c r="HN2" s="127"/>
+      <c r="HO2" s="127"/>
+      <c r="HP2" s="127"/>
+      <c r="HQ2" s="127"/>
+      <c r="HR2" s="127"/>
+      <c r="HS2" s="127"/>
+      <c r="HT2" s="127"/>
+      <c r="HU2" s="127"/>
+      <c r="HV2" s="127"/>
+      <c r="HW2" s="127"/>
+      <c r="HX2" s="127"/>
+      <c r="HY2" s="127"/>
+      <c r="HZ2" s="127"/>
+      <c r="IA2" s="127"/>
+      <c r="IB2" s="127"/>
+      <c r="IC2" s="127"/>
+      <c r="ID2" s="127"/>
+      <c r="IE2" s="127"/>
+      <c r="IF2" s="127"/>
+      <c r="IG2" s="127"/>
+      <c r="IH2" s="127"/>
+      <c r="II2" s="127"/>
+      <c r="IJ2" s="127"/>
+      <c r="IK2" s="127"/>
+      <c r="IL2" s="127"/>
+      <c r="IM2" s="127"/>
+      <c r="IN2" s="127"/>
+      <c r="IO2" s="127"/>
+      <c r="IP2" s="127"/>
+      <c r="IQ2" s="127"/>
+      <c r="IR2" s="127"/>
+      <c r="IS2" s="127"/>
+      <c r="IT2" s="127"/>
+      <c r="IU2" s="127"/>
+      <c r="IV2" s="127"/>
+      <c r="IW2" s="127"/>
+    </row>
+    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="107"/>
       <c r="B3" s="107"/>
       <c r="C3" s="107"/>
@@ -8991,6 +11730,255 @@
         <v>52</v>
       </c>
       <c r="H3" s="108"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="128"/>
+      <c r="S3" s="128"/>
+      <c r="T3" s="128"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="128"/>
+      <c r="AB3" s="128"/>
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="128"/>
+      <c r="AF3" s="128"/>
+      <c r="AG3" s="128"/>
+      <c r="AH3" s="128"/>
+      <c r="AI3" s="128"/>
+      <c r="AJ3" s="128"/>
+      <c r="AK3" s="128"/>
+      <c r="AL3" s="128"/>
+      <c r="AM3" s="128"/>
+      <c r="AN3" s="128"/>
+      <c r="AO3" s="128"/>
+      <c r="AP3" s="128"/>
+      <c r="AQ3" s="128"/>
+      <c r="AR3" s="128"/>
+      <c r="AS3" s="128"/>
+      <c r="AT3" s="128"/>
+      <c r="AU3" s="128"/>
+      <c r="AV3" s="128"/>
+      <c r="AW3" s="128"/>
+      <c r="AX3" s="128"/>
+      <c r="AY3" s="128"/>
+      <c r="AZ3" s="128"/>
+      <c r="BA3" s="128"/>
+      <c r="BB3" s="128"/>
+      <c r="BC3" s="128"/>
+      <c r="BD3" s="128"/>
+      <c r="BE3" s="128"/>
+      <c r="BF3" s="128"/>
+      <c r="BG3" s="128"/>
+      <c r="BH3" s="128"/>
+      <c r="BI3" s="128"/>
+      <c r="BJ3" s="128"/>
+      <c r="BK3" s="128"/>
+      <c r="BL3" s="128"/>
+      <c r="BM3" s="128"/>
+      <c r="BN3" s="128"/>
+      <c r="BO3" s="128"/>
+      <c r="BP3" s="128"/>
+      <c r="BQ3" s="128"/>
+      <c r="BR3" s="128"/>
+      <c r="BS3" s="128"/>
+      <c r="BT3" s="128"/>
+      <c r="BU3" s="128"/>
+      <c r="BV3" s="128"/>
+      <c r="BW3" s="128"/>
+      <c r="BX3" s="128"/>
+      <c r="BY3" s="128"/>
+      <c r="BZ3" s="128"/>
+      <c r="CA3" s="128"/>
+      <c r="CB3" s="128"/>
+      <c r="CC3" s="128"/>
+      <c r="CD3" s="128"/>
+      <c r="CE3" s="128"/>
+      <c r="CF3" s="128"/>
+      <c r="CG3" s="128"/>
+      <c r="CH3" s="128"/>
+      <c r="CI3" s="128"/>
+      <c r="CJ3" s="128"/>
+      <c r="CK3" s="128"/>
+      <c r="CL3" s="128"/>
+      <c r="CM3" s="128"/>
+      <c r="CN3" s="128"/>
+      <c r="CO3" s="128"/>
+      <c r="CP3" s="128"/>
+      <c r="CQ3" s="128"/>
+      <c r="CR3" s="128"/>
+      <c r="CS3" s="128"/>
+      <c r="CT3" s="128"/>
+      <c r="CU3" s="128"/>
+      <c r="CV3" s="128"/>
+      <c r="CW3" s="128"/>
+      <c r="CX3" s="128"/>
+      <c r="CY3" s="128"/>
+      <c r="CZ3" s="128"/>
+      <c r="DA3" s="128"/>
+      <c r="DB3" s="128"/>
+      <c r="DC3" s="128"/>
+      <c r="DD3" s="128"/>
+      <c r="DE3" s="128"/>
+      <c r="DF3" s="128"/>
+      <c r="DG3" s="128"/>
+      <c r="DH3" s="128"/>
+      <c r="DI3" s="128"/>
+      <c r="DJ3" s="128"/>
+      <c r="DK3" s="128"/>
+      <c r="DL3" s="128"/>
+      <c r="DM3" s="128"/>
+      <c r="DN3" s="128"/>
+      <c r="DO3" s="128"/>
+      <c r="DP3" s="128"/>
+      <c r="DQ3" s="128"/>
+      <c r="DR3" s="128"/>
+      <c r="DS3" s="128"/>
+      <c r="DT3" s="128"/>
+      <c r="DU3" s="128"/>
+      <c r="DV3" s="128"/>
+      <c r="DW3" s="128"/>
+      <c r="DX3" s="128"/>
+      <c r="DY3" s="128"/>
+      <c r="DZ3" s="128"/>
+      <c r="EA3" s="128"/>
+      <c r="EB3" s="128"/>
+      <c r="EC3" s="128"/>
+      <c r="ED3" s="128"/>
+      <c r="EE3" s="128"/>
+      <c r="EF3" s="128"/>
+      <c r="EG3" s="128"/>
+      <c r="EH3" s="128"/>
+      <c r="EI3" s="128"/>
+      <c r="EJ3" s="128"/>
+      <c r="EK3" s="128"/>
+      <c r="EL3" s="128"/>
+      <c r="EM3" s="128"/>
+      <c r="EN3" s="128"/>
+      <c r="EO3" s="128"/>
+      <c r="EP3" s="128"/>
+      <c r="EQ3" s="128"/>
+      <c r="ER3" s="128"/>
+      <c r="ES3" s="128"/>
+      <c r="ET3" s="128"/>
+      <c r="EU3" s="128"/>
+      <c r="EV3" s="128"/>
+      <c r="EW3" s="128"/>
+      <c r="EX3" s="128"/>
+      <c r="EY3" s="128"/>
+      <c r="EZ3" s="128"/>
+      <c r="FA3" s="128"/>
+      <c r="FB3" s="128"/>
+      <c r="FC3" s="128"/>
+      <c r="FD3" s="128"/>
+      <c r="FE3" s="128"/>
+      <c r="FF3" s="128"/>
+      <c r="FG3" s="128"/>
+      <c r="FH3" s="128"/>
+      <c r="FI3" s="128"/>
+      <c r="FJ3" s="128"/>
+      <c r="FK3" s="128"/>
+      <c r="FL3" s="128"/>
+      <c r="FM3" s="128"/>
+      <c r="FN3" s="128"/>
+      <c r="FO3" s="128"/>
+      <c r="FP3" s="128"/>
+      <c r="FQ3" s="128"/>
+      <c r="FR3" s="128"/>
+      <c r="FS3" s="128"/>
+      <c r="FT3" s="128"/>
+      <c r="FU3" s="128"/>
+      <c r="FV3" s="128"/>
+      <c r="FW3" s="128"/>
+      <c r="FX3" s="128"/>
+      <c r="FY3" s="128"/>
+      <c r="FZ3" s="128"/>
+      <c r="GA3" s="128"/>
+      <c r="GB3" s="128"/>
+      <c r="GC3" s="128"/>
+      <c r="GD3" s="128"/>
+      <c r="GE3" s="128"/>
+      <c r="GF3" s="128"/>
+      <c r="GG3" s="128"/>
+      <c r="GH3" s="128"/>
+      <c r="GI3" s="128"/>
+      <c r="GJ3" s="128"/>
+      <c r="GK3" s="128"/>
+      <c r="GL3" s="128"/>
+      <c r="GM3" s="128"/>
+      <c r="GN3" s="128"/>
+      <c r="GO3" s="128"/>
+      <c r="GP3" s="128"/>
+      <c r="GQ3" s="128"/>
+      <c r="GR3" s="128"/>
+      <c r="GS3" s="128"/>
+      <c r="GT3" s="128"/>
+      <c r="GU3" s="128"/>
+      <c r="GV3" s="128"/>
+      <c r="GW3" s="128"/>
+      <c r="GX3" s="128"/>
+      <c r="GY3" s="128"/>
+      <c r="GZ3" s="128"/>
+      <c r="HA3" s="128"/>
+      <c r="HB3" s="128"/>
+      <c r="HC3" s="128"/>
+      <c r="HD3" s="128"/>
+      <c r="HE3" s="128"/>
+      <c r="HF3" s="128"/>
+      <c r="HG3" s="128"/>
+      <c r="HH3" s="128"/>
+      <c r="HI3" s="128"/>
+      <c r="HJ3" s="128"/>
+      <c r="HK3" s="128"/>
+      <c r="HL3" s="128"/>
+      <c r="HM3" s="128"/>
+      <c r="HN3" s="128"/>
+      <c r="HO3" s="128"/>
+      <c r="HP3" s="128"/>
+      <c r="HQ3" s="128"/>
+      <c r="HR3" s="128"/>
+      <c r="HS3" s="128"/>
+      <c r="HT3" s="128"/>
+      <c r="HU3" s="128"/>
+      <c r="HV3" s="128"/>
+      <c r="HW3" s="128"/>
+      <c r="HX3" s="128"/>
+      <c r="HY3" s="128"/>
+      <c r="HZ3" s="128"/>
+      <c r="IA3" s="128"/>
+      <c r="IB3" s="128"/>
+      <c r="IC3" s="128"/>
+      <c r="ID3" s="128"/>
+      <c r="IE3" s="128"/>
+      <c r="IF3" s="128"/>
+      <c r="IG3" s="128"/>
+      <c r="IH3" s="128"/>
+      <c r="II3" s="128"/>
+      <c r="IJ3" s="128"/>
+      <c r="IK3" s="128"/>
+      <c r="IL3" s="128"/>
+      <c r="IM3" s="128"/>
+      <c r="IN3" s="128"/>
+      <c r="IO3" s="128"/>
+      <c r="IP3" s="128"/>
+      <c r="IQ3" s="128"/>
+      <c r="IR3" s="128"/>
+      <c r="IS3" s="128"/>
+      <c r="IT3" s="128"/>
+      <c r="IU3" s="128"/>
+      <c r="IV3" s="128"/>
+      <c r="IW3" s="128"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="107"/>
@@ -9002,7 +11990,7 @@
       <c r="G4" s="108"/>
       <c r="H4" s="108"/>
     </row>
-    <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
         <v>46319</v>
       </c>
@@ -9013,6 +12001,7 @@
         <v>56</v>
       </c>
       <c r="D5" s="122"/>
+      <c r="E5" s="119"/>
       <c r="F5" s="130" t="n">
         <v>1200</v>
       </c>
@@ -11210,8 +14199,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW201"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="118" width="8.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="119" width="19.66"/>
@@ -11224,7 +14213,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="9" style="119" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="103" t="s">
         <v>29</v>
       </c>
@@ -11246,8 +14235,257 @@
         <f aca="false">SUM(H5:H200)</f>
         <v>200</v>
       </c>
-    </row>
-    <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="102"/>
+      <c r="AG1" s="102"/>
+      <c r="AH1" s="102"/>
+      <c r="AI1" s="102"/>
+      <c r="AJ1" s="102"/>
+      <c r="AK1" s="102"/>
+      <c r="AL1" s="102"/>
+      <c r="AM1" s="102"/>
+      <c r="AN1" s="102"/>
+      <c r="AO1" s="102"/>
+      <c r="AP1" s="102"/>
+      <c r="AQ1" s="102"/>
+      <c r="AR1" s="102"/>
+      <c r="AS1" s="102"/>
+      <c r="AT1" s="102"/>
+      <c r="AU1" s="102"/>
+      <c r="AV1" s="102"/>
+      <c r="AW1" s="102"/>
+      <c r="AX1" s="102"/>
+      <c r="AY1" s="102"/>
+      <c r="AZ1" s="102"/>
+      <c r="BA1" s="102"/>
+      <c r="BB1" s="102"/>
+      <c r="BC1" s="102"/>
+      <c r="BD1" s="102"/>
+      <c r="BE1" s="102"/>
+      <c r="BF1" s="102"/>
+      <c r="BG1" s="102"/>
+      <c r="BH1" s="102"/>
+      <c r="BI1" s="102"/>
+      <c r="BJ1" s="102"/>
+      <c r="BK1" s="102"/>
+      <c r="BL1" s="102"/>
+      <c r="BM1" s="102"/>
+      <c r="BN1" s="102"/>
+      <c r="BO1" s="102"/>
+      <c r="BP1" s="102"/>
+      <c r="BQ1" s="102"/>
+      <c r="BR1" s="102"/>
+      <c r="BS1" s="102"/>
+      <c r="BT1" s="102"/>
+      <c r="BU1" s="102"/>
+      <c r="BV1" s="102"/>
+      <c r="BW1" s="102"/>
+      <c r="BX1" s="102"/>
+      <c r="BY1" s="102"/>
+      <c r="BZ1" s="102"/>
+      <c r="CA1" s="102"/>
+      <c r="CB1" s="102"/>
+      <c r="CC1" s="102"/>
+      <c r="CD1" s="102"/>
+      <c r="CE1" s="102"/>
+      <c r="CF1" s="102"/>
+      <c r="CG1" s="102"/>
+      <c r="CH1" s="102"/>
+      <c r="CI1" s="102"/>
+      <c r="CJ1" s="102"/>
+      <c r="CK1" s="102"/>
+      <c r="CL1" s="102"/>
+      <c r="CM1" s="102"/>
+      <c r="CN1" s="102"/>
+      <c r="CO1" s="102"/>
+      <c r="CP1" s="102"/>
+      <c r="CQ1" s="102"/>
+      <c r="CR1" s="102"/>
+      <c r="CS1" s="102"/>
+      <c r="CT1" s="102"/>
+      <c r="CU1" s="102"/>
+      <c r="CV1" s="102"/>
+      <c r="CW1" s="102"/>
+      <c r="CX1" s="102"/>
+      <c r="CY1" s="102"/>
+      <c r="CZ1" s="102"/>
+      <c r="DA1" s="102"/>
+      <c r="DB1" s="102"/>
+      <c r="DC1" s="102"/>
+      <c r="DD1" s="102"/>
+      <c r="DE1" s="102"/>
+      <c r="DF1" s="102"/>
+      <c r="DG1" s="102"/>
+      <c r="DH1" s="102"/>
+      <c r="DI1" s="102"/>
+      <c r="DJ1" s="102"/>
+      <c r="DK1" s="102"/>
+      <c r="DL1" s="102"/>
+      <c r="DM1" s="102"/>
+      <c r="DN1" s="102"/>
+      <c r="DO1" s="102"/>
+      <c r="DP1" s="102"/>
+      <c r="DQ1" s="102"/>
+      <c r="DR1" s="102"/>
+      <c r="DS1" s="102"/>
+      <c r="DT1" s="102"/>
+      <c r="DU1" s="102"/>
+      <c r="DV1" s="102"/>
+      <c r="DW1" s="102"/>
+      <c r="DX1" s="102"/>
+      <c r="DY1" s="102"/>
+      <c r="DZ1" s="102"/>
+      <c r="EA1" s="102"/>
+      <c r="EB1" s="102"/>
+      <c r="EC1" s="102"/>
+      <c r="ED1" s="102"/>
+      <c r="EE1" s="102"/>
+      <c r="EF1" s="102"/>
+      <c r="EG1" s="102"/>
+      <c r="EH1" s="102"/>
+      <c r="EI1" s="102"/>
+      <c r="EJ1" s="102"/>
+      <c r="EK1" s="102"/>
+      <c r="EL1" s="102"/>
+      <c r="EM1" s="102"/>
+      <c r="EN1" s="102"/>
+      <c r="EO1" s="102"/>
+      <c r="EP1" s="102"/>
+      <c r="EQ1" s="102"/>
+      <c r="ER1" s="102"/>
+      <c r="ES1" s="102"/>
+      <c r="ET1" s="102"/>
+      <c r="EU1" s="102"/>
+      <c r="EV1" s="102"/>
+      <c r="EW1" s="102"/>
+      <c r="EX1" s="102"/>
+      <c r="EY1" s="102"/>
+      <c r="EZ1" s="102"/>
+      <c r="FA1" s="102"/>
+      <c r="FB1" s="102"/>
+      <c r="FC1" s="102"/>
+      <c r="FD1" s="102"/>
+      <c r="FE1" s="102"/>
+      <c r="FF1" s="102"/>
+      <c r="FG1" s="102"/>
+      <c r="FH1" s="102"/>
+      <c r="FI1" s="102"/>
+      <c r="FJ1" s="102"/>
+      <c r="FK1" s="102"/>
+      <c r="FL1" s="102"/>
+      <c r="FM1" s="102"/>
+      <c r="FN1" s="102"/>
+      <c r="FO1" s="102"/>
+      <c r="FP1" s="102"/>
+      <c r="FQ1" s="102"/>
+      <c r="FR1" s="102"/>
+      <c r="FS1" s="102"/>
+      <c r="FT1" s="102"/>
+      <c r="FU1" s="102"/>
+      <c r="FV1" s="102"/>
+      <c r="FW1" s="102"/>
+      <c r="FX1" s="102"/>
+      <c r="FY1" s="102"/>
+      <c r="FZ1" s="102"/>
+      <c r="GA1" s="102"/>
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="102"/>
+      <c r="HF1" s="102"/>
+      <c r="HG1" s="102"/>
+      <c r="HH1" s="102"/>
+      <c r="HI1" s="102"/>
+      <c r="HJ1" s="102"/>
+      <c r="HK1" s="102"/>
+      <c r="HL1" s="102"/>
+      <c r="HM1" s="102"/>
+      <c r="HN1" s="102"/>
+      <c r="HO1" s="102"/>
+      <c r="HP1" s="102"/>
+      <c r="HQ1" s="102"/>
+      <c r="HR1" s="102"/>
+      <c r="HS1" s="102"/>
+      <c r="HT1" s="102"/>
+      <c r="HU1" s="102"/>
+      <c r="HV1" s="102"/>
+      <c r="HW1" s="102"/>
+      <c r="HX1" s="102"/>
+      <c r="HY1" s="102"/>
+      <c r="HZ1" s="102"/>
+      <c r="IA1" s="102"/>
+      <c r="IB1" s="102"/>
+      <c r="IC1" s="102"/>
+      <c r="ID1" s="102"/>
+      <c r="IE1" s="102"/>
+      <c r="IF1" s="102"/>
+      <c r="IG1" s="102"/>
+      <c r="IH1" s="102"/>
+      <c r="II1" s="102"/>
+      <c r="IJ1" s="102"/>
+      <c r="IK1" s="102"/>
+      <c r="IL1" s="102"/>
+      <c r="IM1" s="102"/>
+      <c r="IN1" s="102"/>
+      <c r="IO1" s="102"/>
+      <c r="IP1" s="102"/>
+      <c r="IQ1" s="102"/>
+      <c r="IR1" s="102"/>
+      <c r="IS1" s="102"/>
+      <c r="IT1" s="102"/>
+      <c r="IU1" s="102"/>
+      <c r="IV1" s="102"/>
+      <c r="IW1" s="102"/>
+    </row>
+    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
         <v>47</v>
       </c>
@@ -11272,8 +14510,257 @@
       <c r="H2" s="108" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
+      <c r="U2" s="127"/>
+      <c r="V2" s="127"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="127"/>
+      <c r="Y2" s="127"/>
+      <c r="Z2" s="127"/>
+      <c r="AA2" s="127"/>
+      <c r="AB2" s="127"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="127"/>
+      <c r="AE2" s="127"/>
+      <c r="AF2" s="127"/>
+      <c r="AG2" s="127"/>
+      <c r="AH2" s="127"/>
+      <c r="AI2" s="127"/>
+      <c r="AJ2" s="127"/>
+      <c r="AK2" s="127"/>
+      <c r="AL2" s="127"/>
+      <c r="AM2" s="127"/>
+      <c r="AN2" s="127"/>
+      <c r="AO2" s="127"/>
+      <c r="AP2" s="127"/>
+      <c r="AQ2" s="127"/>
+      <c r="AR2" s="127"/>
+      <c r="AS2" s="127"/>
+      <c r="AT2" s="127"/>
+      <c r="AU2" s="127"/>
+      <c r="AV2" s="127"/>
+      <c r="AW2" s="127"/>
+      <c r="AX2" s="127"/>
+      <c r="AY2" s="127"/>
+      <c r="AZ2" s="127"/>
+      <c r="BA2" s="127"/>
+      <c r="BB2" s="127"/>
+      <c r="BC2" s="127"/>
+      <c r="BD2" s="127"/>
+      <c r="BE2" s="127"/>
+      <c r="BF2" s="127"/>
+      <c r="BG2" s="127"/>
+      <c r="BH2" s="127"/>
+      <c r="BI2" s="127"/>
+      <c r="BJ2" s="127"/>
+      <c r="BK2" s="127"/>
+      <c r="BL2" s="127"/>
+      <c r="BM2" s="127"/>
+      <c r="BN2" s="127"/>
+      <c r="BO2" s="127"/>
+      <c r="BP2" s="127"/>
+      <c r="BQ2" s="127"/>
+      <c r="BR2" s="127"/>
+      <c r="BS2" s="127"/>
+      <c r="BT2" s="127"/>
+      <c r="BU2" s="127"/>
+      <c r="BV2" s="127"/>
+      <c r="BW2" s="127"/>
+      <c r="BX2" s="127"/>
+      <c r="BY2" s="127"/>
+      <c r="BZ2" s="127"/>
+      <c r="CA2" s="127"/>
+      <c r="CB2" s="127"/>
+      <c r="CC2" s="127"/>
+      <c r="CD2" s="127"/>
+      <c r="CE2" s="127"/>
+      <c r="CF2" s="127"/>
+      <c r="CG2" s="127"/>
+      <c r="CH2" s="127"/>
+      <c r="CI2" s="127"/>
+      <c r="CJ2" s="127"/>
+      <c r="CK2" s="127"/>
+      <c r="CL2" s="127"/>
+      <c r="CM2" s="127"/>
+      <c r="CN2" s="127"/>
+      <c r="CO2" s="127"/>
+      <c r="CP2" s="127"/>
+      <c r="CQ2" s="127"/>
+      <c r="CR2" s="127"/>
+      <c r="CS2" s="127"/>
+      <c r="CT2" s="127"/>
+      <c r="CU2" s="127"/>
+      <c r="CV2" s="127"/>
+      <c r="CW2" s="127"/>
+      <c r="CX2" s="127"/>
+      <c r="CY2" s="127"/>
+      <c r="CZ2" s="127"/>
+      <c r="DA2" s="127"/>
+      <c r="DB2" s="127"/>
+      <c r="DC2" s="127"/>
+      <c r="DD2" s="127"/>
+      <c r="DE2" s="127"/>
+      <c r="DF2" s="127"/>
+      <c r="DG2" s="127"/>
+      <c r="DH2" s="127"/>
+      <c r="DI2" s="127"/>
+      <c r="DJ2" s="127"/>
+      <c r="DK2" s="127"/>
+      <c r="DL2" s="127"/>
+      <c r="DM2" s="127"/>
+      <c r="DN2" s="127"/>
+      <c r="DO2" s="127"/>
+      <c r="DP2" s="127"/>
+      <c r="DQ2" s="127"/>
+      <c r="DR2" s="127"/>
+      <c r="DS2" s="127"/>
+      <c r="DT2" s="127"/>
+      <c r="DU2" s="127"/>
+      <c r="DV2" s="127"/>
+      <c r="DW2" s="127"/>
+      <c r="DX2" s="127"/>
+      <c r="DY2" s="127"/>
+      <c r="DZ2" s="127"/>
+      <c r="EA2" s="127"/>
+      <c r="EB2" s="127"/>
+      <c r="EC2" s="127"/>
+      <c r="ED2" s="127"/>
+      <c r="EE2" s="127"/>
+      <c r="EF2" s="127"/>
+      <c r="EG2" s="127"/>
+      <c r="EH2" s="127"/>
+      <c r="EI2" s="127"/>
+      <c r="EJ2" s="127"/>
+      <c r="EK2" s="127"/>
+      <c r="EL2" s="127"/>
+      <c r="EM2" s="127"/>
+      <c r="EN2" s="127"/>
+      <c r="EO2" s="127"/>
+      <c r="EP2" s="127"/>
+      <c r="EQ2" s="127"/>
+      <c r="ER2" s="127"/>
+      <c r="ES2" s="127"/>
+      <c r="ET2" s="127"/>
+      <c r="EU2" s="127"/>
+      <c r="EV2" s="127"/>
+      <c r="EW2" s="127"/>
+      <c r="EX2" s="127"/>
+      <c r="EY2" s="127"/>
+      <c r="EZ2" s="127"/>
+      <c r="FA2" s="127"/>
+      <c r="FB2" s="127"/>
+      <c r="FC2" s="127"/>
+      <c r="FD2" s="127"/>
+      <c r="FE2" s="127"/>
+      <c r="FF2" s="127"/>
+      <c r="FG2" s="127"/>
+      <c r="FH2" s="127"/>
+      <c r="FI2" s="127"/>
+      <c r="FJ2" s="127"/>
+      <c r="FK2" s="127"/>
+      <c r="FL2" s="127"/>
+      <c r="FM2" s="127"/>
+      <c r="FN2" s="127"/>
+      <c r="FO2" s="127"/>
+      <c r="FP2" s="127"/>
+      <c r="FQ2" s="127"/>
+      <c r="FR2" s="127"/>
+      <c r="FS2" s="127"/>
+      <c r="FT2" s="127"/>
+      <c r="FU2" s="127"/>
+      <c r="FV2" s="127"/>
+      <c r="FW2" s="127"/>
+      <c r="FX2" s="127"/>
+      <c r="FY2" s="127"/>
+      <c r="FZ2" s="127"/>
+      <c r="GA2" s="127"/>
+      <c r="GB2" s="127"/>
+      <c r="GC2" s="127"/>
+      <c r="GD2" s="127"/>
+      <c r="GE2" s="127"/>
+      <c r="GF2" s="127"/>
+      <c r="GG2" s="127"/>
+      <c r="GH2" s="127"/>
+      <c r="GI2" s="127"/>
+      <c r="GJ2" s="127"/>
+      <c r="GK2" s="127"/>
+      <c r="GL2" s="127"/>
+      <c r="GM2" s="127"/>
+      <c r="GN2" s="127"/>
+      <c r="GO2" s="127"/>
+      <c r="GP2" s="127"/>
+      <c r="GQ2" s="127"/>
+      <c r="GR2" s="127"/>
+      <c r="GS2" s="127"/>
+      <c r="GT2" s="127"/>
+      <c r="GU2" s="127"/>
+      <c r="GV2" s="127"/>
+      <c r="GW2" s="127"/>
+      <c r="GX2" s="127"/>
+      <c r="GY2" s="127"/>
+      <c r="GZ2" s="127"/>
+      <c r="HA2" s="127"/>
+      <c r="HB2" s="127"/>
+      <c r="HC2" s="127"/>
+      <c r="HD2" s="127"/>
+      <c r="HE2" s="127"/>
+      <c r="HF2" s="127"/>
+      <c r="HG2" s="127"/>
+      <c r="HH2" s="127"/>
+      <c r="HI2" s="127"/>
+      <c r="HJ2" s="127"/>
+      <c r="HK2" s="127"/>
+      <c r="HL2" s="127"/>
+      <c r="HM2" s="127"/>
+      <c r="HN2" s="127"/>
+      <c r="HO2" s="127"/>
+      <c r="HP2" s="127"/>
+      <c r="HQ2" s="127"/>
+      <c r="HR2" s="127"/>
+      <c r="HS2" s="127"/>
+      <c r="HT2" s="127"/>
+      <c r="HU2" s="127"/>
+      <c r="HV2" s="127"/>
+      <c r="HW2" s="127"/>
+      <c r="HX2" s="127"/>
+      <c r="HY2" s="127"/>
+      <c r="HZ2" s="127"/>
+      <c r="IA2" s="127"/>
+      <c r="IB2" s="127"/>
+      <c r="IC2" s="127"/>
+      <c r="ID2" s="127"/>
+      <c r="IE2" s="127"/>
+      <c r="IF2" s="127"/>
+      <c r="IG2" s="127"/>
+      <c r="IH2" s="127"/>
+      <c r="II2" s="127"/>
+      <c r="IJ2" s="127"/>
+      <c r="IK2" s="127"/>
+      <c r="IL2" s="127"/>
+      <c r="IM2" s="127"/>
+      <c r="IN2" s="127"/>
+      <c r="IO2" s="127"/>
+      <c r="IP2" s="127"/>
+      <c r="IQ2" s="127"/>
+      <c r="IR2" s="127"/>
+      <c r="IS2" s="127"/>
+      <c r="IT2" s="127"/>
+      <c r="IU2" s="127"/>
+      <c r="IV2" s="127"/>
+      <c r="IW2" s="127"/>
+    </row>
+    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="107"/>
       <c r="B3" s="107"/>
       <c r="C3" s="107"/>
@@ -11284,6 +14771,255 @@
         <v>52</v>
       </c>
       <c r="H3" s="108"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="128"/>
+      <c r="S3" s="128"/>
+      <c r="T3" s="128"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="128"/>
+      <c r="AB3" s="128"/>
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="128"/>
+      <c r="AF3" s="128"/>
+      <c r="AG3" s="128"/>
+      <c r="AH3" s="128"/>
+      <c r="AI3" s="128"/>
+      <c r="AJ3" s="128"/>
+      <c r="AK3" s="128"/>
+      <c r="AL3" s="128"/>
+      <c r="AM3" s="128"/>
+      <c r="AN3" s="128"/>
+      <c r="AO3" s="128"/>
+      <c r="AP3" s="128"/>
+      <c r="AQ3" s="128"/>
+      <c r="AR3" s="128"/>
+      <c r="AS3" s="128"/>
+      <c r="AT3" s="128"/>
+      <c r="AU3" s="128"/>
+      <c r="AV3" s="128"/>
+      <c r="AW3" s="128"/>
+      <c r="AX3" s="128"/>
+      <c r="AY3" s="128"/>
+      <c r="AZ3" s="128"/>
+      <c r="BA3" s="128"/>
+      <c r="BB3" s="128"/>
+      <c r="BC3" s="128"/>
+      <c r="BD3" s="128"/>
+      <c r="BE3" s="128"/>
+      <c r="BF3" s="128"/>
+      <c r="BG3" s="128"/>
+      <c r="BH3" s="128"/>
+      <c r="BI3" s="128"/>
+      <c r="BJ3" s="128"/>
+      <c r="BK3" s="128"/>
+      <c r="BL3" s="128"/>
+      <c r="BM3" s="128"/>
+      <c r="BN3" s="128"/>
+      <c r="BO3" s="128"/>
+      <c r="BP3" s="128"/>
+      <c r="BQ3" s="128"/>
+      <c r="BR3" s="128"/>
+      <c r="BS3" s="128"/>
+      <c r="BT3" s="128"/>
+      <c r="BU3" s="128"/>
+      <c r="BV3" s="128"/>
+      <c r="BW3" s="128"/>
+      <c r="BX3" s="128"/>
+      <c r="BY3" s="128"/>
+      <c r="BZ3" s="128"/>
+      <c r="CA3" s="128"/>
+      <c r="CB3" s="128"/>
+      <c r="CC3" s="128"/>
+      <c r="CD3" s="128"/>
+      <c r="CE3" s="128"/>
+      <c r="CF3" s="128"/>
+      <c r="CG3" s="128"/>
+      <c r="CH3" s="128"/>
+      <c r="CI3" s="128"/>
+      <c r="CJ3" s="128"/>
+      <c r="CK3" s="128"/>
+      <c r="CL3" s="128"/>
+      <c r="CM3" s="128"/>
+      <c r="CN3" s="128"/>
+      <c r="CO3" s="128"/>
+      <c r="CP3" s="128"/>
+      <c r="CQ3" s="128"/>
+      <c r="CR3" s="128"/>
+      <c r="CS3" s="128"/>
+      <c r="CT3" s="128"/>
+      <c r="CU3" s="128"/>
+      <c r="CV3" s="128"/>
+      <c r="CW3" s="128"/>
+      <c r="CX3" s="128"/>
+      <c r="CY3" s="128"/>
+      <c r="CZ3" s="128"/>
+      <c r="DA3" s="128"/>
+      <c r="DB3" s="128"/>
+      <c r="DC3" s="128"/>
+      <c r="DD3" s="128"/>
+      <c r="DE3" s="128"/>
+      <c r="DF3" s="128"/>
+      <c r="DG3" s="128"/>
+      <c r="DH3" s="128"/>
+      <c r="DI3" s="128"/>
+      <c r="DJ3" s="128"/>
+      <c r="DK3" s="128"/>
+      <c r="DL3" s="128"/>
+      <c r="DM3" s="128"/>
+      <c r="DN3" s="128"/>
+      <c r="DO3" s="128"/>
+      <c r="DP3" s="128"/>
+      <c r="DQ3" s="128"/>
+      <c r="DR3" s="128"/>
+      <c r="DS3" s="128"/>
+      <c r="DT3" s="128"/>
+      <c r="DU3" s="128"/>
+      <c r="DV3" s="128"/>
+      <c r="DW3" s="128"/>
+      <c r="DX3" s="128"/>
+      <c r="DY3" s="128"/>
+      <c r="DZ3" s="128"/>
+      <c r="EA3" s="128"/>
+      <c r="EB3" s="128"/>
+      <c r="EC3" s="128"/>
+      <c r="ED3" s="128"/>
+      <c r="EE3" s="128"/>
+      <c r="EF3" s="128"/>
+      <c r="EG3" s="128"/>
+      <c r="EH3" s="128"/>
+      <c r="EI3" s="128"/>
+      <c r="EJ3" s="128"/>
+      <c r="EK3" s="128"/>
+      <c r="EL3" s="128"/>
+      <c r="EM3" s="128"/>
+      <c r="EN3" s="128"/>
+      <c r="EO3" s="128"/>
+      <c r="EP3" s="128"/>
+      <c r="EQ3" s="128"/>
+      <c r="ER3" s="128"/>
+      <c r="ES3" s="128"/>
+      <c r="ET3" s="128"/>
+      <c r="EU3" s="128"/>
+      <c r="EV3" s="128"/>
+      <c r="EW3" s="128"/>
+      <c r="EX3" s="128"/>
+      <c r="EY3" s="128"/>
+      <c r="EZ3" s="128"/>
+      <c r="FA3" s="128"/>
+      <c r="FB3" s="128"/>
+      <c r="FC3" s="128"/>
+      <c r="FD3" s="128"/>
+      <c r="FE3" s="128"/>
+      <c r="FF3" s="128"/>
+      <c r="FG3" s="128"/>
+      <c r="FH3" s="128"/>
+      <c r="FI3" s="128"/>
+      <c r="FJ3" s="128"/>
+      <c r="FK3" s="128"/>
+      <c r="FL3" s="128"/>
+      <c r="FM3" s="128"/>
+      <c r="FN3" s="128"/>
+      <c r="FO3" s="128"/>
+      <c r="FP3" s="128"/>
+      <c r="FQ3" s="128"/>
+      <c r="FR3" s="128"/>
+      <c r="FS3" s="128"/>
+      <c r="FT3" s="128"/>
+      <c r="FU3" s="128"/>
+      <c r="FV3" s="128"/>
+      <c r="FW3" s="128"/>
+      <c r="FX3" s="128"/>
+      <c r="FY3" s="128"/>
+      <c r="FZ3" s="128"/>
+      <c r="GA3" s="128"/>
+      <c r="GB3" s="128"/>
+      <c r="GC3" s="128"/>
+      <c r="GD3" s="128"/>
+      <c r="GE3" s="128"/>
+      <c r="GF3" s="128"/>
+      <c r="GG3" s="128"/>
+      <c r="GH3" s="128"/>
+      <c r="GI3" s="128"/>
+      <c r="GJ3" s="128"/>
+      <c r="GK3" s="128"/>
+      <c r="GL3" s="128"/>
+      <c r="GM3" s="128"/>
+      <c r="GN3" s="128"/>
+      <c r="GO3" s="128"/>
+      <c r="GP3" s="128"/>
+      <c r="GQ3" s="128"/>
+      <c r="GR3" s="128"/>
+      <c r="GS3" s="128"/>
+      <c r="GT3" s="128"/>
+      <c r="GU3" s="128"/>
+      <c r="GV3" s="128"/>
+      <c r="GW3" s="128"/>
+      <c r="GX3" s="128"/>
+      <c r="GY3" s="128"/>
+      <c r="GZ3" s="128"/>
+      <c r="HA3" s="128"/>
+      <c r="HB3" s="128"/>
+      <c r="HC3" s="128"/>
+      <c r="HD3" s="128"/>
+      <c r="HE3" s="128"/>
+      <c r="HF3" s="128"/>
+      <c r="HG3" s="128"/>
+      <c r="HH3" s="128"/>
+      <c r="HI3" s="128"/>
+      <c r="HJ3" s="128"/>
+      <c r="HK3" s="128"/>
+      <c r="HL3" s="128"/>
+      <c r="HM3" s="128"/>
+      <c r="HN3" s="128"/>
+      <c r="HO3" s="128"/>
+      <c r="HP3" s="128"/>
+      <c r="HQ3" s="128"/>
+      <c r="HR3" s="128"/>
+      <c r="HS3" s="128"/>
+      <c r="HT3" s="128"/>
+      <c r="HU3" s="128"/>
+      <c r="HV3" s="128"/>
+      <c r="HW3" s="128"/>
+      <c r="HX3" s="128"/>
+      <c r="HY3" s="128"/>
+      <c r="HZ3" s="128"/>
+      <c r="IA3" s="128"/>
+      <c r="IB3" s="128"/>
+      <c r="IC3" s="128"/>
+      <c r="ID3" s="128"/>
+      <c r="IE3" s="128"/>
+      <c r="IF3" s="128"/>
+      <c r="IG3" s="128"/>
+      <c r="IH3" s="128"/>
+      <c r="II3" s="128"/>
+      <c r="IJ3" s="128"/>
+      <c r="IK3" s="128"/>
+      <c r="IL3" s="128"/>
+      <c r="IM3" s="128"/>
+      <c r="IN3" s="128"/>
+      <c r="IO3" s="128"/>
+      <c r="IP3" s="128"/>
+      <c r="IQ3" s="128"/>
+      <c r="IR3" s="128"/>
+      <c r="IS3" s="128"/>
+      <c r="IT3" s="128"/>
+      <c r="IU3" s="128"/>
+      <c r="IV3" s="128"/>
+      <c r="IW3" s="128"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="107"/>
@@ -11295,7 +15031,7 @@
       <c r="G4" s="108"/>
       <c r="H4" s="108"/>
     </row>
-    <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
         <v>46706</v>
       </c>
@@ -11306,6 +15042,7 @@
         <v>58</v>
       </c>
       <c r="D5" s="122"/>
+      <c r="E5" s="119"/>
       <c r="F5" s="130" t="n">
         <v>240</v>
       </c>
@@ -13503,8 +17240,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW201"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="118" width="8.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="119" width="19.66"/>
@@ -13517,7 +17254,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="9" style="119" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="103" t="s">
         <v>29</v>
       </c>
@@ -13539,8 +17276,257 @@
         <f aca="false">SUM(H5:H200)</f>
         <v>300</v>
       </c>
-    </row>
-    <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="102"/>
+      <c r="AG1" s="102"/>
+      <c r="AH1" s="102"/>
+      <c r="AI1" s="102"/>
+      <c r="AJ1" s="102"/>
+      <c r="AK1" s="102"/>
+      <c r="AL1" s="102"/>
+      <c r="AM1" s="102"/>
+      <c r="AN1" s="102"/>
+      <c r="AO1" s="102"/>
+      <c r="AP1" s="102"/>
+      <c r="AQ1" s="102"/>
+      <c r="AR1" s="102"/>
+      <c r="AS1" s="102"/>
+      <c r="AT1" s="102"/>
+      <c r="AU1" s="102"/>
+      <c r="AV1" s="102"/>
+      <c r="AW1" s="102"/>
+      <c r="AX1" s="102"/>
+      <c r="AY1" s="102"/>
+      <c r="AZ1" s="102"/>
+      <c r="BA1" s="102"/>
+      <c r="BB1" s="102"/>
+      <c r="BC1" s="102"/>
+      <c r="BD1" s="102"/>
+      <c r="BE1" s="102"/>
+      <c r="BF1" s="102"/>
+      <c r="BG1" s="102"/>
+      <c r="BH1" s="102"/>
+      <c r="BI1" s="102"/>
+      <c r="BJ1" s="102"/>
+      <c r="BK1" s="102"/>
+      <c r="BL1" s="102"/>
+      <c r="BM1" s="102"/>
+      <c r="BN1" s="102"/>
+      <c r="BO1" s="102"/>
+      <c r="BP1" s="102"/>
+      <c r="BQ1" s="102"/>
+      <c r="BR1" s="102"/>
+      <c r="BS1" s="102"/>
+      <c r="BT1" s="102"/>
+      <c r="BU1" s="102"/>
+      <c r="BV1" s="102"/>
+      <c r="BW1" s="102"/>
+      <c r="BX1" s="102"/>
+      <c r="BY1" s="102"/>
+      <c r="BZ1" s="102"/>
+      <c r="CA1" s="102"/>
+      <c r="CB1" s="102"/>
+      <c r="CC1" s="102"/>
+      <c r="CD1" s="102"/>
+      <c r="CE1" s="102"/>
+      <c r="CF1" s="102"/>
+      <c r="CG1" s="102"/>
+      <c r="CH1" s="102"/>
+      <c r="CI1" s="102"/>
+      <c r="CJ1" s="102"/>
+      <c r="CK1" s="102"/>
+      <c r="CL1" s="102"/>
+      <c r="CM1" s="102"/>
+      <c r="CN1" s="102"/>
+      <c r="CO1" s="102"/>
+      <c r="CP1" s="102"/>
+      <c r="CQ1" s="102"/>
+      <c r="CR1" s="102"/>
+      <c r="CS1" s="102"/>
+      <c r="CT1" s="102"/>
+      <c r="CU1" s="102"/>
+      <c r="CV1" s="102"/>
+      <c r="CW1" s="102"/>
+      <c r="CX1" s="102"/>
+      <c r="CY1" s="102"/>
+      <c r="CZ1" s="102"/>
+      <c r="DA1" s="102"/>
+      <c r="DB1" s="102"/>
+      <c r="DC1" s="102"/>
+      <c r="DD1" s="102"/>
+      <c r="DE1" s="102"/>
+      <c r="DF1" s="102"/>
+      <c r="DG1" s="102"/>
+      <c r="DH1" s="102"/>
+      <c r="DI1" s="102"/>
+      <c r="DJ1" s="102"/>
+      <c r="DK1" s="102"/>
+      <c r="DL1" s="102"/>
+      <c r="DM1" s="102"/>
+      <c r="DN1" s="102"/>
+      <c r="DO1" s="102"/>
+      <c r="DP1" s="102"/>
+      <c r="DQ1" s="102"/>
+      <c r="DR1" s="102"/>
+      <c r="DS1" s="102"/>
+      <c r="DT1" s="102"/>
+      <c r="DU1" s="102"/>
+      <c r="DV1" s="102"/>
+      <c r="DW1" s="102"/>
+      <c r="DX1" s="102"/>
+      <c r="DY1" s="102"/>
+      <c r="DZ1" s="102"/>
+      <c r="EA1" s="102"/>
+      <c r="EB1" s="102"/>
+      <c r="EC1" s="102"/>
+      <c r="ED1" s="102"/>
+      <c r="EE1" s="102"/>
+      <c r="EF1" s="102"/>
+      <c r="EG1" s="102"/>
+      <c r="EH1" s="102"/>
+      <c r="EI1" s="102"/>
+      <c r="EJ1" s="102"/>
+      <c r="EK1" s="102"/>
+      <c r="EL1" s="102"/>
+      <c r="EM1" s="102"/>
+      <c r="EN1" s="102"/>
+      <c r="EO1" s="102"/>
+      <c r="EP1" s="102"/>
+      <c r="EQ1" s="102"/>
+      <c r="ER1" s="102"/>
+      <c r="ES1" s="102"/>
+      <c r="ET1" s="102"/>
+      <c r="EU1" s="102"/>
+      <c r="EV1" s="102"/>
+      <c r="EW1" s="102"/>
+      <c r="EX1" s="102"/>
+      <c r="EY1" s="102"/>
+      <c r="EZ1" s="102"/>
+      <c r="FA1" s="102"/>
+      <c r="FB1" s="102"/>
+      <c r="FC1" s="102"/>
+      <c r="FD1" s="102"/>
+      <c r="FE1" s="102"/>
+      <c r="FF1" s="102"/>
+      <c r="FG1" s="102"/>
+      <c r="FH1" s="102"/>
+      <c r="FI1" s="102"/>
+      <c r="FJ1" s="102"/>
+      <c r="FK1" s="102"/>
+      <c r="FL1" s="102"/>
+      <c r="FM1" s="102"/>
+      <c r="FN1" s="102"/>
+      <c r="FO1" s="102"/>
+      <c r="FP1" s="102"/>
+      <c r="FQ1" s="102"/>
+      <c r="FR1" s="102"/>
+      <c r="FS1" s="102"/>
+      <c r="FT1" s="102"/>
+      <c r="FU1" s="102"/>
+      <c r="FV1" s="102"/>
+      <c r="FW1" s="102"/>
+      <c r="FX1" s="102"/>
+      <c r="FY1" s="102"/>
+      <c r="FZ1" s="102"/>
+      <c r="GA1" s="102"/>
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="102"/>
+      <c r="HF1" s="102"/>
+      <c r="HG1" s="102"/>
+      <c r="HH1" s="102"/>
+      <c r="HI1" s="102"/>
+      <c r="HJ1" s="102"/>
+      <c r="HK1" s="102"/>
+      <c r="HL1" s="102"/>
+      <c r="HM1" s="102"/>
+      <c r="HN1" s="102"/>
+      <c r="HO1" s="102"/>
+      <c r="HP1" s="102"/>
+      <c r="HQ1" s="102"/>
+      <c r="HR1" s="102"/>
+      <c r="HS1" s="102"/>
+      <c r="HT1" s="102"/>
+      <c r="HU1" s="102"/>
+      <c r="HV1" s="102"/>
+      <c r="HW1" s="102"/>
+      <c r="HX1" s="102"/>
+      <c r="HY1" s="102"/>
+      <c r="HZ1" s="102"/>
+      <c r="IA1" s="102"/>
+      <c r="IB1" s="102"/>
+      <c r="IC1" s="102"/>
+      <c r="ID1" s="102"/>
+      <c r="IE1" s="102"/>
+      <c r="IF1" s="102"/>
+      <c r="IG1" s="102"/>
+      <c r="IH1" s="102"/>
+      <c r="II1" s="102"/>
+      <c r="IJ1" s="102"/>
+      <c r="IK1" s="102"/>
+      <c r="IL1" s="102"/>
+      <c r="IM1" s="102"/>
+      <c r="IN1" s="102"/>
+      <c r="IO1" s="102"/>
+      <c r="IP1" s="102"/>
+      <c r="IQ1" s="102"/>
+      <c r="IR1" s="102"/>
+      <c r="IS1" s="102"/>
+      <c r="IT1" s="102"/>
+      <c r="IU1" s="102"/>
+      <c r="IV1" s="102"/>
+      <c r="IW1" s="102"/>
+    </row>
+    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
         <v>47</v>
       </c>
@@ -13565,8 +17551,257 @@
       <c r="H2" s="108" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
+      <c r="U2" s="127"/>
+      <c r="V2" s="127"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="127"/>
+      <c r="Y2" s="127"/>
+      <c r="Z2" s="127"/>
+      <c r="AA2" s="127"/>
+      <c r="AB2" s="127"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="127"/>
+      <c r="AE2" s="127"/>
+      <c r="AF2" s="127"/>
+      <c r="AG2" s="127"/>
+      <c r="AH2" s="127"/>
+      <c r="AI2" s="127"/>
+      <c r="AJ2" s="127"/>
+      <c r="AK2" s="127"/>
+      <c r="AL2" s="127"/>
+      <c r="AM2" s="127"/>
+      <c r="AN2" s="127"/>
+      <c r="AO2" s="127"/>
+      <c r="AP2" s="127"/>
+      <c r="AQ2" s="127"/>
+      <c r="AR2" s="127"/>
+      <c r="AS2" s="127"/>
+      <c r="AT2" s="127"/>
+      <c r="AU2" s="127"/>
+      <c r="AV2" s="127"/>
+      <c r="AW2" s="127"/>
+      <c r="AX2" s="127"/>
+      <c r="AY2" s="127"/>
+      <c r="AZ2" s="127"/>
+      <c r="BA2" s="127"/>
+      <c r="BB2" s="127"/>
+      <c r="BC2" s="127"/>
+      <c r="BD2" s="127"/>
+      <c r="BE2" s="127"/>
+      <c r="BF2" s="127"/>
+      <c r="BG2" s="127"/>
+      <c r="BH2" s="127"/>
+      <c r="BI2" s="127"/>
+      <c r="BJ2" s="127"/>
+      <c r="BK2" s="127"/>
+      <c r="BL2" s="127"/>
+      <c r="BM2" s="127"/>
+      <c r="BN2" s="127"/>
+      <c r="BO2" s="127"/>
+      <c r="BP2" s="127"/>
+      <c r="BQ2" s="127"/>
+      <c r="BR2" s="127"/>
+      <c r="BS2" s="127"/>
+      <c r="BT2" s="127"/>
+      <c r="BU2" s="127"/>
+      <c r="BV2" s="127"/>
+      <c r="BW2" s="127"/>
+      <c r="BX2" s="127"/>
+      <c r="BY2" s="127"/>
+      <c r="BZ2" s="127"/>
+      <c r="CA2" s="127"/>
+      <c r="CB2" s="127"/>
+      <c r="CC2" s="127"/>
+      <c r="CD2" s="127"/>
+      <c r="CE2" s="127"/>
+      <c r="CF2" s="127"/>
+      <c r="CG2" s="127"/>
+      <c r="CH2" s="127"/>
+      <c r="CI2" s="127"/>
+      <c r="CJ2" s="127"/>
+      <c r="CK2" s="127"/>
+      <c r="CL2" s="127"/>
+      <c r="CM2" s="127"/>
+      <c r="CN2" s="127"/>
+      <c r="CO2" s="127"/>
+      <c r="CP2" s="127"/>
+      <c r="CQ2" s="127"/>
+      <c r="CR2" s="127"/>
+      <c r="CS2" s="127"/>
+      <c r="CT2" s="127"/>
+      <c r="CU2" s="127"/>
+      <c r="CV2" s="127"/>
+      <c r="CW2" s="127"/>
+      <c r="CX2" s="127"/>
+      <c r="CY2" s="127"/>
+      <c r="CZ2" s="127"/>
+      <c r="DA2" s="127"/>
+      <c r="DB2" s="127"/>
+      <c r="DC2" s="127"/>
+      <c r="DD2" s="127"/>
+      <c r="DE2" s="127"/>
+      <c r="DF2" s="127"/>
+      <c r="DG2" s="127"/>
+      <c r="DH2" s="127"/>
+      <c r="DI2" s="127"/>
+      <c r="DJ2" s="127"/>
+      <c r="DK2" s="127"/>
+      <c r="DL2" s="127"/>
+      <c r="DM2" s="127"/>
+      <c r="DN2" s="127"/>
+      <c r="DO2" s="127"/>
+      <c r="DP2" s="127"/>
+      <c r="DQ2" s="127"/>
+      <c r="DR2" s="127"/>
+      <c r="DS2" s="127"/>
+      <c r="DT2" s="127"/>
+      <c r="DU2" s="127"/>
+      <c r="DV2" s="127"/>
+      <c r="DW2" s="127"/>
+      <c r="DX2" s="127"/>
+      <c r="DY2" s="127"/>
+      <c r="DZ2" s="127"/>
+      <c r="EA2" s="127"/>
+      <c r="EB2" s="127"/>
+      <c r="EC2" s="127"/>
+      <c r="ED2" s="127"/>
+      <c r="EE2" s="127"/>
+      <c r="EF2" s="127"/>
+      <c r="EG2" s="127"/>
+      <c r="EH2" s="127"/>
+      <c r="EI2" s="127"/>
+      <c r="EJ2" s="127"/>
+      <c r="EK2" s="127"/>
+      <c r="EL2" s="127"/>
+      <c r="EM2" s="127"/>
+      <c r="EN2" s="127"/>
+      <c r="EO2" s="127"/>
+      <c r="EP2" s="127"/>
+      <c r="EQ2" s="127"/>
+      <c r="ER2" s="127"/>
+      <c r="ES2" s="127"/>
+      <c r="ET2" s="127"/>
+      <c r="EU2" s="127"/>
+      <c r="EV2" s="127"/>
+      <c r="EW2" s="127"/>
+      <c r="EX2" s="127"/>
+      <c r="EY2" s="127"/>
+      <c r="EZ2" s="127"/>
+      <c r="FA2" s="127"/>
+      <c r="FB2" s="127"/>
+      <c r="FC2" s="127"/>
+      <c r="FD2" s="127"/>
+      <c r="FE2" s="127"/>
+      <c r="FF2" s="127"/>
+      <c r="FG2" s="127"/>
+      <c r="FH2" s="127"/>
+      <c r="FI2" s="127"/>
+      <c r="FJ2" s="127"/>
+      <c r="FK2" s="127"/>
+      <c r="FL2" s="127"/>
+      <c r="FM2" s="127"/>
+      <c r="FN2" s="127"/>
+      <c r="FO2" s="127"/>
+      <c r="FP2" s="127"/>
+      <c r="FQ2" s="127"/>
+      <c r="FR2" s="127"/>
+      <c r="FS2" s="127"/>
+      <c r="FT2" s="127"/>
+      <c r="FU2" s="127"/>
+      <c r="FV2" s="127"/>
+      <c r="FW2" s="127"/>
+      <c r="FX2" s="127"/>
+      <c r="FY2" s="127"/>
+      <c r="FZ2" s="127"/>
+      <c r="GA2" s="127"/>
+      <c r="GB2" s="127"/>
+      <c r="GC2" s="127"/>
+      <c r="GD2" s="127"/>
+      <c r="GE2" s="127"/>
+      <c r="GF2" s="127"/>
+      <c r="GG2" s="127"/>
+      <c r="GH2" s="127"/>
+      <c r="GI2" s="127"/>
+      <c r="GJ2" s="127"/>
+      <c r="GK2" s="127"/>
+      <c r="GL2" s="127"/>
+      <c r="GM2" s="127"/>
+      <c r="GN2" s="127"/>
+      <c r="GO2" s="127"/>
+      <c r="GP2" s="127"/>
+      <c r="GQ2" s="127"/>
+      <c r="GR2" s="127"/>
+      <c r="GS2" s="127"/>
+      <c r="GT2" s="127"/>
+      <c r="GU2" s="127"/>
+      <c r="GV2" s="127"/>
+      <c r="GW2" s="127"/>
+      <c r="GX2" s="127"/>
+      <c r="GY2" s="127"/>
+      <c r="GZ2" s="127"/>
+      <c r="HA2" s="127"/>
+      <c r="HB2" s="127"/>
+      <c r="HC2" s="127"/>
+      <c r="HD2" s="127"/>
+      <c r="HE2" s="127"/>
+      <c r="HF2" s="127"/>
+      <c r="HG2" s="127"/>
+      <c r="HH2" s="127"/>
+      <c r="HI2" s="127"/>
+      <c r="HJ2" s="127"/>
+      <c r="HK2" s="127"/>
+      <c r="HL2" s="127"/>
+      <c r="HM2" s="127"/>
+      <c r="HN2" s="127"/>
+      <c r="HO2" s="127"/>
+      <c r="HP2" s="127"/>
+      <c r="HQ2" s="127"/>
+      <c r="HR2" s="127"/>
+      <c r="HS2" s="127"/>
+      <c r="HT2" s="127"/>
+      <c r="HU2" s="127"/>
+      <c r="HV2" s="127"/>
+      <c r="HW2" s="127"/>
+      <c r="HX2" s="127"/>
+      <c r="HY2" s="127"/>
+      <c r="HZ2" s="127"/>
+      <c r="IA2" s="127"/>
+      <c r="IB2" s="127"/>
+      <c r="IC2" s="127"/>
+      <c r="ID2" s="127"/>
+      <c r="IE2" s="127"/>
+      <c r="IF2" s="127"/>
+      <c r="IG2" s="127"/>
+      <c r="IH2" s="127"/>
+      <c r="II2" s="127"/>
+      <c r="IJ2" s="127"/>
+      <c r="IK2" s="127"/>
+      <c r="IL2" s="127"/>
+      <c r="IM2" s="127"/>
+      <c r="IN2" s="127"/>
+      <c r="IO2" s="127"/>
+      <c r="IP2" s="127"/>
+      <c r="IQ2" s="127"/>
+      <c r="IR2" s="127"/>
+      <c r="IS2" s="127"/>
+      <c r="IT2" s="127"/>
+      <c r="IU2" s="127"/>
+      <c r="IV2" s="127"/>
+      <c r="IW2" s="127"/>
+    </row>
+    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="107"/>
       <c r="B3" s="107"/>
       <c r="C3" s="107"/>
@@ -13577,6 +17812,255 @@
         <v>52</v>
       </c>
       <c r="H3" s="108"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="128"/>
+      <c r="S3" s="128"/>
+      <c r="T3" s="128"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="128"/>
+      <c r="AB3" s="128"/>
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="128"/>
+      <c r="AF3" s="128"/>
+      <c r="AG3" s="128"/>
+      <c r="AH3" s="128"/>
+      <c r="AI3" s="128"/>
+      <c r="AJ3" s="128"/>
+      <c r="AK3" s="128"/>
+      <c r="AL3" s="128"/>
+      <c r="AM3" s="128"/>
+      <c r="AN3" s="128"/>
+      <c r="AO3" s="128"/>
+      <c r="AP3" s="128"/>
+      <c r="AQ3" s="128"/>
+      <c r="AR3" s="128"/>
+      <c r="AS3" s="128"/>
+      <c r="AT3" s="128"/>
+      <c r="AU3" s="128"/>
+      <c r="AV3" s="128"/>
+      <c r="AW3" s="128"/>
+      <c r="AX3" s="128"/>
+      <c r="AY3" s="128"/>
+      <c r="AZ3" s="128"/>
+      <c r="BA3" s="128"/>
+      <c r="BB3" s="128"/>
+      <c r="BC3" s="128"/>
+      <c r="BD3" s="128"/>
+      <c r="BE3" s="128"/>
+      <c r="BF3" s="128"/>
+      <c r="BG3" s="128"/>
+      <c r="BH3" s="128"/>
+      <c r="BI3" s="128"/>
+      <c r="BJ3" s="128"/>
+      <c r="BK3" s="128"/>
+      <c r="BL3" s="128"/>
+      <c r="BM3" s="128"/>
+      <c r="BN3" s="128"/>
+      <c r="BO3" s="128"/>
+      <c r="BP3" s="128"/>
+      <c r="BQ3" s="128"/>
+      <c r="BR3" s="128"/>
+      <c r="BS3" s="128"/>
+      <c r="BT3" s="128"/>
+      <c r="BU3" s="128"/>
+      <c r="BV3" s="128"/>
+      <c r="BW3" s="128"/>
+      <c r="BX3" s="128"/>
+      <c r="BY3" s="128"/>
+      <c r="BZ3" s="128"/>
+      <c r="CA3" s="128"/>
+      <c r="CB3" s="128"/>
+      <c r="CC3" s="128"/>
+      <c r="CD3" s="128"/>
+      <c r="CE3" s="128"/>
+      <c r="CF3" s="128"/>
+      <c r="CG3" s="128"/>
+      <c r="CH3" s="128"/>
+      <c r="CI3" s="128"/>
+      <c r="CJ3" s="128"/>
+      <c r="CK3" s="128"/>
+      <c r="CL3" s="128"/>
+      <c r="CM3" s="128"/>
+      <c r="CN3" s="128"/>
+      <c r="CO3" s="128"/>
+      <c r="CP3" s="128"/>
+      <c r="CQ3" s="128"/>
+      <c r="CR3" s="128"/>
+      <c r="CS3" s="128"/>
+      <c r="CT3" s="128"/>
+      <c r="CU3" s="128"/>
+      <c r="CV3" s="128"/>
+      <c r="CW3" s="128"/>
+      <c r="CX3" s="128"/>
+      <c r="CY3" s="128"/>
+      <c r="CZ3" s="128"/>
+      <c r="DA3" s="128"/>
+      <c r="DB3" s="128"/>
+      <c r="DC3" s="128"/>
+      <c r="DD3" s="128"/>
+      <c r="DE3" s="128"/>
+      <c r="DF3" s="128"/>
+      <c r="DG3" s="128"/>
+      <c r="DH3" s="128"/>
+      <c r="DI3" s="128"/>
+      <c r="DJ3" s="128"/>
+      <c r="DK3" s="128"/>
+      <c r="DL3" s="128"/>
+      <c r="DM3" s="128"/>
+      <c r="DN3" s="128"/>
+      <c r="DO3" s="128"/>
+      <c r="DP3" s="128"/>
+      <c r="DQ3" s="128"/>
+      <c r="DR3" s="128"/>
+      <c r="DS3" s="128"/>
+      <c r="DT3" s="128"/>
+      <c r="DU3" s="128"/>
+      <c r="DV3" s="128"/>
+      <c r="DW3" s="128"/>
+      <c r="DX3" s="128"/>
+      <c r="DY3" s="128"/>
+      <c r="DZ3" s="128"/>
+      <c r="EA3" s="128"/>
+      <c r="EB3" s="128"/>
+      <c r="EC3" s="128"/>
+      <c r="ED3" s="128"/>
+      <c r="EE3" s="128"/>
+      <c r="EF3" s="128"/>
+      <c r="EG3" s="128"/>
+      <c r="EH3" s="128"/>
+      <c r="EI3" s="128"/>
+      <c r="EJ3" s="128"/>
+      <c r="EK3" s="128"/>
+      <c r="EL3" s="128"/>
+      <c r="EM3" s="128"/>
+      <c r="EN3" s="128"/>
+      <c r="EO3" s="128"/>
+      <c r="EP3" s="128"/>
+      <c r="EQ3" s="128"/>
+      <c r="ER3" s="128"/>
+      <c r="ES3" s="128"/>
+      <c r="ET3" s="128"/>
+      <c r="EU3" s="128"/>
+      <c r="EV3" s="128"/>
+      <c r="EW3" s="128"/>
+      <c r="EX3" s="128"/>
+      <c r="EY3" s="128"/>
+      <c r="EZ3" s="128"/>
+      <c r="FA3" s="128"/>
+      <c r="FB3" s="128"/>
+      <c r="FC3" s="128"/>
+      <c r="FD3" s="128"/>
+      <c r="FE3" s="128"/>
+      <c r="FF3" s="128"/>
+      <c r="FG3" s="128"/>
+      <c r="FH3" s="128"/>
+      <c r="FI3" s="128"/>
+      <c r="FJ3" s="128"/>
+      <c r="FK3" s="128"/>
+      <c r="FL3" s="128"/>
+      <c r="FM3" s="128"/>
+      <c r="FN3" s="128"/>
+      <c r="FO3" s="128"/>
+      <c r="FP3" s="128"/>
+      <c r="FQ3" s="128"/>
+      <c r="FR3" s="128"/>
+      <c r="FS3" s="128"/>
+      <c r="FT3" s="128"/>
+      <c r="FU3" s="128"/>
+      <c r="FV3" s="128"/>
+      <c r="FW3" s="128"/>
+      <c r="FX3" s="128"/>
+      <c r="FY3" s="128"/>
+      <c r="FZ3" s="128"/>
+      <c r="GA3" s="128"/>
+      <c r="GB3" s="128"/>
+      <c r="GC3" s="128"/>
+      <c r="GD3" s="128"/>
+      <c r="GE3" s="128"/>
+      <c r="GF3" s="128"/>
+      <c r="GG3" s="128"/>
+      <c r="GH3" s="128"/>
+      <c r="GI3" s="128"/>
+      <c r="GJ3" s="128"/>
+      <c r="GK3" s="128"/>
+      <c r="GL3" s="128"/>
+      <c r="GM3" s="128"/>
+      <c r="GN3" s="128"/>
+      <c r="GO3" s="128"/>
+      <c r="GP3" s="128"/>
+      <c r="GQ3" s="128"/>
+      <c r="GR3" s="128"/>
+      <c r="GS3" s="128"/>
+      <c r="GT3" s="128"/>
+      <c r="GU3" s="128"/>
+      <c r="GV3" s="128"/>
+      <c r="GW3" s="128"/>
+      <c r="GX3" s="128"/>
+      <c r="GY3" s="128"/>
+      <c r="GZ3" s="128"/>
+      <c r="HA3" s="128"/>
+      <c r="HB3" s="128"/>
+      <c r="HC3" s="128"/>
+      <c r="HD3" s="128"/>
+      <c r="HE3" s="128"/>
+      <c r="HF3" s="128"/>
+      <c r="HG3" s="128"/>
+      <c r="HH3" s="128"/>
+      <c r="HI3" s="128"/>
+      <c r="HJ3" s="128"/>
+      <c r="HK3" s="128"/>
+      <c r="HL3" s="128"/>
+      <c r="HM3" s="128"/>
+      <c r="HN3" s="128"/>
+      <c r="HO3" s="128"/>
+      <c r="HP3" s="128"/>
+      <c r="HQ3" s="128"/>
+      <c r="HR3" s="128"/>
+      <c r="HS3" s="128"/>
+      <c r="HT3" s="128"/>
+      <c r="HU3" s="128"/>
+      <c r="HV3" s="128"/>
+      <c r="HW3" s="128"/>
+      <c r="HX3" s="128"/>
+      <c r="HY3" s="128"/>
+      <c r="HZ3" s="128"/>
+      <c r="IA3" s="128"/>
+      <c r="IB3" s="128"/>
+      <c r="IC3" s="128"/>
+      <c r="ID3" s="128"/>
+      <c r="IE3" s="128"/>
+      <c r="IF3" s="128"/>
+      <c r="IG3" s="128"/>
+      <c r="IH3" s="128"/>
+      <c r="II3" s="128"/>
+      <c r="IJ3" s="128"/>
+      <c r="IK3" s="128"/>
+      <c r="IL3" s="128"/>
+      <c r="IM3" s="128"/>
+      <c r="IN3" s="128"/>
+      <c r="IO3" s="128"/>
+      <c r="IP3" s="128"/>
+      <c r="IQ3" s="128"/>
+      <c r="IR3" s="128"/>
+      <c r="IS3" s="128"/>
+      <c r="IT3" s="128"/>
+      <c r="IU3" s="128"/>
+      <c r="IV3" s="128"/>
+      <c r="IW3" s="128"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="107"/>
@@ -13588,7 +18072,7 @@
       <c r="G4" s="108"/>
       <c r="H4" s="108"/>
     </row>
-    <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
         <v>46740</v>
       </c>
@@ -13599,6 +18083,7 @@
         <v>60</v>
       </c>
       <c r="D5" s="122"/>
+      <c r="E5" s="119"/>
       <c r="F5" s="130" t="n">
         <v>360</v>
       </c>
@@ -15796,8 +20281,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW201"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="118" width="8.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="119" width="19.66"/>
@@ -15810,7 +20295,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="9" style="119" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="103" t="s">
         <v>29</v>
       </c>
@@ -15832,8 +20317,257 @@
         <f aca="false">SUM(H5:H200)</f>
         <v>400</v>
       </c>
-    </row>
-    <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="102"/>
+      <c r="AG1" s="102"/>
+      <c r="AH1" s="102"/>
+      <c r="AI1" s="102"/>
+      <c r="AJ1" s="102"/>
+      <c r="AK1" s="102"/>
+      <c r="AL1" s="102"/>
+      <c r="AM1" s="102"/>
+      <c r="AN1" s="102"/>
+      <c r="AO1" s="102"/>
+      <c r="AP1" s="102"/>
+      <c r="AQ1" s="102"/>
+      <c r="AR1" s="102"/>
+      <c r="AS1" s="102"/>
+      <c r="AT1" s="102"/>
+      <c r="AU1" s="102"/>
+      <c r="AV1" s="102"/>
+      <c r="AW1" s="102"/>
+      <c r="AX1" s="102"/>
+      <c r="AY1" s="102"/>
+      <c r="AZ1" s="102"/>
+      <c r="BA1" s="102"/>
+      <c r="BB1" s="102"/>
+      <c r="BC1" s="102"/>
+      <c r="BD1" s="102"/>
+      <c r="BE1" s="102"/>
+      <c r="BF1" s="102"/>
+      <c r="BG1" s="102"/>
+      <c r="BH1" s="102"/>
+      <c r="BI1" s="102"/>
+      <c r="BJ1" s="102"/>
+      <c r="BK1" s="102"/>
+      <c r="BL1" s="102"/>
+      <c r="BM1" s="102"/>
+      <c r="BN1" s="102"/>
+      <c r="BO1" s="102"/>
+      <c r="BP1" s="102"/>
+      <c r="BQ1" s="102"/>
+      <c r="BR1" s="102"/>
+      <c r="BS1" s="102"/>
+      <c r="BT1" s="102"/>
+      <c r="BU1" s="102"/>
+      <c r="BV1" s="102"/>
+      <c r="BW1" s="102"/>
+      <c r="BX1" s="102"/>
+      <c r="BY1" s="102"/>
+      <c r="BZ1" s="102"/>
+      <c r="CA1" s="102"/>
+      <c r="CB1" s="102"/>
+      <c r="CC1" s="102"/>
+      <c r="CD1" s="102"/>
+      <c r="CE1" s="102"/>
+      <c r="CF1" s="102"/>
+      <c r="CG1" s="102"/>
+      <c r="CH1" s="102"/>
+      <c r="CI1" s="102"/>
+      <c r="CJ1" s="102"/>
+      <c r="CK1" s="102"/>
+      <c r="CL1" s="102"/>
+      <c r="CM1" s="102"/>
+      <c r="CN1" s="102"/>
+      <c r="CO1" s="102"/>
+      <c r="CP1" s="102"/>
+      <c r="CQ1" s="102"/>
+      <c r="CR1" s="102"/>
+      <c r="CS1" s="102"/>
+      <c r="CT1" s="102"/>
+      <c r="CU1" s="102"/>
+      <c r="CV1" s="102"/>
+      <c r="CW1" s="102"/>
+      <c r="CX1" s="102"/>
+      <c r="CY1" s="102"/>
+      <c r="CZ1" s="102"/>
+      <c r="DA1" s="102"/>
+      <c r="DB1" s="102"/>
+      <c r="DC1" s="102"/>
+      <c r="DD1" s="102"/>
+      <c r="DE1" s="102"/>
+      <c r="DF1" s="102"/>
+      <c r="DG1" s="102"/>
+      <c r="DH1" s="102"/>
+      <c r="DI1" s="102"/>
+      <c r="DJ1" s="102"/>
+      <c r="DK1" s="102"/>
+      <c r="DL1" s="102"/>
+      <c r="DM1" s="102"/>
+      <c r="DN1" s="102"/>
+      <c r="DO1" s="102"/>
+      <c r="DP1" s="102"/>
+      <c r="DQ1" s="102"/>
+      <c r="DR1" s="102"/>
+      <c r="DS1" s="102"/>
+      <c r="DT1" s="102"/>
+      <c r="DU1" s="102"/>
+      <c r="DV1" s="102"/>
+      <c r="DW1" s="102"/>
+      <c r="DX1" s="102"/>
+      <c r="DY1" s="102"/>
+      <c r="DZ1" s="102"/>
+      <c r="EA1" s="102"/>
+      <c r="EB1" s="102"/>
+      <c r="EC1" s="102"/>
+      <c r="ED1" s="102"/>
+      <c r="EE1" s="102"/>
+      <c r="EF1" s="102"/>
+      <c r="EG1" s="102"/>
+      <c r="EH1" s="102"/>
+      <c r="EI1" s="102"/>
+      <c r="EJ1" s="102"/>
+      <c r="EK1" s="102"/>
+      <c r="EL1" s="102"/>
+      <c r="EM1" s="102"/>
+      <c r="EN1" s="102"/>
+      <c r="EO1" s="102"/>
+      <c r="EP1" s="102"/>
+      <c r="EQ1" s="102"/>
+      <c r="ER1" s="102"/>
+      <c r="ES1" s="102"/>
+      <c r="ET1" s="102"/>
+      <c r="EU1" s="102"/>
+      <c r="EV1" s="102"/>
+      <c r="EW1" s="102"/>
+      <c r="EX1" s="102"/>
+      <c r="EY1" s="102"/>
+      <c r="EZ1" s="102"/>
+      <c r="FA1" s="102"/>
+      <c r="FB1" s="102"/>
+      <c r="FC1" s="102"/>
+      <c r="FD1" s="102"/>
+      <c r="FE1" s="102"/>
+      <c r="FF1" s="102"/>
+      <c r="FG1" s="102"/>
+      <c r="FH1" s="102"/>
+      <c r="FI1" s="102"/>
+      <c r="FJ1" s="102"/>
+      <c r="FK1" s="102"/>
+      <c r="FL1" s="102"/>
+      <c r="FM1" s="102"/>
+      <c r="FN1" s="102"/>
+      <c r="FO1" s="102"/>
+      <c r="FP1" s="102"/>
+      <c r="FQ1" s="102"/>
+      <c r="FR1" s="102"/>
+      <c r="FS1" s="102"/>
+      <c r="FT1" s="102"/>
+      <c r="FU1" s="102"/>
+      <c r="FV1" s="102"/>
+      <c r="FW1" s="102"/>
+      <c r="FX1" s="102"/>
+      <c r="FY1" s="102"/>
+      <c r="FZ1" s="102"/>
+      <c r="GA1" s="102"/>
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="102"/>
+      <c r="HF1" s="102"/>
+      <c r="HG1" s="102"/>
+      <c r="HH1" s="102"/>
+      <c r="HI1" s="102"/>
+      <c r="HJ1" s="102"/>
+      <c r="HK1" s="102"/>
+      <c r="HL1" s="102"/>
+      <c r="HM1" s="102"/>
+      <c r="HN1" s="102"/>
+      <c r="HO1" s="102"/>
+      <c r="HP1" s="102"/>
+      <c r="HQ1" s="102"/>
+      <c r="HR1" s="102"/>
+      <c r="HS1" s="102"/>
+      <c r="HT1" s="102"/>
+      <c r="HU1" s="102"/>
+      <c r="HV1" s="102"/>
+      <c r="HW1" s="102"/>
+      <c r="HX1" s="102"/>
+      <c r="HY1" s="102"/>
+      <c r="HZ1" s="102"/>
+      <c r="IA1" s="102"/>
+      <c r="IB1" s="102"/>
+      <c r="IC1" s="102"/>
+      <c r="ID1" s="102"/>
+      <c r="IE1" s="102"/>
+      <c r="IF1" s="102"/>
+      <c r="IG1" s="102"/>
+      <c r="IH1" s="102"/>
+      <c r="II1" s="102"/>
+      <c r="IJ1" s="102"/>
+      <c r="IK1" s="102"/>
+      <c r="IL1" s="102"/>
+      <c r="IM1" s="102"/>
+      <c r="IN1" s="102"/>
+      <c r="IO1" s="102"/>
+      <c r="IP1" s="102"/>
+      <c r="IQ1" s="102"/>
+      <c r="IR1" s="102"/>
+      <c r="IS1" s="102"/>
+      <c r="IT1" s="102"/>
+      <c r="IU1" s="102"/>
+      <c r="IV1" s="102"/>
+      <c r="IW1" s="102"/>
+    </row>
+    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
         <v>47</v>
       </c>
@@ -15858,8 +20592,257 @@
       <c r="H2" s="108" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
+      <c r="U2" s="127"/>
+      <c r="V2" s="127"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="127"/>
+      <c r="Y2" s="127"/>
+      <c r="Z2" s="127"/>
+      <c r="AA2" s="127"/>
+      <c r="AB2" s="127"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="127"/>
+      <c r="AE2" s="127"/>
+      <c r="AF2" s="127"/>
+      <c r="AG2" s="127"/>
+      <c r="AH2" s="127"/>
+      <c r="AI2" s="127"/>
+      <c r="AJ2" s="127"/>
+      <c r="AK2" s="127"/>
+      <c r="AL2" s="127"/>
+      <c r="AM2" s="127"/>
+      <c r="AN2" s="127"/>
+      <c r="AO2" s="127"/>
+      <c r="AP2" s="127"/>
+      <c r="AQ2" s="127"/>
+      <c r="AR2" s="127"/>
+      <c r="AS2" s="127"/>
+      <c r="AT2" s="127"/>
+      <c r="AU2" s="127"/>
+      <c r="AV2" s="127"/>
+      <c r="AW2" s="127"/>
+      <c r="AX2" s="127"/>
+      <c r="AY2" s="127"/>
+      <c r="AZ2" s="127"/>
+      <c r="BA2" s="127"/>
+      <c r="BB2" s="127"/>
+      <c r="BC2" s="127"/>
+      <c r="BD2" s="127"/>
+      <c r="BE2" s="127"/>
+      <c r="BF2" s="127"/>
+      <c r="BG2" s="127"/>
+      <c r="BH2" s="127"/>
+      <c r="BI2" s="127"/>
+      <c r="BJ2" s="127"/>
+      <c r="BK2" s="127"/>
+      <c r="BL2" s="127"/>
+      <c r="BM2" s="127"/>
+      <c r="BN2" s="127"/>
+      <c r="BO2" s="127"/>
+      <c r="BP2" s="127"/>
+      <c r="BQ2" s="127"/>
+      <c r="BR2" s="127"/>
+      <c r="BS2" s="127"/>
+      <c r="BT2" s="127"/>
+      <c r="BU2" s="127"/>
+      <c r="BV2" s="127"/>
+      <c r="BW2" s="127"/>
+      <c r="BX2" s="127"/>
+      <c r="BY2" s="127"/>
+      <c r="BZ2" s="127"/>
+      <c r="CA2" s="127"/>
+      <c r="CB2" s="127"/>
+      <c r="CC2" s="127"/>
+      <c r="CD2" s="127"/>
+      <c r="CE2" s="127"/>
+      <c r="CF2" s="127"/>
+      <c r="CG2" s="127"/>
+      <c r="CH2" s="127"/>
+      <c r="CI2" s="127"/>
+      <c r="CJ2" s="127"/>
+      <c r="CK2" s="127"/>
+      <c r="CL2" s="127"/>
+      <c r="CM2" s="127"/>
+      <c r="CN2" s="127"/>
+      <c r="CO2" s="127"/>
+      <c r="CP2" s="127"/>
+      <c r="CQ2" s="127"/>
+      <c r="CR2" s="127"/>
+      <c r="CS2" s="127"/>
+      <c r="CT2" s="127"/>
+      <c r="CU2" s="127"/>
+      <c r="CV2" s="127"/>
+      <c r="CW2" s="127"/>
+      <c r="CX2" s="127"/>
+      <c r="CY2" s="127"/>
+      <c r="CZ2" s="127"/>
+      <c r="DA2" s="127"/>
+      <c r="DB2" s="127"/>
+      <c r="DC2" s="127"/>
+      <c r="DD2" s="127"/>
+      <c r="DE2" s="127"/>
+      <c r="DF2" s="127"/>
+      <c r="DG2" s="127"/>
+      <c r="DH2" s="127"/>
+      <c r="DI2" s="127"/>
+      <c r="DJ2" s="127"/>
+      <c r="DK2" s="127"/>
+      <c r="DL2" s="127"/>
+      <c r="DM2" s="127"/>
+      <c r="DN2" s="127"/>
+      <c r="DO2" s="127"/>
+      <c r="DP2" s="127"/>
+      <c r="DQ2" s="127"/>
+      <c r="DR2" s="127"/>
+      <c r="DS2" s="127"/>
+      <c r="DT2" s="127"/>
+      <c r="DU2" s="127"/>
+      <c r="DV2" s="127"/>
+      <c r="DW2" s="127"/>
+      <c r="DX2" s="127"/>
+      <c r="DY2" s="127"/>
+      <c r="DZ2" s="127"/>
+      <c r="EA2" s="127"/>
+      <c r="EB2" s="127"/>
+      <c r="EC2" s="127"/>
+      <c r="ED2" s="127"/>
+      <c r="EE2" s="127"/>
+      <c r="EF2" s="127"/>
+      <c r="EG2" s="127"/>
+      <c r="EH2" s="127"/>
+      <c r="EI2" s="127"/>
+      <c r="EJ2" s="127"/>
+      <c r="EK2" s="127"/>
+      <c r="EL2" s="127"/>
+      <c r="EM2" s="127"/>
+      <c r="EN2" s="127"/>
+      <c r="EO2" s="127"/>
+      <c r="EP2" s="127"/>
+      <c r="EQ2" s="127"/>
+      <c r="ER2" s="127"/>
+      <c r="ES2" s="127"/>
+      <c r="ET2" s="127"/>
+      <c r="EU2" s="127"/>
+      <c r="EV2" s="127"/>
+      <c r="EW2" s="127"/>
+      <c r="EX2" s="127"/>
+      <c r="EY2" s="127"/>
+      <c r="EZ2" s="127"/>
+      <c r="FA2" s="127"/>
+      <c r="FB2" s="127"/>
+      <c r="FC2" s="127"/>
+      <c r="FD2" s="127"/>
+      <c r="FE2" s="127"/>
+      <c r="FF2" s="127"/>
+      <c r="FG2" s="127"/>
+      <c r="FH2" s="127"/>
+      <c r="FI2" s="127"/>
+      <c r="FJ2" s="127"/>
+      <c r="FK2" s="127"/>
+      <c r="FL2" s="127"/>
+      <c r="FM2" s="127"/>
+      <c r="FN2" s="127"/>
+      <c r="FO2" s="127"/>
+      <c r="FP2" s="127"/>
+      <c r="FQ2" s="127"/>
+      <c r="FR2" s="127"/>
+      <c r="FS2" s="127"/>
+      <c r="FT2" s="127"/>
+      <c r="FU2" s="127"/>
+      <c r="FV2" s="127"/>
+      <c r="FW2" s="127"/>
+      <c r="FX2" s="127"/>
+      <c r="FY2" s="127"/>
+      <c r="FZ2" s="127"/>
+      <c r="GA2" s="127"/>
+      <c r="GB2" s="127"/>
+      <c r="GC2" s="127"/>
+      <c r="GD2" s="127"/>
+      <c r="GE2" s="127"/>
+      <c r="GF2" s="127"/>
+      <c r="GG2" s="127"/>
+      <c r="GH2" s="127"/>
+      <c r="GI2" s="127"/>
+      <c r="GJ2" s="127"/>
+      <c r="GK2" s="127"/>
+      <c r="GL2" s="127"/>
+      <c r="GM2" s="127"/>
+      <c r="GN2" s="127"/>
+      <c r="GO2" s="127"/>
+      <c r="GP2" s="127"/>
+      <c r="GQ2" s="127"/>
+      <c r="GR2" s="127"/>
+      <c r="GS2" s="127"/>
+      <c r="GT2" s="127"/>
+      <c r="GU2" s="127"/>
+      <c r="GV2" s="127"/>
+      <c r="GW2" s="127"/>
+      <c r="GX2" s="127"/>
+      <c r="GY2" s="127"/>
+      <c r="GZ2" s="127"/>
+      <c r="HA2" s="127"/>
+      <c r="HB2" s="127"/>
+      <c r="HC2" s="127"/>
+      <c r="HD2" s="127"/>
+      <c r="HE2" s="127"/>
+      <c r="HF2" s="127"/>
+      <c r="HG2" s="127"/>
+      <c r="HH2" s="127"/>
+      <c r="HI2" s="127"/>
+      <c r="HJ2" s="127"/>
+      <c r="HK2" s="127"/>
+      <c r="HL2" s="127"/>
+      <c r="HM2" s="127"/>
+      <c r="HN2" s="127"/>
+      <c r="HO2" s="127"/>
+      <c r="HP2" s="127"/>
+      <c r="HQ2" s="127"/>
+      <c r="HR2" s="127"/>
+      <c r="HS2" s="127"/>
+      <c r="HT2" s="127"/>
+      <c r="HU2" s="127"/>
+      <c r="HV2" s="127"/>
+      <c r="HW2" s="127"/>
+      <c r="HX2" s="127"/>
+      <c r="HY2" s="127"/>
+      <c r="HZ2" s="127"/>
+      <c r="IA2" s="127"/>
+      <c r="IB2" s="127"/>
+      <c r="IC2" s="127"/>
+      <c r="ID2" s="127"/>
+      <c r="IE2" s="127"/>
+      <c r="IF2" s="127"/>
+      <c r="IG2" s="127"/>
+      <c r="IH2" s="127"/>
+      <c r="II2" s="127"/>
+      <c r="IJ2" s="127"/>
+      <c r="IK2" s="127"/>
+      <c r="IL2" s="127"/>
+      <c r="IM2" s="127"/>
+      <c r="IN2" s="127"/>
+      <c r="IO2" s="127"/>
+      <c r="IP2" s="127"/>
+      <c r="IQ2" s="127"/>
+      <c r="IR2" s="127"/>
+      <c r="IS2" s="127"/>
+      <c r="IT2" s="127"/>
+      <c r="IU2" s="127"/>
+      <c r="IV2" s="127"/>
+      <c r="IW2" s="127"/>
+    </row>
+    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="107"/>
       <c r="B3" s="107"/>
       <c r="C3" s="107"/>
@@ -15870,6 +20853,255 @@
         <v>52</v>
       </c>
       <c r="H3" s="108"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="128"/>
+      <c r="S3" s="128"/>
+      <c r="T3" s="128"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="128"/>
+      <c r="AB3" s="128"/>
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="128"/>
+      <c r="AF3" s="128"/>
+      <c r="AG3" s="128"/>
+      <c r="AH3" s="128"/>
+      <c r="AI3" s="128"/>
+      <c r="AJ3" s="128"/>
+      <c r="AK3" s="128"/>
+      <c r="AL3" s="128"/>
+      <c r="AM3" s="128"/>
+      <c r="AN3" s="128"/>
+      <c r="AO3" s="128"/>
+      <c r="AP3" s="128"/>
+      <c r="AQ3" s="128"/>
+      <c r="AR3" s="128"/>
+      <c r="AS3" s="128"/>
+      <c r="AT3" s="128"/>
+      <c r="AU3" s="128"/>
+      <c r="AV3" s="128"/>
+      <c r="AW3" s="128"/>
+      <c r="AX3" s="128"/>
+      <c r="AY3" s="128"/>
+      <c r="AZ3" s="128"/>
+      <c r="BA3" s="128"/>
+      <c r="BB3" s="128"/>
+      <c r="BC3" s="128"/>
+      <c r="BD3" s="128"/>
+      <c r="BE3" s="128"/>
+      <c r="BF3" s="128"/>
+      <c r="BG3" s="128"/>
+      <c r="BH3" s="128"/>
+      <c r="BI3" s="128"/>
+      <c r="BJ3" s="128"/>
+      <c r="BK3" s="128"/>
+      <c r="BL3" s="128"/>
+      <c r="BM3" s="128"/>
+      <c r="BN3" s="128"/>
+      <c r="BO3" s="128"/>
+      <c r="BP3" s="128"/>
+      <c r="BQ3" s="128"/>
+      <c r="BR3" s="128"/>
+      <c r="BS3" s="128"/>
+      <c r="BT3" s="128"/>
+      <c r="BU3" s="128"/>
+      <c r="BV3" s="128"/>
+      <c r="BW3" s="128"/>
+      <c r="BX3" s="128"/>
+      <c r="BY3" s="128"/>
+      <c r="BZ3" s="128"/>
+      <c r="CA3" s="128"/>
+      <c r="CB3" s="128"/>
+      <c r="CC3" s="128"/>
+      <c r="CD3" s="128"/>
+      <c r="CE3" s="128"/>
+      <c r="CF3" s="128"/>
+      <c r="CG3" s="128"/>
+      <c r="CH3" s="128"/>
+      <c r="CI3" s="128"/>
+      <c r="CJ3" s="128"/>
+      <c r="CK3" s="128"/>
+      <c r="CL3" s="128"/>
+      <c r="CM3" s="128"/>
+      <c r="CN3" s="128"/>
+      <c r="CO3" s="128"/>
+      <c r="CP3" s="128"/>
+      <c r="CQ3" s="128"/>
+      <c r="CR3" s="128"/>
+      <c r="CS3" s="128"/>
+      <c r="CT3" s="128"/>
+      <c r="CU3" s="128"/>
+      <c r="CV3" s="128"/>
+      <c r="CW3" s="128"/>
+      <c r="CX3" s="128"/>
+      <c r="CY3" s="128"/>
+      <c r="CZ3" s="128"/>
+      <c r="DA3" s="128"/>
+      <c r="DB3" s="128"/>
+      <c r="DC3" s="128"/>
+      <c r="DD3" s="128"/>
+      <c r="DE3" s="128"/>
+      <c r="DF3" s="128"/>
+      <c r="DG3" s="128"/>
+      <c r="DH3" s="128"/>
+      <c r="DI3" s="128"/>
+      <c r="DJ3" s="128"/>
+      <c r="DK3" s="128"/>
+      <c r="DL3" s="128"/>
+      <c r="DM3" s="128"/>
+      <c r="DN3" s="128"/>
+      <c r="DO3" s="128"/>
+      <c r="DP3" s="128"/>
+      <c r="DQ3" s="128"/>
+      <c r="DR3" s="128"/>
+      <c r="DS3" s="128"/>
+      <c r="DT3" s="128"/>
+      <c r="DU3" s="128"/>
+      <c r="DV3" s="128"/>
+      <c r="DW3" s="128"/>
+      <c r="DX3" s="128"/>
+      <c r="DY3" s="128"/>
+      <c r="DZ3" s="128"/>
+      <c r="EA3" s="128"/>
+      <c r="EB3" s="128"/>
+      <c r="EC3" s="128"/>
+      <c r="ED3" s="128"/>
+      <c r="EE3" s="128"/>
+      <c r="EF3" s="128"/>
+      <c r="EG3" s="128"/>
+      <c r="EH3" s="128"/>
+      <c r="EI3" s="128"/>
+      <c r="EJ3" s="128"/>
+      <c r="EK3" s="128"/>
+      <c r="EL3" s="128"/>
+      <c r="EM3" s="128"/>
+      <c r="EN3" s="128"/>
+      <c r="EO3" s="128"/>
+      <c r="EP3" s="128"/>
+      <c r="EQ3" s="128"/>
+      <c r="ER3" s="128"/>
+      <c r="ES3" s="128"/>
+      <c r="ET3" s="128"/>
+      <c r="EU3" s="128"/>
+      <c r="EV3" s="128"/>
+      <c r="EW3" s="128"/>
+      <c r="EX3" s="128"/>
+      <c r="EY3" s="128"/>
+      <c r="EZ3" s="128"/>
+      <c r="FA3" s="128"/>
+      <c r="FB3" s="128"/>
+      <c r="FC3" s="128"/>
+      <c r="FD3" s="128"/>
+      <c r="FE3" s="128"/>
+      <c r="FF3" s="128"/>
+      <c r="FG3" s="128"/>
+      <c r="FH3" s="128"/>
+      <c r="FI3" s="128"/>
+      <c r="FJ3" s="128"/>
+      <c r="FK3" s="128"/>
+      <c r="FL3" s="128"/>
+      <c r="FM3" s="128"/>
+      <c r="FN3" s="128"/>
+      <c r="FO3" s="128"/>
+      <c r="FP3" s="128"/>
+      <c r="FQ3" s="128"/>
+      <c r="FR3" s="128"/>
+      <c r="FS3" s="128"/>
+      <c r="FT3" s="128"/>
+      <c r="FU3" s="128"/>
+      <c r="FV3" s="128"/>
+      <c r="FW3" s="128"/>
+      <c r="FX3" s="128"/>
+      <c r="FY3" s="128"/>
+      <c r="FZ3" s="128"/>
+      <c r="GA3" s="128"/>
+      <c r="GB3" s="128"/>
+      <c r="GC3" s="128"/>
+      <c r="GD3" s="128"/>
+      <c r="GE3" s="128"/>
+      <c r="GF3" s="128"/>
+      <c r="GG3" s="128"/>
+      <c r="GH3" s="128"/>
+      <c r="GI3" s="128"/>
+      <c r="GJ3" s="128"/>
+      <c r="GK3" s="128"/>
+      <c r="GL3" s="128"/>
+      <c r="GM3" s="128"/>
+      <c r="GN3" s="128"/>
+      <c r="GO3" s="128"/>
+      <c r="GP3" s="128"/>
+      <c r="GQ3" s="128"/>
+      <c r="GR3" s="128"/>
+      <c r="GS3" s="128"/>
+      <c r="GT3" s="128"/>
+      <c r="GU3" s="128"/>
+      <c r="GV3" s="128"/>
+      <c r="GW3" s="128"/>
+      <c r="GX3" s="128"/>
+      <c r="GY3" s="128"/>
+      <c r="GZ3" s="128"/>
+      <c r="HA3" s="128"/>
+      <c r="HB3" s="128"/>
+      <c r="HC3" s="128"/>
+      <c r="HD3" s="128"/>
+      <c r="HE3" s="128"/>
+      <c r="HF3" s="128"/>
+      <c r="HG3" s="128"/>
+      <c r="HH3" s="128"/>
+      <c r="HI3" s="128"/>
+      <c r="HJ3" s="128"/>
+      <c r="HK3" s="128"/>
+      <c r="HL3" s="128"/>
+      <c r="HM3" s="128"/>
+      <c r="HN3" s="128"/>
+      <c r="HO3" s="128"/>
+      <c r="HP3" s="128"/>
+      <c r="HQ3" s="128"/>
+      <c r="HR3" s="128"/>
+      <c r="HS3" s="128"/>
+      <c r="HT3" s="128"/>
+      <c r="HU3" s="128"/>
+      <c r="HV3" s="128"/>
+      <c r="HW3" s="128"/>
+      <c r="HX3" s="128"/>
+      <c r="HY3" s="128"/>
+      <c r="HZ3" s="128"/>
+      <c r="IA3" s="128"/>
+      <c r="IB3" s="128"/>
+      <c r="IC3" s="128"/>
+      <c r="ID3" s="128"/>
+      <c r="IE3" s="128"/>
+      <c r="IF3" s="128"/>
+      <c r="IG3" s="128"/>
+      <c r="IH3" s="128"/>
+      <c r="II3" s="128"/>
+      <c r="IJ3" s="128"/>
+      <c r="IK3" s="128"/>
+      <c r="IL3" s="128"/>
+      <c r="IM3" s="128"/>
+      <c r="IN3" s="128"/>
+      <c r="IO3" s="128"/>
+      <c r="IP3" s="128"/>
+      <c r="IQ3" s="128"/>
+      <c r="IR3" s="128"/>
+      <c r="IS3" s="128"/>
+      <c r="IT3" s="128"/>
+      <c r="IU3" s="128"/>
+      <c r="IV3" s="128"/>
+      <c r="IW3" s="128"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="107"/>
@@ -15881,7 +21113,7 @@
       <c r="G4" s="108"/>
       <c r="H4" s="108"/>
     </row>
-    <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
         <v>46768</v>
       </c>
@@ -15892,6 +21124,7 @@
         <v>61</v>
       </c>
       <c r="D5" s="122"/>
+      <c r="E5" s="119"/>
       <c r="F5" s="130" t="n">
         <v>480</v>
       </c>
@@ -18090,7 +23323,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.66"/>
@@ -18657,7 +23890,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.66"/>
@@ -19224,7 +24457,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.66"/>
@@ -19791,7 +25024,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.66"/>
@@ -20357,8 +25590,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW21"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="63" width="1.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="64" width="24.82"/>
@@ -20385,7 +25618,7 @@
       <c r="M1" s="71"/>
       <c r="N1" s="72"/>
     </row>
-    <row r="2" s="80" customFormat="true" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="73"/>
       <c r="B2" s="74" t="s">
         <v>18</v>
@@ -20422,8 +25655,251 @@
         <v>28</v>
       </c>
       <c r="N2" s="79"/>
-    </row>
-    <row r="3" s="80" customFormat="true" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="80"/>
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="80"/>
+      <c r="AD2" s="80"/>
+      <c r="AE2" s="80"/>
+      <c r="AF2" s="80"/>
+      <c r="AG2" s="80"/>
+      <c r="AH2" s="80"/>
+      <c r="AI2" s="80"/>
+      <c r="AJ2" s="80"/>
+      <c r="AK2" s="80"/>
+      <c r="AL2" s="80"/>
+      <c r="AM2" s="80"/>
+      <c r="AN2" s="80"/>
+      <c r="AO2" s="80"/>
+      <c r="AP2" s="80"/>
+      <c r="AQ2" s="80"/>
+      <c r="AR2" s="80"/>
+      <c r="AS2" s="80"/>
+      <c r="AT2" s="80"/>
+      <c r="AU2" s="80"/>
+      <c r="AV2" s="80"/>
+      <c r="AW2" s="80"/>
+      <c r="AX2" s="80"/>
+      <c r="AY2" s="80"/>
+      <c r="AZ2" s="80"/>
+      <c r="BA2" s="80"/>
+      <c r="BB2" s="80"/>
+      <c r="BC2" s="80"/>
+      <c r="BD2" s="80"/>
+      <c r="BE2" s="80"/>
+      <c r="BF2" s="80"/>
+      <c r="BG2" s="80"/>
+      <c r="BH2" s="80"/>
+      <c r="BI2" s="80"/>
+      <c r="BJ2" s="80"/>
+      <c r="BK2" s="80"/>
+      <c r="BL2" s="80"/>
+      <c r="BM2" s="80"/>
+      <c r="BN2" s="80"/>
+      <c r="BO2" s="80"/>
+      <c r="BP2" s="80"/>
+      <c r="BQ2" s="80"/>
+      <c r="BR2" s="80"/>
+      <c r="BS2" s="80"/>
+      <c r="BT2" s="80"/>
+      <c r="BU2" s="80"/>
+      <c r="BV2" s="80"/>
+      <c r="BW2" s="80"/>
+      <c r="BX2" s="80"/>
+      <c r="BY2" s="80"/>
+      <c r="BZ2" s="80"/>
+      <c r="CA2" s="80"/>
+      <c r="CB2" s="80"/>
+      <c r="CC2" s="80"/>
+      <c r="CD2" s="80"/>
+      <c r="CE2" s="80"/>
+      <c r="CF2" s="80"/>
+      <c r="CG2" s="80"/>
+      <c r="CH2" s="80"/>
+      <c r="CI2" s="80"/>
+      <c r="CJ2" s="80"/>
+      <c r="CK2" s="80"/>
+      <c r="CL2" s="80"/>
+      <c r="CM2" s="80"/>
+      <c r="CN2" s="80"/>
+      <c r="CO2" s="80"/>
+      <c r="CP2" s="80"/>
+      <c r="CQ2" s="80"/>
+      <c r="CR2" s="80"/>
+      <c r="CS2" s="80"/>
+      <c r="CT2" s="80"/>
+      <c r="CU2" s="80"/>
+      <c r="CV2" s="80"/>
+      <c r="CW2" s="80"/>
+      <c r="CX2" s="80"/>
+      <c r="CY2" s="80"/>
+      <c r="CZ2" s="80"/>
+      <c r="DA2" s="80"/>
+      <c r="DB2" s="80"/>
+      <c r="DC2" s="80"/>
+      <c r="DD2" s="80"/>
+      <c r="DE2" s="80"/>
+      <c r="DF2" s="80"/>
+      <c r="DG2" s="80"/>
+      <c r="DH2" s="80"/>
+      <c r="DI2" s="80"/>
+      <c r="DJ2" s="80"/>
+      <c r="DK2" s="80"/>
+      <c r="DL2" s="80"/>
+      <c r="DM2" s="80"/>
+      <c r="DN2" s="80"/>
+      <c r="DO2" s="80"/>
+      <c r="DP2" s="80"/>
+      <c r="DQ2" s="80"/>
+      <c r="DR2" s="80"/>
+      <c r="DS2" s="80"/>
+      <c r="DT2" s="80"/>
+      <c r="DU2" s="80"/>
+      <c r="DV2" s="80"/>
+      <c r="DW2" s="80"/>
+      <c r="DX2" s="80"/>
+      <c r="DY2" s="80"/>
+      <c r="DZ2" s="80"/>
+      <c r="EA2" s="80"/>
+      <c r="EB2" s="80"/>
+      <c r="EC2" s="80"/>
+      <c r="ED2" s="80"/>
+      <c r="EE2" s="80"/>
+      <c r="EF2" s="80"/>
+      <c r="EG2" s="80"/>
+      <c r="EH2" s="80"/>
+      <c r="EI2" s="80"/>
+      <c r="EJ2" s="80"/>
+      <c r="EK2" s="80"/>
+      <c r="EL2" s="80"/>
+      <c r="EM2" s="80"/>
+      <c r="EN2" s="80"/>
+      <c r="EO2" s="80"/>
+      <c r="EP2" s="80"/>
+      <c r="EQ2" s="80"/>
+      <c r="ER2" s="80"/>
+      <c r="ES2" s="80"/>
+      <c r="ET2" s="80"/>
+      <c r="EU2" s="80"/>
+      <c r="EV2" s="80"/>
+      <c r="EW2" s="80"/>
+      <c r="EX2" s="80"/>
+      <c r="EY2" s="80"/>
+      <c r="EZ2" s="80"/>
+      <c r="FA2" s="80"/>
+      <c r="FB2" s="80"/>
+      <c r="FC2" s="80"/>
+      <c r="FD2" s="80"/>
+      <c r="FE2" s="80"/>
+      <c r="FF2" s="80"/>
+      <c r="FG2" s="80"/>
+      <c r="FH2" s="80"/>
+      <c r="FI2" s="80"/>
+      <c r="FJ2" s="80"/>
+      <c r="FK2" s="80"/>
+      <c r="FL2" s="80"/>
+      <c r="FM2" s="80"/>
+      <c r="FN2" s="80"/>
+      <c r="FO2" s="80"/>
+      <c r="FP2" s="80"/>
+      <c r="FQ2" s="80"/>
+      <c r="FR2" s="80"/>
+      <c r="FS2" s="80"/>
+      <c r="FT2" s="80"/>
+      <c r="FU2" s="80"/>
+      <c r="FV2" s="80"/>
+      <c r="FW2" s="80"/>
+      <c r="FX2" s="80"/>
+      <c r="FY2" s="80"/>
+      <c r="FZ2" s="80"/>
+      <c r="GA2" s="80"/>
+      <c r="GB2" s="80"/>
+      <c r="GC2" s="80"/>
+      <c r="GD2" s="80"/>
+      <c r="GE2" s="80"/>
+      <c r="GF2" s="80"/>
+      <c r="GG2" s="80"/>
+      <c r="GH2" s="80"/>
+      <c r="GI2" s="80"/>
+      <c r="GJ2" s="80"/>
+      <c r="GK2" s="80"/>
+      <c r="GL2" s="80"/>
+      <c r="GM2" s="80"/>
+      <c r="GN2" s="80"/>
+      <c r="GO2" s="80"/>
+      <c r="GP2" s="80"/>
+      <c r="GQ2" s="80"/>
+      <c r="GR2" s="80"/>
+      <c r="GS2" s="80"/>
+      <c r="GT2" s="80"/>
+      <c r="GU2" s="80"/>
+      <c r="GV2" s="80"/>
+      <c r="GW2" s="80"/>
+      <c r="GX2" s="80"/>
+      <c r="GY2" s="80"/>
+      <c r="GZ2" s="80"/>
+      <c r="HA2" s="80"/>
+      <c r="HB2" s="80"/>
+      <c r="HC2" s="80"/>
+      <c r="HD2" s="80"/>
+      <c r="HE2" s="80"/>
+      <c r="HF2" s="80"/>
+      <c r="HG2" s="80"/>
+      <c r="HH2" s="80"/>
+      <c r="HI2" s="80"/>
+      <c r="HJ2" s="80"/>
+      <c r="HK2" s="80"/>
+      <c r="HL2" s="80"/>
+      <c r="HM2" s="80"/>
+      <c r="HN2" s="80"/>
+      <c r="HO2" s="80"/>
+      <c r="HP2" s="80"/>
+      <c r="HQ2" s="80"/>
+      <c r="HR2" s="80"/>
+      <c r="HS2" s="80"/>
+      <c r="HT2" s="80"/>
+      <c r="HU2" s="80"/>
+      <c r="HV2" s="80"/>
+      <c r="HW2" s="80"/>
+      <c r="HX2" s="80"/>
+      <c r="HY2" s="80"/>
+      <c r="HZ2" s="80"/>
+      <c r="IA2" s="80"/>
+      <c r="IB2" s="80"/>
+      <c r="IC2" s="80"/>
+      <c r="ID2" s="80"/>
+      <c r="IE2" s="80"/>
+      <c r="IF2" s="80"/>
+      <c r="IG2" s="80"/>
+      <c r="IH2" s="80"/>
+      <c r="II2" s="80"/>
+      <c r="IJ2" s="80"/>
+      <c r="IK2" s="80"/>
+      <c r="IL2" s="80"/>
+      <c r="IM2" s="80"/>
+      <c r="IN2" s="80"/>
+      <c r="IO2" s="80"/>
+      <c r="IP2" s="80"/>
+      <c r="IQ2" s="80"/>
+      <c r="IR2" s="80"/>
+      <c r="IS2" s="80"/>
+      <c r="IT2" s="80"/>
+      <c r="IU2" s="80"/>
+      <c r="IV2" s="80"/>
+      <c r="IW2" s="80"/>
+    </row>
+    <row r="3" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="73"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -20438,6 +25914,249 @@
       <c r="L3" s="77"/>
       <c r="M3" s="77"/>
       <c r="N3" s="79"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="80"/>
+      <c r="V3" s="80"/>
+      <c r="W3" s="80"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="80"/>
+      <c r="AC3" s="80"/>
+      <c r="AD3" s="80"/>
+      <c r="AE3" s="80"/>
+      <c r="AF3" s="80"/>
+      <c r="AG3" s="80"/>
+      <c r="AH3" s="80"/>
+      <c r="AI3" s="80"/>
+      <c r="AJ3" s="80"/>
+      <c r="AK3" s="80"/>
+      <c r="AL3" s="80"/>
+      <c r="AM3" s="80"/>
+      <c r="AN3" s="80"/>
+      <c r="AO3" s="80"/>
+      <c r="AP3" s="80"/>
+      <c r="AQ3" s="80"/>
+      <c r="AR3" s="80"/>
+      <c r="AS3" s="80"/>
+      <c r="AT3" s="80"/>
+      <c r="AU3" s="80"/>
+      <c r="AV3" s="80"/>
+      <c r="AW3" s="80"/>
+      <c r="AX3" s="80"/>
+      <c r="AY3" s="80"/>
+      <c r="AZ3" s="80"/>
+      <c r="BA3" s="80"/>
+      <c r="BB3" s="80"/>
+      <c r="BC3" s="80"/>
+      <c r="BD3" s="80"/>
+      <c r="BE3" s="80"/>
+      <c r="BF3" s="80"/>
+      <c r="BG3" s="80"/>
+      <c r="BH3" s="80"/>
+      <c r="BI3" s="80"/>
+      <c r="BJ3" s="80"/>
+      <c r="BK3" s="80"/>
+      <c r="BL3" s="80"/>
+      <c r="BM3" s="80"/>
+      <c r="BN3" s="80"/>
+      <c r="BO3" s="80"/>
+      <c r="BP3" s="80"/>
+      <c r="BQ3" s="80"/>
+      <c r="BR3" s="80"/>
+      <c r="BS3" s="80"/>
+      <c r="BT3" s="80"/>
+      <c r="BU3" s="80"/>
+      <c r="BV3" s="80"/>
+      <c r="BW3" s="80"/>
+      <c r="BX3" s="80"/>
+      <c r="BY3" s="80"/>
+      <c r="BZ3" s="80"/>
+      <c r="CA3" s="80"/>
+      <c r="CB3" s="80"/>
+      <c r="CC3" s="80"/>
+      <c r="CD3" s="80"/>
+      <c r="CE3" s="80"/>
+      <c r="CF3" s="80"/>
+      <c r="CG3" s="80"/>
+      <c r="CH3" s="80"/>
+      <c r="CI3" s="80"/>
+      <c r="CJ3" s="80"/>
+      <c r="CK3" s="80"/>
+      <c r="CL3" s="80"/>
+      <c r="CM3" s="80"/>
+      <c r="CN3" s="80"/>
+      <c r="CO3" s="80"/>
+      <c r="CP3" s="80"/>
+      <c r="CQ3" s="80"/>
+      <c r="CR3" s="80"/>
+      <c r="CS3" s="80"/>
+      <c r="CT3" s="80"/>
+      <c r="CU3" s="80"/>
+      <c r="CV3" s="80"/>
+      <c r="CW3" s="80"/>
+      <c r="CX3" s="80"/>
+      <c r="CY3" s="80"/>
+      <c r="CZ3" s="80"/>
+      <c r="DA3" s="80"/>
+      <c r="DB3" s="80"/>
+      <c r="DC3" s="80"/>
+      <c r="DD3" s="80"/>
+      <c r="DE3" s="80"/>
+      <c r="DF3" s="80"/>
+      <c r="DG3" s="80"/>
+      <c r="DH3" s="80"/>
+      <c r="DI3" s="80"/>
+      <c r="DJ3" s="80"/>
+      <c r="DK3" s="80"/>
+      <c r="DL3" s="80"/>
+      <c r="DM3" s="80"/>
+      <c r="DN3" s="80"/>
+      <c r="DO3" s="80"/>
+      <c r="DP3" s="80"/>
+      <c r="DQ3" s="80"/>
+      <c r="DR3" s="80"/>
+      <c r="DS3" s="80"/>
+      <c r="DT3" s="80"/>
+      <c r="DU3" s="80"/>
+      <c r="DV3" s="80"/>
+      <c r="DW3" s="80"/>
+      <c r="DX3" s="80"/>
+      <c r="DY3" s="80"/>
+      <c r="DZ3" s="80"/>
+      <c r="EA3" s="80"/>
+      <c r="EB3" s="80"/>
+      <c r="EC3" s="80"/>
+      <c r="ED3" s="80"/>
+      <c r="EE3" s="80"/>
+      <c r="EF3" s="80"/>
+      <c r="EG3" s="80"/>
+      <c r="EH3" s="80"/>
+      <c r="EI3" s="80"/>
+      <c r="EJ3" s="80"/>
+      <c r="EK3" s="80"/>
+      <c r="EL3" s="80"/>
+      <c r="EM3" s="80"/>
+      <c r="EN3" s="80"/>
+      <c r="EO3" s="80"/>
+      <c r="EP3" s="80"/>
+      <c r="EQ3" s="80"/>
+      <c r="ER3" s="80"/>
+      <c r="ES3" s="80"/>
+      <c r="ET3" s="80"/>
+      <c r="EU3" s="80"/>
+      <c r="EV3" s="80"/>
+      <c r="EW3" s="80"/>
+      <c r="EX3" s="80"/>
+      <c r="EY3" s="80"/>
+      <c r="EZ3" s="80"/>
+      <c r="FA3" s="80"/>
+      <c r="FB3" s="80"/>
+      <c r="FC3" s="80"/>
+      <c r="FD3" s="80"/>
+      <c r="FE3" s="80"/>
+      <c r="FF3" s="80"/>
+      <c r="FG3" s="80"/>
+      <c r="FH3" s="80"/>
+      <c r="FI3" s="80"/>
+      <c r="FJ3" s="80"/>
+      <c r="FK3" s="80"/>
+      <c r="FL3" s="80"/>
+      <c r="FM3" s="80"/>
+      <c r="FN3" s="80"/>
+      <c r="FO3" s="80"/>
+      <c r="FP3" s="80"/>
+      <c r="FQ3" s="80"/>
+      <c r="FR3" s="80"/>
+      <c r="FS3" s="80"/>
+      <c r="FT3" s="80"/>
+      <c r="FU3" s="80"/>
+      <c r="FV3" s="80"/>
+      <c r="FW3" s="80"/>
+      <c r="FX3" s="80"/>
+      <c r="FY3" s="80"/>
+      <c r="FZ3" s="80"/>
+      <c r="GA3" s="80"/>
+      <c r="GB3" s="80"/>
+      <c r="GC3" s="80"/>
+      <c r="GD3" s="80"/>
+      <c r="GE3" s="80"/>
+      <c r="GF3" s="80"/>
+      <c r="GG3" s="80"/>
+      <c r="GH3" s="80"/>
+      <c r="GI3" s="80"/>
+      <c r="GJ3" s="80"/>
+      <c r="GK3" s="80"/>
+      <c r="GL3" s="80"/>
+      <c r="GM3" s="80"/>
+      <c r="GN3" s="80"/>
+      <c r="GO3" s="80"/>
+      <c r="GP3" s="80"/>
+      <c r="GQ3" s="80"/>
+      <c r="GR3" s="80"/>
+      <c r="GS3" s="80"/>
+      <c r="GT3" s="80"/>
+      <c r="GU3" s="80"/>
+      <c r="GV3" s="80"/>
+      <c r="GW3" s="80"/>
+      <c r="GX3" s="80"/>
+      <c r="GY3" s="80"/>
+      <c r="GZ3" s="80"/>
+      <c r="HA3" s="80"/>
+      <c r="HB3" s="80"/>
+      <c r="HC3" s="80"/>
+      <c r="HD3" s="80"/>
+      <c r="HE3" s="80"/>
+      <c r="HF3" s="80"/>
+      <c r="HG3" s="80"/>
+      <c r="HH3" s="80"/>
+      <c r="HI3" s="80"/>
+      <c r="HJ3" s="80"/>
+      <c r="HK3" s="80"/>
+      <c r="HL3" s="80"/>
+      <c r="HM3" s="80"/>
+      <c r="HN3" s="80"/>
+      <c r="HO3" s="80"/>
+      <c r="HP3" s="80"/>
+      <c r="HQ3" s="80"/>
+      <c r="HR3" s="80"/>
+      <c r="HS3" s="80"/>
+      <c r="HT3" s="80"/>
+      <c r="HU3" s="80"/>
+      <c r="HV3" s="80"/>
+      <c r="HW3" s="80"/>
+      <c r="HX3" s="80"/>
+      <c r="HY3" s="80"/>
+      <c r="HZ3" s="80"/>
+      <c r="IA3" s="80"/>
+      <c r="IB3" s="80"/>
+      <c r="IC3" s="80"/>
+      <c r="ID3" s="80"/>
+      <c r="IE3" s="80"/>
+      <c r="IF3" s="80"/>
+      <c r="IG3" s="80"/>
+      <c r="IH3" s="80"/>
+      <c r="II3" s="80"/>
+      <c r="IJ3" s="80"/>
+      <c r="IK3" s="80"/>
+      <c r="IL3" s="80"/>
+      <c r="IM3" s="80"/>
+      <c r="IN3" s="80"/>
+      <c r="IO3" s="80"/>
+      <c r="IP3" s="80"/>
+      <c r="IQ3" s="80"/>
+      <c r="IR3" s="80"/>
+      <c r="IS3" s="80"/>
+      <c r="IT3" s="80"/>
+      <c r="IU3" s="80"/>
+      <c r="IV3" s="80"/>
+      <c r="IW3" s="80"/>
     </row>
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="84"/>
@@ -21280,8 +26999,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW201"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="98" width="9.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="99" width="20.15"/>
@@ -21293,7 +27012,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="9" style="102" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="106" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="103" t="s">
         <v>29</v>
       </c>
@@ -21315,8 +27034,257 @@
         <f aca="false">SUM(H5:H500)</f>
         <v>4000</v>
       </c>
-    </row>
-    <row r="2" s="106" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
+      <c r="AC1" s="106"/>
+      <c r="AD1" s="106"/>
+      <c r="AE1" s="106"/>
+      <c r="AF1" s="106"/>
+      <c r="AG1" s="106"/>
+      <c r="AH1" s="106"/>
+      <c r="AI1" s="106"/>
+      <c r="AJ1" s="106"/>
+      <c r="AK1" s="106"/>
+      <c r="AL1" s="106"/>
+      <c r="AM1" s="106"/>
+      <c r="AN1" s="106"/>
+      <c r="AO1" s="106"/>
+      <c r="AP1" s="106"/>
+      <c r="AQ1" s="106"/>
+      <c r="AR1" s="106"/>
+      <c r="AS1" s="106"/>
+      <c r="AT1" s="106"/>
+      <c r="AU1" s="106"/>
+      <c r="AV1" s="106"/>
+      <c r="AW1" s="106"/>
+      <c r="AX1" s="106"/>
+      <c r="AY1" s="106"/>
+      <c r="AZ1" s="106"/>
+      <c r="BA1" s="106"/>
+      <c r="BB1" s="106"/>
+      <c r="BC1" s="106"/>
+      <c r="BD1" s="106"/>
+      <c r="BE1" s="106"/>
+      <c r="BF1" s="106"/>
+      <c r="BG1" s="106"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="106"/>
+      <c r="BJ1" s="106"/>
+      <c r="BK1" s="106"/>
+      <c r="BL1" s="106"/>
+      <c r="BM1" s="106"/>
+      <c r="BN1" s="106"/>
+      <c r="BO1" s="106"/>
+      <c r="BP1" s="106"/>
+      <c r="BQ1" s="106"/>
+      <c r="BR1" s="106"/>
+      <c r="BS1" s="106"/>
+      <c r="BT1" s="106"/>
+      <c r="BU1" s="106"/>
+      <c r="BV1" s="106"/>
+      <c r="BW1" s="106"/>
+      <c r="BX1" s="106"/>
+      <c r="BY1" s="106"/>
+      <c r="BZ1" s="106"/>
+      <c r="CA1" s="106"/>
+      <c r="CB1" s="106"/>
+      <c r="CC1" s="106"/>
+      <c r="CD1" s="106"/>
+      <c r="CE1" s="106"/>
+      <c r="CF1" s="106"/>
+      <c r="CG1" s="106"/>
+      <c r="CH1" s="106"/>
+      <c r="CI1" s="106"/>
+      <c r="CJ1" s="106"/>
+      <c r="CK1" s="106"/>
+      <c r="CL1" s="106"/>
+      <c r="CM1" s="106"/>
+      <c r="CN1" s="106"/>
+      <c r="CO1" s="106"/>
+      <c r="CP1" s="106"/>
+      <c r="CQ1" s="106"/>
+      <c r="CR1" s="106"/>
+      <c r="CS1" s="106"/>
+      <c r="CT1" s="106"/>
+      <c r="CU1" s="106"/>
+      <c r="CV1" s="106"/>
+      <c r="CW1" s="106"/>
+      <c r="CX1" s="106"/>
+      <c r="CY1" s="106"/>
+      <c r="CZ1" s="106"/>
+      <c r="DA1" s="106"/>
+      <c r="DB1" s="106"/>
+      <c r="DC1" s="106"/>
+      <c r="DD1" s="106"/>
+      <c r="DE1" s="106"/>
+      <c r="DF1" s="106"/>
+      <c r="DG1" s="106"/>
+      <c r="DH1" s="106"/>
+      <c r="DI1" s="106"/>
+      <c r="DJ1" s="106"/>
+      <c r="DK1" s="106"/>
+      <c r="DL1" s="106"/>
+      <c r="DM1" s="106"/>
+      <c r="DN1" s="106"/>
+      <c r="DO1" s="106"/>
+      <c r="DP1" s="106"/>
+      <c r="DQ1" s="106"/>
+      <c r="DR1" s="106"/>
+      <c r="DS1" s="106"/>
+      <c r="DT1" s="106"/>
+      <c r="DU1" s="106"/>
+      <c r="DV1" s="106"/>
+      <c r="DW1" s="106"/>
+      <c r="DX1" s="106"/>
+      <c r="DY1" s="106"/>
+      <c r="DZ1" s="106"/>
+      <c r="EA1" s="106"/>
+      <c r="EB1" s="106"/>
+      <c r="EC1" s="106"/>
+      <c r="ED1" s="106"/>
+      <c r="EE1" s="106"/>
+      <c r="EF1" s="106"/>
+      <c r="EG1" s="106"/>
+      <c r="EH1" s="106"/>
+      <c r="EI1" s="106"/>
+      <c r="EJ1" s="106"/>
+      <c r="EK1" s="106"/>
+      <c r="EL1" s="106"/>
+      <c r="EM1" s="106"/>
+      <c r="EN1" s="106"/>
+      <c r="EO1" s="106"/>
+      <c r="EP1" s="106"/>
+      <c r="EQ1" s="106"/>
+      <c r="ER1" s="106"/>
+      <c r="ES1" s="106"/>
+      <c r="ET1" s="106"/>
+      <c r="EU1" s="106"/>
+      <c r="EV1" s="106"/>
+      <c r="EW1" s="106"/>
+      <c r="EX1" s="106"/>
+      <c r="EY1" s="106"/>
+      <c r="EZ1" s="106"/>
+      <c r="FA1" s="106"/>
+      <c r="FB1" s="106"/>
+      <c r="FC1" s="106"/>
+      <c r="FD1" s="106"/>
+      <c r="FE1" s="106"/>
+      <c r="FF1" s="106"/>
+      <c r="FG1" s="106"/>
+      <c r="FH1" s="106"/>
+      <c r="FI1" s="106"/>
+      <c r="FJ1" s="106"/>
+      <c r="FK1" s="106"/>
+      <c r="FL1" s="106"/>
+      <c r="FM1" s="106"/>
+      <c r="FN1" s="106"/>
+      <c r="FO1" s="106"/>
+      <c r="FP1" s="106"/>
+      <c r="FQ1" s="106"/>
+      <c r="FR1" s="106"/>
+      <c r="FS1" s="106"/>
+      <c r="FT1" s="106"/>
+      <c r="FU1" s="106"/>
+      <c r="FV1" s="106"/>
+      <c r="FW1" s="106"/>
+      <c r="FX1" s="106"/>
+      <c r="FY1" s="106"/>
+      <c r="FZ1" s="106"/>
+      <c r="GA1" s="106"/>
+      <c r="GB1" s="106"/>
+      <c r="GC1" s="106"/>
+      <c r="GD1" s="106"/>
+      <c r="GE1" s="106"/>
+      <c r="GF1" s="106"/>
+      <c r="GG1" s="106"/>
+      <c r="GH1" s="106"/>
+      <c r="GI1" s="106"/>
+      <c r="GJ1" s="106"/>
+      <c r="GK1" s="106"/>
+      <c r="GL1" s="106"/>
+      <c r="GM1" s="106"/>
+      <c r="GN1" s="106"/>
+      <c r="GO1" s="106"/>
+      <c r="GP1" s="106"/>
+      <c r="GQ1" s="106"/>
+      <c r="GR1" s="106"/>
+      <c r="GS1" s="106"/>
+      <c r="GT1" s="106"/>
+      <c r="GU1" s="106"/>
+      <c r="GV1" s="106"/>
+      <c r="GW1" s="106"/>
+      <c r="GX1" s="106"/>
+      <c r="GY1" s="106"/>
+      <c r="GZ1" s="106"/>
+      <c r="HA1" s="106"/>
+      <c r="HB1" s="106"/>
+      <c r="HC1" s="106"/>
+      <c r="HD1" s="106"/>
+      <c r="HE1" s="106"/>
+      <c r="HF1" s="106"/>
+      <c r="HG1" s="106"/>
+      <c r="HH1" s="106"/>
+      <c r="HI1" s="106"/>
+      <c r="HJ1" s="106"/>
+      <c r="HK1" s="106"/>
+      <c r="HL1" s="106"/>
+      <c r="HM1" s="106"/>
+      <c r="HN1" s="106"/>
+      <c r="HO1" s="106"/>
+      <c r="HP1" s="106"/>
+      <c r="HQ1" s="106"/>
+      <c r="HR1" s="106"/>
+      <c r="HS1" s="106"/>
+      <c r="HT1" s="106"/>
+      <c r="HU1" s="106"/>
+      <c r="HV1" s="106"/>
+      <c r="HW1" s="106"/>
+      <c r="HX1" s="106"/>
+      <c r="HY1" s="106"/>
+      <c r="HZ1" s="106"/>
+      <c r="IA1" s="106"/>
+      <c r="IB1" s="106"/>
+      <c r="IC1" s="106"/>
+      <c r="ID1" s="106"/>
+      <c r="IE1" s="106"/>
+      <c r="IF1" s="106"/>
+      <c r="IG1" s="106"/>
+      <c r="IH1" s="106"/>
+      <c r="II1" s="106"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="106"/>
+      <c r="IL1" s="106"/>
+      <c r="IM1" s="106"/>
+      <c r="IN1" s="106"/>
+      <c r="IO1" s="106"/>
+      <c r="IP1" s="106"/>
+      <c r="IQ1" s="106"/>
+      <c r="IR1" s="106"/>
+      <c r="IS1" s="106"/>
+      <c r="IT1" s="106"/>
+      <c r="IU1" s="106"/>
+      <c r="IV1" s="106"/>
+      <c r="IW1" s="106"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
         <v>31</v>
       </c>
@@ -21340,8 +27308,257 @@
       <c r="H2" s="108" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" s="112" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="106"/>
+      <c r="R2" s="106"/>
+      <c r="S2" s="106"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="106"/>
+      <c r="W2" s="106"/>
+      <c r="X2" s="106"/>
+      <c r="Y2" s="106"/>
+      <c r="Z2" s="106"/>
+      <c r="AA2" s="106"/>
+      <c r="AB2" s="106"/>
+      <c r="AC2" s="106"/>
+      <c r="AD2" s="106"/>
+      <c r="AE2" s="106"/>
+      <c r="AF2" s="106"/>
+      <c r="AG2" s="106"/>
+      <c r="AH2" s="106"/>
+      <c r="AI2" s="106"/>
+      <c r="AJ2" s="106"/>
+      <c r="AK2" s="106"/>
+      <c r="AL2" s="106"/>
+      <c r="AM2" s="106"/>
+      <c r="AN2" s="106"/>
+      <c r="AO2" s="106"/>
+      <c r="AP2" s="106"/>
+      <c r="AQ2" s="106"/>
+      <c r="AR2" s="106"/>
+      <c r="AS2" s="106"/>
+      <c r="AT2" s="106"/>
+      <c r="AU2" s="106"/>
+      <c r="AV2" s="106"/>
+      <c r="AW2" s="106"/>
+      <c r="AX2" s="106"/>
+      <c r="AY2" s="106"/>
+      <c r="AZ2" s="106"/>
+      <c r="BA2" s="106"/>
+      <c r="BB2" s="106"/>
+      <c r="BC2" s="106"/>
+      <c r="BD2" s="106"/>
+      <c r="BE2" s="106"/>
+      <c r="BF2" s="106"/>
+      <c r="BG2" s="106"/>
+      <c r="BH2" s="106"/>
+      <c r="BI2" s="106"/>
+      <c r="BJ2" s="106"/>
+      <c r="BK2" s="106"/>
+      <c r="BL2" s="106"/>
+      <c r="BM2" s="106"/>
+      <c r="BN2" s="106"/>
+      <c r="BO2" s="106"/>
+      <c r="BP2" s="106"/>
+      <c r="BQ2" s="106"/>
+      <c r="BR2" s="106"/>
+      <c r="BS2" s="106"/>
+      <c r="BT2" s="106"/>
+      <c r="BU2" s="106"/>
+      <c r="BV2" s="106"/>
+      <c r="BW2" s="106"/>
+      <c r="BX2" s="106"/>
+      <c r="BY2" s="106"/>
+      <c r="BZ2" s="106"/>
+      <c r="CA2" s="106"/>
+      <c r="CB2" s="106"/>
+      <c r="CC2" s="106"/>
+      <c r="CD2" s="106"/>
+      <c r="CE2" s="106"/>
+      <c r="CF2" s="106"/>
+      <c r="CG2" s="106"/>
+      <c r="CH2" s="106"/>
+      <c r="CI2" s="106"/>
+      <c r="CJ2" s="106"/>
+      <c r="CK2" s="106"/>
+      <c r="CL2" s="106"/>
+      <c r="CM2" s="106"/>
+      <c r="CN2" s="106"/>
+      <c r="CO2" s="106"/>
+      <c r="CP2" s="106"/>
+      <c r="CQ2" s="106"/>
+      <c r="CR2" s="106"/>
+      <c r="CS2" s="106"/>
+      <c r="CT2" s="106"/>
+      <c r="CU2" s="106"/>
+      <c r="CV2" s="106"/>
+      <c r="CW2" s="106"/>
+      <c r="CX2" s="106"/>
+      <c r="CY2" s="106"/>
+      <c r="CZ2" s="106"/>
+      <c r="DA2" s="106"/>
+      <c r="DB2" s="106"/>
+      <c r="DC2" s="106"/>
+      <c r="DD2" s="106"/>
+      <c r="DE2" s="106"/>
+      <c r="DF2" s="106"/>
+      <c r="DG2" s="106"/>
+      <c r="DH2" s="106"/>
+      <c r="DI2" s="106"/>
+      <c r="DJ2" s="106"/>
+      <c r="DK2" s="106"/>
+      <c r="DL2" s="106"/>
+      <c r="DM2" s="106"/>
+      <c r="DN2" s="106"/>
+      <c r="DO2" s="106"/>
+      <c r="DP2" s="106"/>
+      <c r="DQ2" s="106"/>
+      <c r="DR2" s="106"/>
+      <c r="DS2" s="106"/>
+      <c r="DT2" s="106"/>
+      <c r="DU2" s="106"/>
+      <c r="DV2" s="106"/>
+      <c r="DW2" s="106"/>
+      <c r="DX2" s="106"/>
+      <c r="DY2" s="106"/>
+      <c r="DZ2" s="106"/>
+      <c r="EA2" s="106"/>
+      <c r="EB2" s="106"/>
+      <c r="EC2" s="106"/>
+      <c r="ED2" s="106"/>
+      <c r="EE2" s="106"/>
+      <c r="EF2" s="106"/>
+      <c r="EG2" s="106"/>
+      <c r="EH2" s="106"/>
+      <c r="EI2" s="106"/>
+      <c r="EJ2" s="106"/>
+      <c r="EK2" s="106"/>
+      <c r="EL2" s="106"/>
+      <c r="EM2" s="106"/>
+      <c r="EN2" s="106"/>
+      <c r="EO2" s="106"/>
+      <c r="EP2" s="106"/>
+      <c r="EQ2" s="106"/>
+      <c r="ER2" s="106"/>
+      <c r="ES2" s="106"/>
+      <c r="ET2" s="106"/>
+      <c r="EU2" s="106"/>
+      <c r="EV2" s="106"/>
+      <c r="EW2" s="106"/>
+      <c r="EX2" s="106"/>
+      <c r="EY2" s="106"/>
+      <c r="EZ2" s="106"/>
+      <c r="FA2" s="106"/>
+      <c r="FB2" s="106"/>
+      <c r="FC2" s="106"/>
+      <c r="FD2" s="106"/>
+      <c r="FE2" s="106"/>
+      <c r="FF2" s="106"/>
+      <c r="FG2" s="106"/>
+      <c r="FH2" s="106"/>
+      <c r="FI2" s="106"/>
+      <c r="FJ2" s="106"/>
+      <c r="FK2" s="106"/>
+      <c r="FL2" s="106"/>
+      <c r="FM2" s="106"/>
+      <c r="FN2" s="106"/>
+      <c r="FO2" s="106"/>
+      <c r="FP2" s="106"/>
+      <c r="FQ2" s="106"/>
+      <c r="FR2" s="106"/>
+      <c r="FS2" s="106"/>
+      <c r="FT2" s="106"/>
+      <c r="FU2" s="106"/>
+      <c r="FV2" s="106"/>
+      <c r="FW2" s="106"/>
+      <c r="FX2" s="106"/>
+      <c r="FY2" s="106"/>
+      <c r="FZ2" s="106"/>
+      <c r="GA2" s="106"/>
+      <c r="GB2" s="106"/>
+      <c r="GC2" s="106"/>
+      <c r="GD2" s="106"/>
+      <c r="GE2" s="106"/>
+      <c r="GF2" s="106"/>
+      <c r="GG2" s="106"/>
+      <c r="GH2" s="106"/>
+      <c r="GI2" s="106"/>
+      <c r="GJ2" s="106"/>
+      <c r="GK2" s="106"/>
+      <c r="GL2" s="106"/>
+      <c r="GM2" s="106"/>
+      <c r="GN2" s="106"/>
+      <c r="GO2" s="106"/>
+      <c r="GP2" s="106"/>
+      <c r="GQ2" s="106"/>
+      <c r="GR2" s="106"/>
+      <c r="GS2" s="106"/>
+      <c r="GT2" s="106"/>
+      <c r="GU2" s="106"/>
+      <c r="GV2" s="106"/>
+      <c r="GW2" s="106"/>
+      <c r="GX2" s="106"/>
+      <c r="GY2" s="106"/>
+      <c r="GZ2" s="106"/>
+      <c r="HA2" s="106"/>
+      <c r="HB2" s="106"/>
+      <c r="HC2" s="106"/>
+      <c r="HD2" s="106"/>
+      <c r="HE2" s="106"/>
+      <c r="HF2" s="106"/>
+      <c r="HG2" s="106"/>
+      <c r="HH2" s="106"/>
+      <c r="HI2" s="106"/>
+      <c r="HJ2" s="106"/>
+      <c r="HK2" s="106"/>
+      <c r="HL2" s="106"/>
+      <c r="HM2" s="106"/>
+      <c r="HN2" s="106"/>
+      <c r="HO2" s="106"/>
+      <c r="HP2" s="106"/>
+      <c r="HQ2" s="106"/>
+      <c r="HR2" s="106"/>
+      <c r="HS2" s="106"/>
+      <c r="HT2" s="106"/>
+      <c r="HU2" s="106"/>
+      <c r="HV2" s="106"/>
+      <c r="HW2" s="106"/>
+      <c r="HX2" s="106"/>
+      <c r="HY2" s="106"/>
+      <c r="HZ2" s="106"/>
+      <c r="IA2" s="106"/>
+      <c r="IB2" s="106"/>
+      <c r="IC2" s="106"/>
+      <c r="ID2" s="106"/>
+      <c r="IE2" s="106"/>
+      <c r="IF2" s="106"/>
+      <c r="IG2" s="106"/>
+      <c r="IH2" s="106"/>
+      <c r="II2" s="106"/>
+      <c r="IJ2" s="106"/>
+      <c r="IK2" s="106"/>
+      <c r="IL2" s="106"/>
+      <c r="IM2" s="106"/>
+      <c r="IN2" s="106"/>
+      <c r="IO2" s="106"/>
+      <c r="IP2" s="106"/>
+      <c r="IQ2" s="106"/>
+      <c r="IR2" s="106"/>
+      <c r="IS2" s="106"/>
+      <c r="IT2" s="106"/>
+      <c r="IU2" s="106"/>
+      <c r="IV2" s="106"/>
+      <c r="IW2" s="106"/>
+    </row>
+    <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="107"/>
       <c r="B3" s="108"/>
       <c r="C3" s="109"/>
@@ -21352,6 +27569,255 @@
         <v>37</v>
       </c>
       <c r="H3" s="108"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
+      <c r="L3" s="112"/>
+      <c r="M3" s="112"/>
+      <c r="N3" s="112"/>
+      <c r="O3" s="112"/>
+      <c r="P3" s="112"/>
+      <c r="Q3" s="112"/>
+      <c r="R3" s="112"/>
+      <c r="S3" s="112"/>
+      <c r="T3" s="112"/>
+      <c r="U3" s="112"/>
+      <c r="V3" s="112"/>
+      <c r="W3" s="112"/>
+      <c r="X3" s="112"/>
+      <c r="Y3" s="112"/>
+      <c r="Z3" s="112"/>
+      <c r="AA3" s="112"/>
+      <c r="AB3" s="112"/>
+      <c r="AC3" s="112"/>
+      <c r="AD3" s="112"/>
+      <c r="AE3" s="112"/>
+      <c r="AF3" s="112"/>
+      <c r="AG3" s="112"/>
+      <c r="AH3" s="112"/>
+      <c r="AI3" s="112"/>
+      <c r="AJ3" s="112"/>
+      <c r="AK3" s="112"/>
+      <c r="AL3" s="112"/>
+      <c r="AM3" s="112"/>
+      <c r="AN3" s="112"/>
+      <c r="AO3" s="112"/>
+      <c r="AP3" s="112"/>
+      <c r="AQ3" s="112"/>
+      <c r="AR3" s="112"/>
+      <c r="AS3" s="112"/>
+      <c r="AT3" s="112"/>
+      <c r="AU3" s="112"/>
+      <c r="AV3" s="112"/>
+      <c r="AW3" s="112"/>
+      <c r="AX3" s="112"/>
+      <c r="AY3" s="112"/>
+      <c r="AZ3" s="112"/>
+      <c r="BA3" s="112"/>
+      <c r="BB3" s="112"/>
+      <c r="BC3" s="112"/>
+      <c r="BD3" s="112"/>
+      <c r="BE3" s="112"/>
+      <c r="BF3" s="112"/>
+      <c r="BG3" s="112"/>
+      <c r="BH3" s="112"/>
+      <c r="BI3" s="112"/>
+      <c r="BJ3" s="112"/>
+      <c r="BK3" s="112"/>
+      <c r="BL3" s="112"/>
+      <c r="BM3" s="112"/>
+      <c r="BN3" s="112"/>
+      <c r="BO3" s="112"/>
+      <c r="BP3" s="112"/>
+      <c r="BQ3" s="112"/>
+      <c r="BR3" s="112"/>
+      <c r="BS3" s="112"/>
+      <c r="BT3" s="112"/>
+      <c r="BU3" s="112"/>
+      <c r="BV3" s="112"/>
+      <c r="BW3" s="112"/>
+      <c r="BX3" s="112"/>
+      <c r="BY3" s="112"/>
+      <c r="BZ3" s="112"/>
+      <c r="CA3" s="112"/>
+      <c r="CB3" s="112"/>
+      <c r="CC3" s="112"/>
+      <c r="CD3" s="112"/>
+      <c r="CE3" s="112"/>
+      <c r="CF3" s="112"/>
+      <c r="CG3" s="112"/>
+      <c r="CH3" s="112"/>
+      <c r="CI3" s="112"/>
+      <c r="CJ3" s="112"/>
+      <c r="CK3" s="112"/>
+      <c r="CL3" s="112"/>
+      <c r="CM3" s="112"/>
+      <c r="CN3" s="112"/>
+      <c r="CO3" s="112"/>
+      <c r="CP3" s="112"/>
+      <c r="CQ3" s="112"/>
+      <c r="CR3" s="112"/>
+      <c r="CS3" s="112"/>
+      <c r="CT3" s="112"/>
+      <c r="CU3" s="112"/>
+      <c r="CV3" s="112"/>
+      <c r="CW3" s="112"/>
+      <c r="CX3" s="112"/>
+      <c r="CY3" s="112"/>
+      <c r="CZ3" s="112"/>
+      <c r="DA3" s="112"/>
+      <c r="DB3" s="112"/>
+      <c r="DC3" s="112"/>
+      <c r="DD3" s="112"/>
+      <c r="DE3" s="112"/>
+      <c r="DF3" s="112"/>
+      <c r="DG3" s="112"/>
+      <c r="DH3" s="112"/>
+      <c r="DI3" s="112"/>
+      <c r="DJ3" s="112"/>
+      <c r="DK3" s="112"/>
+      <c r="DL3" s="112"/>
+      <c r="DM3" s="112"/>
+      <c r="DN3" s="112"/>
+      <c r="DO3" s="112"/>
+      <c r="DP3" s="112"/>
+      <c r="DQ3" s="112"/>
+      <c r="DR3" s="112"/>
+      <c r="DS3" s="112"/>
+      <c r="DT3" s="112"/>
+      <c r="DU3" s="112"/>
+      <c r="DV3" s="112"/>
+      <c r="DW3" s="112"/>
+      <c r="DX3" s="112"/>
+      <c r="DY3" s="112"/>
+      <c r="DZ3" s="112"/>
+      <c r="EA3" s="112"/>
+      <c r="EB3" s="112"/>
+      <c r="EC3" s="112"/>
+      <c r="ED3" s="112"/>
+      <c r="EE3" s="112"/>
+      <c r="EF3" s="112"/>
+      <c r="EG3" s="112"/>
+      <c r="EH3" s="112"/>
+      <c r="EI3" s="112"/>
+      <c r="EJ3" s="112"/>
+      <c r="EK3" s="112"/>
+      <c r="EL3" s="112"/>
+      <c r="EM3" s="112"/>
+      <c r="EN3" s="112"/>
+      <c r="EO3" s="112"/>
+      <c r="EP3" s="112"/>
+      <c r="EQ3" s="112"/>
+      <c r="ER3" s="112"/>
+      <c r="ES3" s="112"/>
+      <c r="ET3" s="112"/>
+      <c r="EU3" s="112"/>
+      <c r="EV3" s="112"/>
+      <c r="EW3" s="112"/>
+      <c r="EX3" s="112"/>
+      <c r="EY3" s="112"/>
+      <c r="EZ3" s="112"/>
+      <c r="FA3" s="112"/>
+      <c r="FB3" s="112"/>
+      <c r="FC3" s="112"/>
+      <c r="FD3" s="112"/>
+      <c r="FE3" s="112"/>
+      <c r="FF3" s="112"/>
+      <c r="FG3" s="112"/>
+      <c r="FH3" s="112"/>
+      <c r="FI3" s="112"/>
+      <c r="FJ3" s="112"/>
+      <c r="FK3" s="112"/>
+      <c r="FL3" s="112"/>
+      <c r="FM3" s="112"/>
+      <c r="FN3" s="112"/>
+      <c r="FO3" s="112"/>
+      <c r="FP3" s="112"/>
+      <c r="FQ3" s="112"/>
+      <c r="FR3" s="112"/>
+      <c r="FS3" s="112"/>
+      <c r="FT3" s="112"/>
+      <c r="FU3" s="112"/>
+      <c r="FV3" s="112"/>
+      <c r="FW3" s="112"/>
+      <c r="FX3" s="112"/>
+      <c r="FY3" s="112"/>
+      <c r="FZ3" s="112"/>
+      <c r="GA3" s="112"/>
+      <c r="GB3" s="112"/>
+      <c r="GC3" s="112"/>
+      <c r="GD3" s="112"/>
+      <c r="GE3" s="112"/>
+      <c r="GF3" s="112"/>
+      <c r="GG3" s="112"/>
+      <c r="GH3" s="112"/>
+      <c r="GI3" s="112"/>
+      <c r="GJ3" s="112"/>
+      <c r="GK3" s="112"/>
+      <c r="GL3" s="112"/>
+      <c r="GM3" s="112"/>
+      <c r="GN3" s="112"/>
+      <c r="GO3" s="112"/>
+      <c r="GP3" s="112"/>
+      <c r="GQ3" s="112"/>
+      <c r="GR3" s="112"/>
+      <c r="GS3" s="112"/>
+      <c r="GT3" s="112"/>
+      <c r="GU3" s="112"/>
+      <c r="GV3" s="112"/>
+      <c r="GW3" s="112"/>
+      <c r="GX3" s="112"/>
+      <c r="GY3" s="112"/>
+      <c r="GZ3" s="112"/>
+      <c r="HA3" s="112"/>
+      <c r="HB3" s="112"/>
+      <c r="HC3" s="112"/>
+      <c r="HD3" s="112"/>
+      <c r="HE3" s="112"/>
+      <c r="HF3" s="112"/>
+      <c r="HG3" s="112"/>
+      <c r="HH3" s="112"/>
+      <c r="HI3" s="112"/>
+      <c r="HJ3" s="112"/>
+      <c r="HK3" s="112"/>
+      <c r="HL3" s="112"/>
+      <c r="HM3" s="112"/>
+      <c r="HN3" s="112"/>
+      <c r="HO3" s="112"/>
+      <c r="HP3" s="112"/>
+      <c r="HQ3" s="112"/>
+      <c r="HR3" s="112"/>
+      <c r="HS3" s="112"/>
+      <c r="HT3" s="112"/>
+      <c r="HU3" s="112"/>
+      <c r="HV3" s="112"/>
+      <c r="HW3" s="112"/>
+      <c r="HX3" s="112"/>
+      <c r="HY3" s="112"/>
+      <c r="HZ3" s="112"/>
+      <c r="IA3" s="112"/>
+      <c r="IB3" s="112"/>
+      <c r="IC3" s="112"/>
+      <c r="ID3" s="112"/>
+      <c r="IE3" s="112"/>
+      <c r="IF3" s="112"/>
+      <c r="IG3" s="112"/>
+      <c r="IH3" s="112"/>
+      <c r="II3" s="112"/>
+      <c r="IJ3" s="112"/>
+      <c r="IK3" s="112"/>
+      <c r="IL3" s="112"/>
+      <c r="IM3" s="112"/>
+      <c r="IN3" s="112"/>
+      <c r="IO3" s="112"/>
+      <c r="IP3" s="112"/>
+      <c r="IQ3" s="112"/>
+      <c r="IR3" s="112"/>
+      <c r="IS3" s="112"/>
+      <c r="IT3" s="112"/>
+      <c r="IU3" s="112"/>
+      <c r="IV3" s="112"/>
+      <c r="IW3" s="112"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="107"/>
@@ -23376,8 +29842,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW201"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="98" width="9.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="99" width="20.15"/>
@@ -23389,7 +29855,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="9" style="102" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="106" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="103" t="s">
         <v>29</v>
       </c>
@@ -23411,8 +29877,257 @@
         <f aca="false">SUM(H5:H500)</f>
         <v>2000</v>
       </c>
-    </row>
-    <row r="2" s="106" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
+      <c r="AC1" s="106"/>
+      <c r="AD1" s="106"/>
+      <c r="AE1" s="106"/>
+      <c r="AF1" s="106"/>
+      <c r="AG1" s="106"/>
+      <c r="AH1" s="106"/>
+      <c r="AI1" s="106"/>
+      <c r="AJ1" s="106"/>
+      <c r="AK1" s="106"/>
+      <c r="AL1" s="106"/>
+      <c r="AM1" s="106"/>
+      <c r="AN1" s="106"/>
+      <c r="AO1" s="106"/>
+      <c r="AP1" s="106"/>
+      <c r="AQ1" s="106"/>
+      <c r="AR1" s="106"/>
+      <c r="AS1" s="106"/>
+      <c r="AT1" s="106"/>
+      <c r="AU1" s="106"/>
+      <c r="AV1" s="106"/>
+      <c r="AW1" s="106"/>
+      <c r="AX1" s="106"/>
+      <c r="AY1" s="106"/>
+      <c r="AZ1" s="106"/>
+      <c r="BA1" s="106"/>
+      <c r="BB1" s="106"/>
+      <c r="BC1" s="106"/>
+      <c r="BD1" s="106"/>
+      <c r="BE1" s="106"/>
+      <c r="BF1" s="106"/>
+      <c r="BG1" s="106"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="106"/>
+      <c r="BJ1" s="106"/>
+      <c r="BK1" s="106"/>
+      <c r="BL1" s="106"/>
+      <c r="BM1" s="106"/>
+      <c r="BN1" s="106"/>
+      <c r="BO1" s="106"/>
+      <c r="BP1" s="106"/>
+      <c r="BQ1" s="106"/>
+      <c r="BR1" s="106"/>
+      <c r="BS1" s="106"/>
+      <c r="BT1" s="106"/>
+      <c r="BU1" s="106"/>
+      <c r="BV1" s="106"/>
+      <c r="BW1" s="106"/>
+      <c r="BX1" s="106"/>
+      <c r="BY1" s="106"/>
+      <c r="BZ1" s="106"/>
+      <c r="CA1" s="106"/>
+      <c r="CB1" s="106"/>
+      <c r="CC1" s="106"/>
+      <c r="CD1" s="106"/>
+      <c r="CE1" s="106"/>
+      <c r="CF1" s="106"/>
+      <c r="CG1" s="106"/>
+      <c r="CH1" s="106"/>
+      <c r="CI1" s="106"/>
+      <c r="CJ1" s="106"/>
+      <c r="CK1" s="106"/>
+      <c r="CL1" s="106"/>
+      <c r="CM1" s="106"/>
+      <c r="CN1" s="106"/>
+      <c r="CO1" s="106"/>
+      <c r="CP1" s="106"/>
+      <c r="CQ1" s="106"/>
+      <c r="CR1" s="106"/>
+      <c r="CS1" s="106"/>
+      <c r="CT1" s="106"/>
+      <c r="CU1" s="106"/>
+      <c r="CV1" s="106"/>
+      <c r="CW1" s="106"/>
+      <c r="CX1" s="106"/>
+      <c r="CY1" s="106"/>
+      <c r="CZ1" s="106"/>
+      <c r="DA1" s="106"/>
+      <c r="DB1" s="106"/>
+      <c r="DC1" s="106"/>
+      <c r="DD1" s="106"/>
+      <c r="DE1" s="106"/>
+      <c r="DF1" s="106"/>
+      <c r="DG1" s="106"/>
+      <c r="DH1" s="106"/>
+      <c r="DI1" s="106"/>
+      <c r="DJ1" s="106"/>
+      <c r="DK1" s="106"/>
+      <c r="DL1" s="106"/>
+      <c r="DM1" s="106"/>
+      <c r="DN1" s="106"/>
+      <c r="DO1" s="106"/>
+      <c r="DP1" s="106"/>
+      <c r="DQ1" s="106"/>
+      <c r="DR1" s="106"/>
+      <c r="DS1" s="106"/>
+      <c r="DT1" s="106"/>
+      <c r="DU1" s="106"/>
+      <c r="DV1" s="106"/>
+      <c r="DW1" s="106"/>
+      <c r="DX1" s="106"/>
+      <c r="DY1" s="106"/>
+      <c r="DZ1" s="106"/>
+      <c r="EA1" s="106"/>
+      <c r="EB1" s="106"/>
+      <c r="EC1" s="106"/>
+      <c r="ED1" s="106"/>
+      <c r="EE1" s="106"/>
+      <c r="EF1" s="106"/>
+      <c r="EG1" s="106"/>
+      <c r="EH1" s="106"/>
+      <c r="EI1" s="106"/>
+      <c r="EJ1" s="106"/>
+      <c r="EK1" s="106"/>
+      <c r="EL1" s="106"/>
+      <c r="EM1" s="106"/>
+      <c r="EN1" s="106"/>
+      <c r="EO1" s="106"/>
+      <c r="EP1" s="106"/>
+      <c r="EQ1" s="106"/>
+      <c r="ER1" s="106"/>
+      <c r="ES1" s="106"/>
+      <c r="ET1" s="106"/>
+      <c r="EU1" s="106"/>
+      <c r="EV1" s="106"/>
+      <c r="EW1" s="106"/>
+      <c r="EX1" s="106"/>
+      <c r="EY1" s="106"/>
+      <c r="EZ1" s="106"/>
+      <c r="FA1" s="106"/>
+      <c r="FB1" s="106"/>
+      <c r="FC1" s="106"/>
+      <c r="FD1" s="106"/>
+      <c r="FE1" s="106"/>
+      <c r="FF1" s="106"/>
+      <c r="FG1" s="106"/>
+      <c r="FH1" s="106"/>
+      <c r="FI1" s="106"/>
+      <c r="FJ1" s="106"/>
+      <c r="FK1" s="106"/>
+      <c r="FL1" s="106"/>
+      <c r="FM1" s="106"/>
+      <c r="FN1" s="106"/>
+      <c r="FO1" s="106"/>
+      <c r="FP1" s="106"/>
+      <c r="FQ1" s="106"/>
+      <c r="FR1" s="106"/>
+      <c r="FS1" s="106"/>
+      <c r="FT1" s="106"/>
+      <c r="FU1" s="106"/>
+      <c r="FV1" s="106"/>
+      <c r="FW1" s="106"/>
+      <c r="FX1" s="106"/>
+      <c r="FY1" s="106"/>
+      <c r="FZ1" s="106"/>
+      <c r="GA1" s="106"/>
+      <c r="GB1" s="106"/>
+      <c r="GC1" s="106"/>
+      <c r="GD1" s="106"/>
+      <c r="GE1" s="106"/>
+      <c r="GF1" s="106"/>
+      <c r="GG1" s="106"/>
+      <c r="GH1" s="106"/>
+      <c r="GI1" s="106"/>
+      <c r="GJ1" s="106"/>
+      <c r="GK1" s="106"/>
+      <c r="GL1" s="106"/>
+      <c r="GM1" s="106"/>
+      <c r="GN1" s="106"/>
+      <c r="GO1" s="106"/>
+      <c r="GP1" s="106"/>
+      <c r="GQ1" s="106"/>
+      <c r="GR1" s="106"/>
+      <c r="GS1" s="106"/>
+      <c r="GT1" s="106"/>
+      <c r="GU1" s="106"/>
+      <c r="GV1" s="106"/>
+      <c r="GW1" s="106"/>
+      <c r="GX1" s="106"/>
+      <c r="GY1" s="106"/>
+      <c r="GZ1" s="106"/>
+      <c r="HA1" s="106"/>
+      <c r="HB1" s="106"/>
+      <c r="HC1" s="106"/>
+      <c r="HD1" s="106"/>
+      <c r="HE1" s="106"/>
+      <c r="HF1" s="106"/>
+      <c r="HG1" s="106"/>
+      <c r="HH1" s="106"/>
+      <c r="HI1" s="106"/>
+      <c r="HJ1" s="106"/>
+      <c r="HK1" s="106"/>
+      <c r="HL1" s="106"/>
+      <c r="HM1" s="106"/>
+      <c r="HN1" s="106"/>
+      <c r="HO1" s="106"/>
+      <c r="HP1" s="106"/>
+      <c r="HQ1" s="106"/>
+      <c r="HR1" s="106"/>
+      <c r="HS1" s="106"/>
+      <c r="HT1" s="106"/>
+      <c r="HU1" s="106"/>
+      <c r="HV1" s="106"/>
+      <c r="HW1" s="106"/>
+      <c r="HX1" s="106"/>
+      <c r="HY1" s="106"/>
+      <c r="HZ1" s="106"/>
+      <c r="IA1" s="106"/>
+      <c r="IB1" s="106"/>
+      <c r="IC1" s="106"/>
+      <c r="ID1" s="106"/>
+      <c r="IE1" s="106"/>
+      <c r="IF1" s="106"/>
+      <c r="IG1" s="106"/>
+      <c r="IH1" s="106"/>
+      <c r="II1" s="106"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="106"/>
+      <c r="IL1" s="106"/>
+      <c r="IM1" s="106"/>
+      <c r="IN1" s="106"/>
+      <c r="IO1" s="106"/>
+      <c r="IP1" s="106"/>
+      <c r="IQ1" s="106"/>
+      <c r="IR1" s="106"/>
+      <c r="IS1" s="106"/>
+      <c r="IT1" s="106"/>
+      <c r="IU1" s="106"/>
+      <c r="IV1" s="106"/>
+      <c r="IW1" s="106"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
         <v>31</v>
       </c>
@@ -23436,8 +30151,257 @@
       <c r="H2" s="108" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" s="112" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="106"/>
+      <c r="R2" s="106"/>
+      <c r="S2" s="106"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="106"/>
+      <c r="W2" s="106"/>
+      <c r="X2" s="106"/>
+      <c r="Y2" s="106"/>
+      <c r="Z2" s="106"/>
+      <c r="AA2" s="106"/>
+      <c r="AB2" s="106"/>
+      <c r="AC2" s="106"/>
+      <c r="AD2" s="106"/>
+      <c r="AE2" s="106"/>
+      <c r="AF2" s="106"/>
+      <c r="AG2" s="106"/>
+      <c r="AH2" s="106"/>
+      <c r="AI2" s="106"/>
+      <c r="AJ2" s="106"/>
+      <c r="AK2" s="106"/>
+      <c r="AL2" s="106"/>
+      <c r="AM2" s="106"/>
+      <c r="AN2" s="106"/>
+      <c r="AO2" s="106"/>
+      <c r="AP2" s="106"/>
+      <c r="AQ2" s="106"/>
+      <c r="AR2" s="106"/>
+      <c r="AS2" s="106"/>
+      <c r="AT2" s="106"/>
+      <c r="AU2" s="106"/>
+      <c r="AV2" s="106"/>
+      <c r="AW2" s="106"/>
+      <c r="AX2" s="106"/>
+      <c r="AY2" s="106"/>
+      <c r="AZ2" s="106"/>
+      <c r="BA2" s="106"/>
+      <c r="BB2" s="106"/>
+      <c r="BC2" s="106"/>
+      <c r="BD2" s="106"/>
+      <c r="BE2" s="106"/>
+      <c r="BF2" s="106"/>
+      <c r="BG2" s="106"/>
+      <c r="BH2" s="106"/>
+      <c r="BI2" s="106"/>
+      <c r="BJ2" s="106"/>
+      <c r="BK2" s="106"/>
+      <c r="BL2" s="106"/>
+      <c r="BM2" s="106"/>
+      <c r="BN2" s="106"/>
+      <c r="BO2" s="106"/>
+      <c r="BP2" s="106"/>
+      <c r="BQ2" s="106"/>
+      <c r="BR2" s="106"/>
+      <c r="BS2" s="106"/>
+      <c r="BT2" s="106"/>
+      <c r="BU2" s="106"/>
+      <c r="BV2" s="106"/>
+      <c r="BW2" s="106"/>
+      <c r="BX2" s="106"/>
+      <c r="BY2" s="106"/>
+      <c r="BZ2" s="106"/>
+      <c r="CA2" s="106"/>
+      <c r="CB2" s="106"/>
+      <c r="CC2" s="106"/>
+      <c r="CD2" s="106"/>
+      <c r="CE2" s="106"/>
+      <c r="CF2" s="106"/>
+      <c r="CG2" s="106"/>
+      <c r="CH2" s="106"/>
+      <c r="CI2" s="106"/>
+      <c r="CJ2" s="106"/>
+      <c r="CK2" s="106"/>
+      <c r="CL2" s="106"/>
+      <c r="CM2" s="106"/>
+      <c r="CN2" s="106"/>
+      <c r="CO2" s="106"/>
+      <c r="CP2" s="106"/>
+      <c r="CQ2" s="106"/>
+      <c r="CR2" s="106"/>
+      <c r="CS2" s="106"/>
+      <c r="CT2" s="106"/>
+      <c r="CU2" s="106"/>
+      <c r="CV2" s="106"/>
+      <c r="CW2" s="106"/>
+      <c r="CX2" s="106"/>
+      <c r="CY2" s="106"/>
+      <c r="CZ2" s="106"/>
+      <c r="DA2" s="106"/>
+      <c r="DB2" s="106"/>
+      <c r="DC2" s="106"/>
+      <c r="DD2" s="106"/>
+      <c r="DE2" s="106"/>
+      <c r="DF2" s="106"/>
+      <c r="DG2" s="106"/>
+      <c r="DH2" s="106"/>
+      <c r="DI2" s="106"/>
+      <c r="DJ2" s="106"/>
+      <c r="DK2" s="106"/>
+      <c r="DL2" s="106"/>
+      <c r="DM2" s="106"/>
+      <c r="DN2" s="106"/>
+      <c r="DO2" s="106"/>
+      <c r="DP2" s="106"/>
+      <c r="DQ2" s="106"/>
+      <c r="DR2" s="106"/>
+      <c r="DS2" s="106"/>
+      <c r="DT2" s="106"/>
+      <c r="DU2" s="106"/>
+      <c r="DV2" s="106"/>
+      <c r="DW2" s="106"/>
+      <c r="DX2" s="106"/>
+      <c r="DY2" s="106"/>
+      <c r="DZ2" s="106"/>
+      <c r="EA2" s="106"/>
+      <c r="EB2" s="106"/>
+      <c r="EC2" s="106"/>
+      <c r="ED2" s="106"/>
+      <c r="EE2" s="106"/>
+      <c r="EF2" s="106"/>
+      <c r="EG2" s="106"/>
+      <c r="EH2" s="106"/>
+      <c r="EI2" s="106"/>
+      <c r="EJ2" s="106"/>
+      <c r="EK2" s="106"/>
+      <c r="EL2" s="106"/>
+      <c r="EM2" s="106"/>
+      <c r="EN2" s="106"/>
+      <c r="EO2" s="106"/>
+      <c r="EP2" s="106"/>
+      <c r="EQ2" s="106"/>
+      <c r="ER2" s="106"/>
+      <c r="ES2" s="106"/>
+      <c r="ET2" s="106"/>
+      <c r="EU2" s="106"/>
+      <c r="EV2" s="106"/>
+      <c r="EW2" s="106"/>
+      <c r="EX2" s="106"/>
+      <c r="EY2" s="106"/>
+      <c r="EZ2" s="106"/>
+      <c r="FA2" s="106"/>
+      <c r="FB2" s="106"/>
+      <c r="FC2" s="106"/>
+      <c r="FD2" s="106"/>
+      <c r="FE2" s="106"/>
+      <c r="FF2" s="106"/>
+      <c r="FG2" s="106"/>
+      <c r="FH2" s="106"/>
+      <c r="FI2" s="106"/>
+      <c r="FJ2" s="106"/>
+      <c r="FK2" s="106"/>
+      <c r="FL2" s="106"/>
+      <c r="FM2" s="106"/>
+      <c r="FN2" s="106"/>
+      <c r="FO2" s="106"/>
+      <c r="FP2" s="106"/>
+      <c r="FQ2" s="106"/>
+      <c r="FR2" s="106"/>
+      <c r="FS2" s="106"/>
+      <c r="FT2" s="106"/>
+      <c r="FU2" s="106"/>
+      <c r="FV2" s="106"/>
+      <c r="FW2" s="106"/>
+      <c r="FX2" s="106"/>
+      <c r="FY2" s="106"/>
+      <c r="FZ2" s="106"/>
+      <c r="GA2" s="106"/>
+      <c r="GB2" s="106"/>
+      <c r="GC2" s="106"/>
+      <c r="GD2" s="106"/>
+      <c r="GE2" s="106"/>
+      <c r="GF2" s="106"/>
+      <c r="GG2" s="106"/>
+      <c r="GH2" s="106"/>
+      <c r="GI2" s="106"/>
+      <c r="GJ2" s="106"/>
+      <c r="GK2" s="106"/>
+      <c r="GL2" s="106"/>
+      <c r="GM2" s="106"/>
+      <c r="GN2" s="106"/>
+      <c r="GO2" s="106"/>
+      <c r="GP2" s="106"/>
+      <c r="GQ2" s="106"/>
+      <c r="GR2" s="106"/>
+      <c r="GS2" s="106"/>
+      <c r="GT2" s="106"/>
+      <c r="GU2" s="106"/>
+      <c r="GV2" s="106"/>
+      <c r="GW2" s="106"/>
+      <c r="GX2" s="106"/>
+      <c r="GY2" s="106"/>
+      <c r="GZ2" s="106"/>
+      <c r="HA2" s="106"/>
+      <c r="HB2" s="106"/>
+      <c r="HC2" s="106"/>
+      <c r="HD2" s="106"/>
+      <c r="HE2" s="106"/>
+      <c r="HF2" s="106"/>
+      <c r="HG2" s="106"/>
+      <c r="HH2" s="106"/>
+      <c r="HI2" s="106"/>
+      <c r="HJ2" s="106"/>
+      <c r="HK2" s="106"/>
+      <c r="HL2" s="106"/>
+      <c r="HM2" s="106"/>
+      <c r="HN2" s="106"/>
+      <c r="HO2" s="106"/>
+      <c r="HP2" s="106"/>
+      <c r="HQ2" s="106"/>
+      <c r="HR2" s="106"/>
+      <c r="HS2" s="106"/>
+      <c r="HT2" s="106"/>
+      <c r="HU2" s="106"/>
+      <c r="HV2" s="106"/>
+      <c r="HW2" s="106"/>
+      <c r="HX2" s="106"/>
+      <c r="HY2" s="106"/>
+      <c r="HZ2" s="106"/>
+      <c r="IA2" s="106"/>
+      <c r="IB2" s="106"/>
+      <c r="IC2" s="106"/>
+      <c r="ID2" s="106"/>
+      <c r="IE2" s="106"/>
+      <c r="IF2" s="106"/>
+      <c r="IG2" s="106"/>
+      <c r="IH2" s="106"/>
+      <c r="II2" s="106"/>
+      <c r="IJ2" s="106"/>
+      <c r="IK2" s="106"/>
+      <c r="IL2" s="106"/>
+      <c r="IM2" s="106"/>
+      <c r="IN2" s="106"/>
+      <c r="IO2" s="106"/>
+      <c r="IP2" s="106"/>
+      <c r="IQ2" s="106"/>
+      <c r="IR2" s="106"/>
+      <c r="IS2" s="106"/>
+      <c r="IT2" s="106"/>
+      <c r="IU2" s="106"/>
+      <c r="IV2" s="106"/>
+      <c r="IW2" s="106"/>
+    </row>
+    <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="107"/>
       <c r="B3" s="108"/>
       <c r="C3" s="109"/>
@@ -23448,6 +30412,255 @@
         <v>37</v>
       </c>
       <c r="H3" s="108"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
+      <c r="L3" s="112"/>
+      <c r="M3" s="112"/>
+      <c r="N3" s="112"/>
+      <c r="O3" s="112"/>
+      <c r="P3" s="112"/>
+      <c r="Q3" s="112"/>
+      <c r="R3" s="112"/>
+      <c r="S3" s="112"/>
+      <c r="T3" s="112"/>
+      <c r="U3" s="112"/>
+      <c r="V3" s="112"/>
+      <c r="W3" s="112"/>
+      <c r="X3" s="112"/>
+      <c r="Y3" s="112"/>
+      <c r="Z3" s="112"/>
+      <c r="AA3" s="112"/>
+      <c r="AB3" s="112"/>
+      <c r="AC3" s="112"/>
+      <c r="AD3" s="112"/>
+      <c r="AE3" s="112"/>
+      <c r="AF3" s="112"/>
+      <c r="AG3" s="112"/>
+      <c r="AH3" s="112"/>
+      <c r="AI3" s="112"/>
+      <c r="AJ3" s="112"/>
+      <c r="AK3" s="112"/>
+      <c r="AL3" s="112"/>
+      <c r="AM3" s="112"/>
+      <c r="AN3" s="112"/>
+      <c r="AO3" s="112"/>
+      <c r="AP3" s="112"/>
+      <c r="AQ3" s="112"/>
+      <c r="AR3" s="112"/>
+      <c r="AS3" s="112"/>
+      <c r="AT3" s="112"/>
+      <c r="AU3" s="112"/>
+      <c r="AV3" s="112"/>
+      <c r="AW3" s="112"/>
+      <c r="AX3" s="112"/>
+      <c r="AY3" s="112"/>
+      <c r="AZ3" s="112"/>
+      <c r="BA3" s="112"/>
+      <c r="BB3" s="112"/>
+      <c r="BC3" s="112"/>
+      <c r="BD3" s="112"/>
+      <c r="BE3" s="112"/>
+      <c r="BF3" s="112"/>
+      <c r="BG3" s="112"/>
+      <c r="BH3" s="112"/>
+      <c r="BI3" s="112"/>
+      <c r="BJ3" s="112"/>
+      <c r="BK3" s="112"/>
+      <c r="BL3" s="112"/>
+      <c r="BM3" s="112"/>
+      <c r="BN3" s="112"/>
+      <c r="BO3" s="112"/>
+      <c r="BP3" s="112"/>
+      <c r="BQ3" s="112"/>
+      <c r="BR3" s="112"/>
+      <c r="BS3" s="112"/>
+      <c r="BT3" s="112"/>
+      <c r="BU3" s="112"/>
+      <c r="BV3" s="112"/>
+      <c r="BW3" s="112"/>
+      <c r="BX3" s="112"/>
+      <c r="BY3" s="112"/>
+      <c r="BZ3" s="112"/>
+      <c r="CA3" s="112"/>
+      <c r="CB3" s="112"/>
+      <c r="CC3" s="112"/>
+      <c r="CD3" s="112"/>
+      <c r="CE3" s="112"/>
+      <c r="CF3" s="112"/>
+      <c r="CG3" s="112"/>
+      <c r="CH3" s="112"/>
+      <c r="CI3" s="112"/>
+      <c r="CJ3" s="112"/>
+      <c r="CK3" s="112"/>
+      <c r="CL3" s="112"/>
+      <c r="CM3" s="112"/>
+      <c r="CN3" s="112"/>
+      <c r="CO3" s="112"/>
+      <c r="CP3" s="112"/>
+      <c r="CQ3" s="112"/>
+      <c r="CR3" s="112"/>
+      <c r="CS3" s="112"/>
+      <c r="CT3" s="112"/>
+      <c r="CU3" s="112"/>
+      <c r="CV3" s="112"/>
+      <c r="CW3" s="112"/>
+      <c r="CX3" s="112"/>
+      <c r="CY3" s="112"/>
+      <c r="CZ3" s="112"/>
+      <c r="DA3" s="112"/>
+      <c r="DB3" s="112"/>
+      <c r="DC3" s="112"/>
+      <c r="DD3" s="112"/>
+      <c r="DE3" s="112"/>
+      <c r="DF3" s="112"/>
+      <c r="DG3" s="112"/>
+      <c r="DH3" s="112"/>
+      <c r="DI3" s="112"/>
+      <c r="DJ3" s="112"/>
+      <c r="DK3" s="112"/>
+      <c r="DL3" s="112"/>
+      <c r="DM3" s="112"/>
+      <c r="DN3" s="112"/>
+      <c r="DO3" s="112"/>
+      <c r="DP3" s="112"/>
+      <c r="DQ3" s="112"/>
+      <c r="DR3" s="112"/>
+      <c r="DS3" s="112"/>
+      <c r="DT3" s="112"/>
+      <c r="DU3" s="112"/>
+      <c r="DV3" s="112"/>
+      <c r="DW3" s="112"/>
+      <c r="DX3" s="112"/>
+      <c r="DY3" s="112"/>
+      <c r="DZ3" s="112"/>
+      <c r="EA3" s="112"/>
+      <c r="EB3" s="112"/>
+      <c r="EC3" s="112"/>
+      <c r="ED3" s="112"/>
+      <c r="EE3" s="112"/>
+      <c r="EF3" s="112"/>
+      <c r="EG3" s="112"/>
+      <c r="EH3" s="112"/>
+      <c r="EI3" s="112"/>
+      <c r="EJ3" s="112"/>
+      <c r="EK3" s="112"/>
+      <c r="EL3" s="112"/>
+      <c r="EM3" s="112"/>
+      <c r="EN3" s="112"/>
+      <c r="EO3" s="112"/>
+      <c r="EP3" s="112"/>
+      <c r="EQ3" s="112"/>
+      <c r="ER3" s="112"/>
+      <c r="ES3" s="112"/>
+      <c r="ET3" s="112"/>
+      <c r="EU3" s="112"/>
+      <c r="EV3" s="112"/>
+      <c r="EW3" s="112"/>
+      <c r="EX3" s="112"/>
+      <c r="EY3" s="112"/>
+      <c r="EZ3" s="112"/>
+      <c r="FA3" s="112"/>
+      <c r="FB3" s="112"/>
+      <c r="FC3" s="112"/>
+      <c r="FD3" s="112"/>
+      <c r="FE3" s="112"/>
+      <c r="FF3" s="112"/>
+      <c r="FG3" s="112"/>
+      <c r="FH3" s="112"/>
+      <c r="FI3" s="112"/>
+      <c r="FJ3" s="112"/>
+      <c r="FK3" s="112"/>
+      <c r="FL3" s="112"/>
+      <c r="FM3" s="112"/>
+      <c r="FN3" s="112"/>
+      <c r="FO3" s="112"/>
+      <c r="FP3" s="112"/>
+      <c r="FQ3" s="112"/>
+      <c r="FR3" s="112"/>
+      <c r="FS3" s="112"/>
+      <c r="FT3" s="112"/>
+      <c r="FU3" s="112"/>
+      <c r="FV3" s="112"/>
+      <c r="FW3" s="112"/>
+      <c r="FX3" s="112"/>
+      <c r="FY3" s="112"/>
+      <c r="FZ3" s="112"/>
+      <c r="GA3" s="112"/>
+      <c r="GB3" s="112"/>
+      <c r="GC3" s="112"/>
+      <c r="GD3" s="112"/>
+      <c r="GE3" s="112"/>
+      <c r="GF3" s="112"/>
+      <c r="GG3" s="112"/>
+      <c r="GH3" s="112"/>
+      <c r="GI3" s="112"/>
+      <c r="GJ3" s="112"/>
+      <c r="GK3" s="112"/>
+      <c r="GL3" s="112"/>
+      <c r="GM3" s="112"/>
+      <c r="GN3" s="112"/>
+      <c r="GO3" s="112"/>
+      <c r="GP3" s="112"/>
+      <c r="GQ3" s="112"/>
+      <c r="GR3" s="112"/>
+      <c r="GS3" s="112"/>
+      <c r="GT3" s="112"/>
+      <c r="GU3" s="112"/>
+      <c r="GV3" s="112"/>
+      <c r="GW3" s="112"/>
+      <c r="GX3" s="112"/>
+      <c r="GY3" s="112"/>
+      <c r="GZ3" s="112"/>
+      <c r="HA3" s="112"/>
+      <c r="HB3" s="112"/>
+      <c r="HC3" s="112"/>
+      <c r="HD3" s="112"/>
+      <c r="HE3" s="112"/>
+      <c r="HF3" s="112"/>
+      <c r="HG3" s="112"/>
+      <c r="HH3" s="112"/>
+      <c r="HI3" s="112"/>
+      <c r="HJ3" s="112"/>
+      <c r="HK3" s="112"/>
+      <c r="HL3" s="112"/>
+      <c r="HM3" s="112"/>
+      <c r="HN3" s="112"/>
+      <c r="HO3" s="112"/>
+      <c r="HP3" s="112"/>
+      <c r="HQ3" s="112"/>
+      <c r="HR3" s="112"/>
+      <c r="HS3" s="112"/>
+      <c r="HT3" s="112"/>
+      <c r="HU3" s="112"/>
+      <c r="HV3" s="112"/>
+      <c r="HW3" s="112"/>
+      <c r="HX3" s="112"/>
+      <c r="HY3" s="112"/>
+      <c r="HZ3" s="112"/>
+      <c r="IA3" s="112"/>
+      <c r="IB3" s="112"/>
+      <c r="IC3" s="112"/>
+      <c r="ID3" s="112"/>
+      <c r="IE3" s="112"/>
+      <c r="IF3" s="112"/>
+      <c r="IG3" s="112"/>
+      <c r="IH3" s="112"/>
+      <c r="II3" s="112"/>
+      <c r="IJ3" s="112"/>
+      <c r="IK3" s="112"/>
+      <c r="IL3" s="112"/>
+      <c r="IM3" s="112"/>
+      <c r="IN3" s="112"/>
+      <c r="IO3" s="112"/>
+      <c r="IP3" s="112"/>
+      <c r="IQ3" s="112"/>
+      <c r="IR3" s="112"/>
+      <c r="IS3" s="112"/>
+      <c r="IT3" s="112"/>
+      <c r="IU3" s="112"/>
+      <c r="IV3" s="112"/>
+      <c r="IW3" s="112"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="107"/>
@@ -25472,8 +32685,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW201"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="98" width="9.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="99" width="20.15"/>
@@ -25485,7 +32698,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="9" style="102" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="106" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="103" t="s">
         <v>29</v>
       </c>
@@ -25507,8 +32720,257 @@
         <f aca="false">SUM(H5:H500)</f>
         <v>3000</v>
       </c>
-    </row>
-    <row r="2" s="106" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
+      <c r="AC1" s="106"/>
+      <c r="AD1" s="106"/>
+      <c r="AE1" s="106"/>
+      <c r="AF1" s="106"/>
+      <c r="AG1" s="106"/>
+      <c r="AH1" s="106"/>
+      <c r="AI1" s="106"/>
+      <c r="AJ1" s="106"/>
+      <c r="AK1" s="106"/>
+      <c r="AL1" s="106"/>
+      <c r="AM1" s="106"/>
+      <c r="AN1" s="106"/>
+      <c r="AO1" s="106"/>
+      <c r="AP1" s="106"/>
+      <c r="AQ1" s="106"/>
+      <c r="AR1" s="106"/>
+      <c r="AS1" s="106"/>
+      <c r="AT1" s="106"/>
+      <c r="AU1" s="106"/>
+      <c r="AV1" s="106"/>
+      <c r="AW1" s="106"/>
+      <c r="AX1" s="106"/>
+      <c r="AY1" s="106"/>
+      <c r="AZ1" s="106"/>
+      <c r="BA1" s="106"/>
+      <c r="BB1" s="106"/>
+      <c r="BC1" s="106"/>
+      <c r="BD1" s="106"/>
+      <c r="BE1" s="106"/>
+      <c r="BF1" s="106"/>
+      <c r="BG1" s="106"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="106"/>
+      <c r="BJ1" s="106"/>
+      <c r="BK1" s="106"/>
+      <c r="BL1" s="106"/>
+      <c r="BM1" s="106"/>
+      <c r="BN1" s="106"/>
+      <c r="BO1" s="106"/>
+      <c r="BP1" s="106"/>
+      <c r="BQ1" s="106"/>
+      <c r="BR1" s="106"/>
+      <c r="BS1" s="106"/>
+      <c r="BT1" s="106"/>
+      <c r="BU1" s="106"/>
+      <c r="BV1" s="106"/>
+      <c r="BW1" s="106"/>
+      <c r="BX1" s="106"/>
+      <c r="BY1" s="106"/>
+      <c r="BZ1" s="106"/>
+      <c r="CA1" s="106"/>
+      <c r="CB1" s="106"/>
+      <c r="CC1" s="106"/>
+      <c r="CD1" s="106"/>
+      <c r="CE1" s="106"/>
+      <c r="CF1" s="106"/>
+      <c r="CG1" s="106"/>
+      <c r="CH1" s="106"/>
+      <c r="CI1" s="106"/>
+      <c r="CJ1" s="106"/>
+      <c r="CK1" s="106"/>
+      <c r="CL1" s="106"/>
+      <c r="CM1" s="106"/>
+      <c r="CN1" s="106"/>
+      <c r="CO1" s="106"/>
+      <c r="CP1" s="106"/>
+      <c r="CQ1" s="106"/>
+      <c r="CR1" s="106"/>
+      <c r="CS1" s="106"/>
+      <c r="CT1" s="106"/>
+      <c r="CU1" s="106"/>
+      <c r="CV1" s="106"/>
+      <c r="CW1" s="106"/>
+      <c r="CX1" s="106"/>
+      <c r="CY1" s="106"/>
+      <c r="CZ1" s="106"/>
+      <c r="DA1" s="106"/>
+      <c r="DB1" s="106"/>
+      <c r="DC1" s="106"/>
+      <c r="DD1" s="106"/>
+      <c r="DE1" s="106"/>
+      <c r="DF1" s="106"/>
+      <c r="DG1" s="106"/>
+      <c r="DH1" s="106"/>
+      <c r="DI1" s="106"/>
+      <c r="DJ1" s="106"/>
+      <c r="DK1" s="106"/>
+      <c r="DL1" s="106"/>
+      <c r="DM1" s="106"/>
+      <c r="DN1" s="106"/>
+      <c r="DO1" s="106"/>
+      <c r="DP1" s="106"/>
+      <c r="DQ1" s="106"/>
+      <c r="DR1" s="106"/>
+      <c r="DS1" s="106"/>
+      <c r="DT1" s="106"/>
+      <c r="DU1" s="106"/>
+      <c r="DV1" s="106"/>
+      <c r="DW1" s="106"/>
+      <c r="DX1" s="106"/>
+      <c r="DY1" s="106"/>
+      <c r="DZ1" s="106"/>
+      <c r="EA1" s="106"/>
+      <c r="EB1" s="106"/>
+      <c r="EC1" s="106"/>
+      <c r="ED1" s="106"/>
+      <c r="EE1" s="106"/>
+      <c r="EF1" s="106"/>
+      <c r="EG1" s="106"/>
+      <c r="EH1" s="106"/>
+      <c r="EI1" s="106"/>
+      <c r="EJ1" s="106"/>
+      <c r="EK1" s="106"/>
+      <c r="EL1" s="106"/>
+      <c r="EM1" s="106"/>
+      <c r="EN1" s="106"/>
+      <c r="EO1" s="106"/>
+      <c r="EP1" s="106"/>
+      <c r="EQ1" s="106"/>
+      <c r="ER1" s="106"/>
+      <c r="ES1" s="106"/>
+      <c r="ET1" s="106"/>
+      <c r="EU1" s="106"/>
+      <c r="EV1" s="106"/>
+      <c r="EW1" s="106"/>
+      <c r="EX1" s="106"/>
+      <c r="EY1" s="106"/>
+      <c r="EZ1" s="106"/>
+      <c r="FA1" s="106"/>
+      <c r="FB1" s="106"/>
+      <c r="FC1" s="106"/>
+      <c r="FD1" s="106"/>
+      <c r="FE1" s="106"/>
+      <c r="FF1" s="106"/>
+      <c r="FG1" s="106"/>
+      <c r="FH1" s="106"/>
+      <c r="FI1" s="106"/>
+      <c r="FJ1" s="106"/>
+      <c r="FK1" s="106"/>
+      <c r="FL1" s="106"/>
+      <c r="FM1" s="106"/>
+      <c r="FN1" s="106"/>
+      <c r="FO1" s="106"/>
+      <c r="FP1" s="106"/>
+      <c r="FQ1" s="106"/>
+      <c r="FR1" s="106"/>
+      <c r="FS1" s="106"/>
+      <c r="FT1" s="106"/>
+      <c r="FU1" s="106"/>
+      <c r="FV1" s="106"/>
+      <c r="FW1" s="106"/>
+      <c r="FX1" s="106"/>
+      <c r="FY1" s="106"/>
+      <c r="FZ1" s="106"/>
+      <c r="GA1" s="106"/>
+      <c r="GB1" s="106"/>
+      <c r="GC1" s="106"/>
+      <c r="GD1" s="106"/>
+      <c r="GE1" s="106"/>
+      <c r="GF1" s="106"/>
+      <c r="GG1" s="106"/>
+      <c r="GH1" s="106"/>
+      <c r="GI1" s="106"/>
+      <c r="GJ1" s="106"/>
+      <c r="GK1" s="106"/>
+      <c r="GL1" s="106"/>
+      <c r="GM1" s="106"/>
+      <c r="GN1" s="106"/>
+      <c r="GO1" s="106"/>
+      <c r="GP1" s="106"/>
+      <c r="GQ1" s="106"/>
+      <c r="GR1" s="106"/>
+      <c r="GS1" s="106"/>
+      <c r="GT1" s="106"/>
+      <c r="GU1" s="106"/>
+      <c r="GV1" s="106"/>
+      <c r="GW1" s="106"/>
+      <c r="GX1" s="106"/>
+      <c r="GY1" s="106"/>
+      <c r="GZ1" s="106"/>
+      <c r="HA1" s="106"/>
+      <c r="HB1" s="106"/>
+      <c r="HC1" s="106"/>
+      <c r="HD1" s="106"/>
+      <c r="HE1" s="106"/>
+      <c r="HF1" s="106"/>
+      <c r="HG1" s="106"/>
+      <c r="HH1" s="106"/>
+      <c r="HI1" s="106"/>
+      <c r="HJ1" s="106"/>
+      <c r="HK1" s="106"/>
+      <c r="HL1" s="106"/>
+      <c r="HM1" s="106"/>
+      <c r="HN1" s="106"/>
+      <c r="HO1" s="106"/>
+      <c r="HP1" s="106"/>
+      <c r="HQ1" s="106"/>
+      <c r="HR1" s="106"/>
+      <c r="HS1" s="106"/>
+      <c r="HT1" s="106"/>
+      <c r="HU1" s="106"/>
+      <c r="HV1" s="106"/>
+      <c r="HW1" s="106"/>
+      <c r="HX1" s="106"/>
+      <c r="HY1" s="106"/>
+      <c r="HZ1" s="106"/>
+      <c r="IA1" s="106"/>
+      <c r="IB1" s="106"/>
+      <c r="IC1" s="106"/>
+      <c r="ID1" s="106"/>
+      <c r="IE1" s="106"/>
+      <c r="IF1" s="106"/>
+      <c r="IG1" s="106"/>
+      <c r="IH1" s="106"/>
+      <c r="II1" s="106"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="106"/>
+      <c r="IL1" s="106"/>
+      <c r="IM1" s="106"/>
+      <c r="IN1" s="106"/>
+      <c r="IO1" s="106"/>
+      <c r="IP1" s="106"/>
+      <c r="IQ1" s="106"/>
+      <c r="IR1" s="106"/>
+      <c r="IS1" s="106"/>
+      <c r="IT1" s="106"/>
+      <c r="IU1" s="106"/>
+      <c r="IV1" s="106"/>
+      <c r="IW1" s="106"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
         <v>31</v>
       </c>
@@ -25532,8 +32994,257 @@
       <c r="H2" s="108" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" s="112" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="106"/>
+      <c r="R2" s="106"/>
+      <c r="S2" s="106"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="106"/>
+      <c r="W2" s="106"/>
+      <c r="X2" s="106"/>
+      <c r="Y2" s="106"/>
+      <c r="Z2" s="106"/>
+      <c r="AA2" s="106"/>
+      <c r="AB2" s="106"/>
+      <c r="AC2" s="106"/>
+      <c r="AD2" s="106"/>
+      <c r="AE2" s="106"/>
+      <c r="AF2" s="106"/>
+      <c r="AG2" s="106"/>
+      <c r="AH2" s="106"/>
+      <c r="AI2" s="106"/>
+      <c r="AJ2" s="106"/>
+      <c r="AK2" s="106"/>
+      <c r="AL2" s="106"/>
+      <c r="AM2" s="106"/>
+      <c r="AN2" s="106"/>
+      <c r="AO2" s="106"/>
+      <c r="AP2" s="106"/>
+      <c r="AQ2" s="106"/>
+      <c r="AR2" s="106"/>
+      <c r="AS2" s="106"/>
+      <c r="AT2" s="106"/>
+      <c r="AU2" s="106"/>
+      <c r="AV2" s="106"/>
+      <c r="AW2" s="106"/>
+      <c r="AX2" s="106"/>
+      <c r="AY2" s="106"/>
+      <c r="AZ2" s="106"/>
+      <c r="BA2" s="106"/>
+      <c r="BB2" s="106"/>
+      <c r="BC2" s="106"/>
+      <c r="BD2" s="106"/>
+      <c r="BE2" s="106"/>
+      <c r="BF2" s="106"/>
+      <c r="BG2" s="106"/>
+      <c r="BH2" s="106"/>
+      <c r="BI2" s="106"/>
+      <c r="BJ2" s="106"/>
+      <c r="BK2" s="106"/>
+      <c r="BL2" s="106"/>
+      <c r="BM2" s="106"/>
+      <c r="BN2" s="106"/>
+      <c r="BO2" s="106"/>
+      <c r="BP2" s="106"/>
+      <c r="BQ2" s="106"/>
+      <c r="BR2" s="106"/>
+      <c r="BS2" s="106"/>
+      <c r="BT2" s="106"/>
+      <c r="BU2" s="106"/>
+      <c r="BV2" s="106"/>
+      <c r="BW2" s="106"/>
+      <c r="BX2" s="106"/>
+      <c r="BY2" s="106"/>
+      <c r="BZ2" s="106"/>
+      <c r="CA2" s="106"/>
+      <c r="CB2" s="106"/>
+      <c r="CC2" s="106"/>
+      <c r="CD2" s="106"/>
+      <c r="CE2" s="106"/>
+      <c r="CF2" s="106"/>
+      <c r="CG2" s="106"/>
+      <c r="CH2" s="106"/>
+      <c r="CI2" s="106"/>
+      <c r="CJ2" s="106"/>
+      <c r="CK2" s="106"/>
+      <c r="CL2" s="106"/>
+      <c r="CM2" s="106"/>
+      <c r="CN2" s="106"/>
+      <c r="CO2" s="106"/>
+      <c r="CP2" s="106"/>
+      <c r="CQ2" s="106"/>
+      <c r="CR2" s="106"/>
+      <c r="CS2" s="106"/>
+      <c r="CT2" s="106"/>
+      <c r="CU2" s="106"/>
+      <c r="CV2" s="106"/>
+      <c r="CW2" s="106"/>
+      <c r="CX2" s="106"/>
+      <c r="CY2" s="106"/>
+      <c r="CZ2" s="106"/>
+      <c r="DA2" s="106"/>
+      <c r="DB2" s="106"/>
+      <c r="DC2" s="106"/>
+      <c r="DD2" s="106"/>
+      <c r="DE2" s="106"/>
+      <c r="DF2" s="106"/>
+      <c r="DG2" s="106"/>
+      <c r="DH2" s="106"/>
+      <c r="DI2" s="106"/>
+      <c r="DJ2" s="106"/>
+      <c r="DK2" s="106"/>
+      <c r="DL2" s="106"/>
+      <c r="DM2" s="106"/>
+      <c r="DN2" s="106"/>
+      <c r="DO2" s="106"/>
+      <c r="DP2" s="106"/>
+      <c r="DQ2" s="106"/>
+      <c r="DR2" s="106"/>
+      <c r="DS2" s="106"/>
+      <c r="DT2" s="106"/>
+      <c r="DU2" s="106"/>
+      <c r="DV2" s="106"/>
+      <c r="DW2" s="106"/>
+      <c r="DX2" s="106"/>
+      <c r="DY2" s="106"/>
+      <c r="DZ2" s="106"/>
+      <c r="EA2" s="106"/>
+      <c r="EB2" s="106"/>
+      <c r="EC2" s="106"/>
+      <c r="ED2" s="106"/>
+      <c r="EE2" s="106"/>
+      <c r="EF2" s="106"/>
+      <c r="EG2" s="106"/>
+      <c r="EH2" s="106"/>
+      <c r="EI2" s="106"/>
+      <c r="EJ2" s="106"/>
+      <c r="EK2" s="106"/>
+      <c r="EL2" s="106"/>
+      <c r="EM2" s="106"/>
+      <c r="EN2" s="106"/>
+      <c r="EO2" s="106"/>
+      <c r="EP2" s="106"/>
+      <c r="EQ2" s="106"/>
+      <c r="ER2" s="106"/>
+      <c r="ES2" s="106"/>
+      <c r="ET2" s="106"/>
+      <c r="EU2" s="106"/>
+      <c r="EV2" s="106"/>
+      <c r="EW2" s="106"/>
+      <c r="EX2" s="106"/>
+      <c r="EY2" s="106"/>
+      <c r="EZ2" s="106"/>
+      <c r="FA2" s="106"/>
+      <c r="FB2" s="106"/>
+      <c r="FC2" s="106"/>
+      <c r="FD2" s="106"/>
+      <c r="FE2" s="106"/>
+      <c r="FF2" s="106"/>
+      <c r="FG2" s="106"/>
+      <c r="FH2" s="106"/>
+      <c r="FI2" s="106"/>
+      <c r="FJ2" s="106"/>
+      <c r="FK2" s="106"/>
+      <c r="FL2" s="106"/>
+      <c r="FM2" s="106"/>
+      <c r="FN2" s="106"/>
+      <c r="FO2" s="106"/>
+      <c r="FP2" s="106"/>
+      <c r="FQ2" s="106"/>
+      <c r="FR2" s="106"/>
+      <c r="FS2" s="106"/>
+      <c r="FT2" s="106"/>
+      <c r="FU2" s="106"/>
+      <c r="FV2" s="106"/>
+      <c r="FW2" s="106"/>
+      <c r="FX2" s="106"/>
+      <c r="FY2" s="106"/>
+      <c r="FZ2" s="106"/>
+      <c r="GA2" s="106"/>
+      <c r="GB2" s="106"/>
+      <c r="GC2" s="106"/>
+      <c r="GD2" s="106"/>
+      <c r="GE2" s="106"/>
+      <c r="GF2" s="106"/>
+      <c r="GG2" s="106"/>
+      <c r="GH2" s="106"/>
+      <c r="GI2" s="106"/>
+      <c r="GJ2" s="106"/>
+      <c r="GK2" s="106"/>
+      <c r="GL2" s="106"/>
+      <c r="GM2" s="106"/>
+      <c r="GN2" s="106"/>
+      <c r="GO2" s="106"/>
+      <c r="GP2" s="106"/>
+      <c r="GQ2" s="106"/>
+      <c r="GR2" s="106"/>
+      <c r="GS2" s="106"/>
+      <c r="GT2" s="106"/>
+      <c r="GU2" s="106"/>
+      <c r="GV2" s="106"/>
+      <c r="GW2" s="106"/>
+      <c r="GX2" s="106"/>
+      <c r="GY2" s="106"/>
+      <c r="GZ2" s="106"/>
+      <c r="HA2" s="106"/>
+      <c r="HB2" s="106"/>
+      <c r="HC2" s="106"/>
+      <c r="HD2" s="106"/>
+      <c r="HE2" s="106"/>
+      <c r="HF2" s="106"/>
+      <c r="HG2" s="106"/>
+      <c r="HH2" s="106"/>
+      <c r="HI2" s="106"/>
+      <c r="HJ2" s="106"/>
+      <c r="HK2" s="106"/>
+      <c r="HL2" s="106"/>
+      <c r="HM2" s="106"/>
+      <c r="HN2" s="106"/>
+      <c r="HO2" s="106"/>
+      <c r="HP2" s="106"/>
+      <c r="HQ2" s="106"/>
+      <c r="HR2" s="106"/>
+      <c r="HS2" s="106"/>
+      <c r="HT2" s="106"/>
+      <c r="HU2" s="106"/>
+      <c r="HV2" s="106"/>
+      <c r="HW2" s="106"/>
+      <c r="HX2" s="106"/>
+      <c r="HY2" s="106"/>
+      <c r="HZ2" s="106"/>
+      <c r="IA2" s="106"/>
+      <c r="IB2" s="106"/>
+      <c r="IC2" s="106"/>
+      <c r="ID2" s="106"/>
+      <c r="IE2" s="106"/>
+      <c r="IF2" s="106"/>
+      <c r="IG2" s="106"/>
+      <c r="IH2" s="106"/>
+      <c r="II2" s="106"/>
+      <c r="IJ2" s="106"/>
+      <c r="IK2" s="106"/>
+      <c r="IL2" s="106"/>
+      <c r="IM2" s="106"/>
+      <c r="IN2" s="106"/>
+      <c r="IO2" s="106"/>
+      <c r="IP2" s="106"/>
+      <c r="IQ2" s="106"/>
+      <c r="IR2" s="106"/>
+      <c r="IS2" s="106"/>
+      <c r="IT2" s="106"/>
+      <c r="IU2" s="106"/>
+      <c r="IV2" s="106"/>
+      <c r="IW2" s="106"/>
+    </row>
+    <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="107"/>
       <c r="B3" s="108"/>
       <c r="C3" s="109"/>
@@ -25544,6 +33255,255 @@
         <v>37</v>
       </c>
       <c r="H3" s="108"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
+      <c r="L3" s="112"/>
+      <c r="M3" s="112"/>
+      <c r="N3" s="112"/>
+      <c r="O3" s="112"/>
+      <c r="P3" s="112"/>
+      <c r="Q3" s="112"/>
+      <c r="R3" s="112"/>
+      <c r="S3" s="112"/>
+      <c r="T3" s="112"/>
+      <c r="U3" s="112"/>
+      <c r="V3" s="112"/>
+      <c r="W3" s="112"/>
+      <c r="X3" s="112"/>
+      <c r="Y3" s="112"/>
+      <c r="Z3" s="112"/>
+      <c r="AA3" s="112"/>
+      <c r="AB3" s="112"/>
+      <c r="AC3" s="112"/>
+      <c r="AD3" s="112"/>
+      <c r="AE3" s="112"/>
+      <c r="AF3" s="112"/>
+      <c r="AG3" s="112"/>
+      <c r="AH3" s="112"/>
+      <c r="AI3" s="112"/>
+      <c r="AJ3" s="112"/>
+      <c r="AK3" s="112"/>
+      <c r="AL3" s="112"/>
+      <c r="AM3" s="112"/>
+      <c r="AN3" s="112"/>
+      <c r="AO3" s="112"/>
+      <c r="AP3" s="112"/>
+      <c r="AQ3" s="112"/>
+      <c r="AR3" s="112"/>
+      <c r="AS3" s="112"/>
+      <c r="AT3" s="112"/>
+      <c r="AU3" s="112"/>
+      <c r="AV3" s="112"/>
+      <c r="AW3" s="112"/>
+      <c r="AX3" s="112"/>
+      <c r="AY3" s="112"/>
+      <c r="AZ3" s="112"/>
+      <c r="BA3" s="112"/>
+      <c r="BB3" s="112"/>
+      <c r="BC3" s="112"/>
+      <c r="BD3" s="112"/>
+      <c r="BE3" s="112"/>
+      <c r="BF3" s="112"/>
+      <c r="BG3" s="112"/>
+      <c r="BH3" s="112"/>
+      <c r="BI3" s="112"/>
+      <c r="BJ3" s="112"/>
+      <c r="BK3" s="112"/>
+      <c r="BL3" s="112"/>
+      <c r="BM3" s="112"/>
+      <c r="BN3" s="112"/>
+      <c r="BO3" s="112"/>
+      <c r="BP3" s="112"/>
+      <c r="BQ3" s="112"/>
+      <c r="BR3" s="112"/>
+      <c r="BS3" s="112"/>
+      <c r="BT3" s="112"/>
+      <c r="BU3" s="112"/>
+      <c r="BV3" s="112"/>
+      <c r="BW3" s="112"/>
+      <c r="BX3" s="112"/>
+      <c r="BY3" s="112"/>
+      <c r="BZ3" s="112"/>
+      <c r="CA3" s="112"/>
+      <c r="CB3" s="112"/>
+      <c r="CC3" s="112"/>
+      <c r="CD3" s="112"/>
+      <c r="CE3" s="112"/>
+      <c r="CF3" s="112"/>
+      <c r="CG3" s="112"/>
+      <c r="CH3" s="112"/>
+      <c r="CI3" s="112"/>
+      <c r="CJ3" s="112"/>
+      <c r="CK3" s="112"/>
+      <c r="CL3" s="112"/>
+      <c r="CM3" s="112"/>
+      <c r="CN3" s="112"/>
+      <c r="CO3" s="112"/>
+      <c r="CP3" s="112"/>
+      <c r="CQ3" s="112"/>
+      <c r="CR3" s="112"/>
+      <c r="CS3" s="112"/>
+      <c r="CT3" s="112"/>
+      <c r="CU3" s="112"/>
+      <c r="CV3" s="112"/>
+      <c r="CW3" s="112"/>
+      <c r="CX3" s="112"/>
+      <c r="CY3" s="112"/>
+      <c r="CZ3" s="112"/>
+      <c r="DA3" s="112"/>
+      <c r="DB3" s="112"/>
+      <c r="DC3" s="112"/>
+      <c r="DD3" s="112"/>
+      <c r="DE3" s="112"/>
+      <c r="DF3" s="112"/>
+      <c r="DG3" s="112"/>
+      <c r="DH3" s="112"/>
+      <c r="DI3" s="112"/>
+      <c r="DJ3" s="112"/>
+      <c r="DK3" s="112"/>
+      <c r="DL3" s="112"/>
+      <c r="DM3" s="112"/>
+      <c r="DN3" s="112"/>
+      <c r="DO3" s="112"/>
+      <c r="DP3" s="112"/>
+      <c r="DQ3" s="112"/>
+      <c r="DR3" s="112"/>
+      <c r="DS3" s="112"/>
+      <c r="DT3" s="112"/>
+      <c r="DU3" s="112"/>
+      <c r="DV3" s="112"/>
+      <c r="DW3" s="112"/>
+      <c r="DX3" s="112"/>
+      <c r="DY3" s="112"/>
+      <c r="DZ3" s="112"/>
+      <c r="EA3" s="112"/>
+      <c r="EB3" s="112"/>
+      <c r="EC3" s="112"/>
+      <c r="ED3" s="112"/>
+      <c r="EE3" s="112"/>
+      <c r="EF3" s="112"/>
+      <c r="EG3" s="112"/>
+      <c r="EH3" s="112"/>
+      <c r="EI3" s="112"/>
+      <c r="EJ3" s="112"/>
+      <c r="EK3" s="112"/>
+      <c r="EL3" s="112"/>
+      <c r="EM3" s="112"/>
+      <c r="EN3" s="112"/>
+      <c r="EO3" s="112"/>
+      <c r="EP3" s="112"/>
+      <c r="EQ3" s="112"/>
+      <c r="ER3" s="112"/>
+      <c r="ES3" s="112"/>
+      <c r="ET3" s="112"/>
+      <c r="EU3" s="112"/>
+      <c r="EV3" s="112"/>
+      <c r="EW3" s="112"/>
+      <c r="EX3" s="112"/>
+      <c r="EY3" s="112"/>
+      <c r="EZ3" s="112"/>
+      <c r="FA3" s="112"/>
+      <c r="FB3" s="112"/>
+      <c r="FC3" s="112"/>
+      <c r="FD3" s="112"/>
+      <c r="FE3" s="112"/>
+      <c r="FF3" s="112"/>
+      <c r="FG3" s="112"/>
+      <c r="FH3" s="112"/>
+      <c r="FI3" s="112"/>
+      <c r="FJ3" s="112"/>
+      <c r="FK3" s="112"/>
+      <c r="FL3" s="112"/>
+      <c r="FM3" s="112"/>
+      <c r="FN3" s="112"/>
+      <c r="FO3" s="112"/>
+      <c r="FP3" s="112"/>
+      <c r="FQ3" s="112"/>
+      <c r="FR3" s="112"/>
+      <c r="FS3" s="112"/>
+      <c r="FT3" s="112"/>
+      <c r="FU3" s="112"/>
+      <c r="FV3" s="112"/>
+      <c r="FW3" s="112"/>
+      <c r="FX3" s="112"/>
+      <c r="FY3" s="112"/>
+      <c r="FZ3" s="112"/>
+      <c r="GA3" s="112"/>
+      <c r="GB3" s="112"/>
+      <c r="GC3" s="112"/>
+      <c r="GD3" s="112"/>
+      <c r="GE3" s="112"/>
+      <c r="GF3" s="112"/>
+      <c r="GG3" s="112"/>
+      <c r="GH3" s="112"/>
+      <c r="GI3" s="112"/>
+      <c r="GJ3" s="112"/>
+      <c r="GK3" s="112"/>
+      <c r="GL3" s="112"/>
+      <c r="GM3" s="112"/>
+      <c r="GN3" s="112"/>
+      <c r="GO3" s="112"/>
+      <c r="GP3" s="112"/>
+      <c r="GQ3" s="112"/>
+      <c r="GR3" s="112"/>
+      <c r="GS3" s="112"/>
+      <c r="GT3" s="112"/>
+      <c r="GU3" s="112"/>
+      <c r="GV3" s="112"/>
+      <c r="GW3" s="112"/>
+      <c r="GX3" s="112"/>
+      <c r="GY3" s="112"/>
+      <c r="GZ3" s="112"/>
+      <c r="HA3" s="112"/>
+      <c r="HB3" s="112"/>
+      <c r="HC3" s="112"/>
+      <c r="HD3" s="112"/>
+      <c r="HE3" s="112"/>
+      <c r="HF3" s="112"/>
+      <c r="HG3" s="112"/>
+      <c r="HH3" s="112"/>
+      <c r="HI3" s="112"/>
+      <c r="HJ3" s="112"/>
+      <c r="HK3" s="112"/>
+      <c r="HL3" s="112"/>
+      <c r="HM3" s="112"/>
+      <c r="HN3" s="112"/>
+      <c r="HO3" s="112"/>
+      <c r="HP3" s="112"/>
+      <c r="HQ3" s="112"/>
+      <c r="HR3" s="112"/>
+      <c r="HS3" s="112"/>
+      <c r="HT3" s="112"/>
+      <c r="HU3" s="112"/>
+      <c r="HV3" s="112"/>
+      <c r="HW3" s="112"/>
+      <c r="HX3" s="112"/>
+      <c r="HY3" s="112"/>
+      <c r="HZ3" s="112"/>
+      <c r="IA3" s="112"/>
+      <c r="IB3" s="112"/>
+      <c r="IC3" s="112"/>
+      <c r="ID3" s="112"/>
+      <c r="IE3" s="112"/>
+      <c r="IF3" s="112"/>
+      <c r="IG3" s="112"/>
+      <c r="IH3" s="112"/>
+      <c r="II3" s="112"/>
+      <c r="IJ3" s="112"/>
+      <c r="IK3" s="112"/>
+      <c r="IL3" s="112"/>
+      <c r="IM3" s="112"/>
+      <c r="IN3" s="112"/>
+      <c r="IO3" s="112"/>
+      <c r="IP3" s="112"/>
+      <c r="IQ3" s="112"/>
+      <c r="IR3" s="112"/>
+      <c r="IS3" s="112"/>
+      <c r="IT3" s="112"/>
+      <c r="IU3" s="112"/>
+      <c r="IV3" s="112"/>
+      <c r="IW3" s="112"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="107"/>

--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -1490,10 +1490,10 @@
       <sheetData sheetId="7">
         <row r="1">
           <cell r="G1">
-            <v>5226.66666666667</v>
+            <v>5106.66666666667</v>
           </cell>
           <cell r="H1">
-            <v>26133.3333333333</v>
+            <v>25533.3333333333</v>
           </cell>
         </row>
         <row r="4">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="G9" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)</f>
-        <v>16860</v>
+        <v>16740</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="14"/>
@@ -24690,7 +24690,7 @@
       </c>
       <c r="G13" s="37" t="n">
         <f aca="false">G9+G11</f>
-        <v>16860</v>
+        <v>16740</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="14"/>
@@ -24765,7 +24765,7 @@
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">G13-G15</f>
-        <v>14754.2916666667</v>
+        <v>14634.2916666667</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14"/>
@@ -24824,7 +24824,7 @@
       </c>
       <c r="G21" s="52" t="n">
         <f aca="false">IF(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!M1:M20)&gt;0,(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20)+LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)),LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20))</f>
-        <v>84299.9999999999</v>
+        <v>83699.9999999999</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="14"/>
@@ -26783,19 +26783,19 @@
       </c>
       <c r="D17" s="86" t="n">
         <f aca="false">[2]Oct!$H$1</f>
-        <v>26133.3333333333</v>
+        <v>25533.3333333333</v>
       </c>
       <c r="E17" s="87" t="n">
         <f aca="false">SUM(D15:D17)</f>
-        <v>84299.9999999999</v>
+        <v>83699.9999999999</v>
       </c>
       <c r="F17" s="87" t="n">
         <f aca="false">[2]Oct!$G$1</f>
-        <v>5226.66666666667</v>
+        <v>5106.66666666667</v>
       </c>
       <c r="G17" s="87" t="n">
         <f aca="false">SUM(F15:F17)</f>
-        <v>16860</v>
+        <v>16740</v>
       </c>
       <c r="H17" s="87" t="n">
         <f aca="false">[3]Oct!$H$1</f>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="E18" s="87" t="n">
         <f aca="false">SUM(D16:D18)</f>
-        <v>57766.6666666666</v>
+        <v>57166.6666666666</v>
       </c>
       <c r="F18" s="87" t="n">
         <f aca="false">S04Y2!$G$1</f>
@@ -26844,7 +26844,7 @@
       </c>
       <c r="G18" s="87" t="n">
         <f aca="false">SUM(F16:F18)</f>
-        <v>11553.3333333333</v>
+        <v>11433.3333333333</v>
       </c>
       <c r="H18" s="87" t="n">
         <f aca="false">P04Y2!$H$1</f>
@@ -26885,7 +26885,7 @@
       </c>
       <c r="E19" s="87" t="n">
         <f aca="false">SUM(D17:D19)</f>
-        <v>30633.3333333333</v>
+        <v>30033.3333333333</v>
       </c>
       <c r="F19" s="87" t="n">
         <f aca="false">S05Y2!$G$1</f>
@@ -26893,7 +26893,7 @@
       </c>
       <c r="G19" s="87" t="n">
         <f aca="false">SUM(F17:F19)</f>
-        <v>6126.66666666667</v>
+        <v>6006.66666666667</v>
       </c>
       <c r="H19" s="87" t="n">
         <f aca="false">P05Y2!$H$1</f>
